--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1350"/>
+  <dimension ref="A1:G1707"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -31449,9 +31449,8220 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1351">
+      <c r="A1351" t="str">
+        <v>V-1774645155809-28rgu</v>
+      </c>
+      <c r="B1351" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1351" t="str">
+        <v>03:59 p. m.</v>
+      </c>
+      <c r="D1351" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1351" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1351">
+        <v>10000</v>
+      </c>
+      <c r="G1351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="str">
+        <v>V-1774645232870-r1faj</v>
+      </c>
+      <c r="B1352" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1352" t="str">
+        <v>04:00 p. m.</v>
+      </c>
+      <c r="D1352" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1352" t="str">
+        <v>Postobon y Pepsi (x2)</v>
+      </c>
+      <c r="F1352">
+        <v>10000</v>
+      </c>
+      <c r="G1352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="str">
+        <v>V-1774645496279-vdubz</v>
+      </c>
+      <c r="B1353" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1353" t="str">
+        <v>04:04 p. m.</v>
+      </c>
+      <c r="D1353" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1353" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1353">
+        <v>10000</v>
+      </c>
+      <c r="G1353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="str">
+        <v>V-1774645828923-73w91</v>
+      </c>
+      <c r="B1354" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1354" t="str">
+        <v>04:10 p. m.</v>
+      </c>
+      <c r="D1354" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1354" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1354">
+        <v>10000</v>
+      </c>
+      <c r="G1354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="str">
+        <v>V-1774646194119-j7qud</v>
+      </c>
+      <c r="B1355" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1355" t="str">
+        <v>04:16 p. m.</v>
+      </c>
+      <c r="D1355" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1355" t="str">
+        <v>Cerveza Poker (x1), Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1355">
+        <v>30000</v>
+      </c>
+      <c r="G1355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="str">
+        <v>V-1774646924478-hzdo8</v>
+      </c>
+      <c r="B1356" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1356" t="str">
+        <v>04:28 p. m.</v>
+      </c>
+      <c r="D1356" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1356" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F1356">
+        <v>5000</v>
+      </c>
+      <c r="G1356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="str">
+        <v>V-1774647011398-taunc</v>
+      </c>
+      <c r="B1357" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1357" t="str">
+        <v>04:30 p. m.</v>
+      </c>
+      <c r="D1357" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1357" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1357">
+        <v>5000</v>
+      </c>
+      <c r="G1357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="str">
+        <v>V-1774647214795-w2y4o</v>
+      </c>
+      <c r="B1358" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1358" t="str">
+        <v>04:33 p. m.</v>
+      </c>
+      <c r="D1358" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1358" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1358">
+        <v>20000</v>
+      </c>
+      <c r="G1358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="str">
+        <v>V-1774647500115-z3qdl</v>
+      </c>
+      <c r="B1359" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1359" t="str">
+        <v>04:38 p. m.</v>
+      </c>
+      <c r="D1359" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1359" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1359">
+        <v>10000</v>
+      </c>
+      <c r="G1359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="str">
+        <v>V-1774647972492-z3xvy</v>
+      </c>
+      <c r="B1360" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1360" t="str">
+        <v>04:46 p. m.</v>
+      </c>
+      <c r="D1360" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1360" t="str">
+        <v>Cerveza Aguila Ligth (x2), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1360">
+        <v>30000</v>
+      </c>
+      <c r="G1360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="str">
+        <v>V-1774648520769-lzx68</v>
+      </c>
+      <c r="B1361" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1361" t="str">
+        <v>04:55 p. m.</v>
+      </c>
+      <c r="D1361" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1361" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1361">
+        <v>20000</v>
+      </c>
+      <c r="G1361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="str">
+        <v>V-1774648992414-9grfi</v>
+      </c>
+      <c r="B1362" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1362" t="str">
+        <v>05:03 p. m.</v>
+      </c>
+      <c r="D1362" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1362" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1362">
+        <v>5000</v>
+      </c>
+      <c r="G1362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="str">
+        <v>V-1774649180390-e8j5b</v>
+      </c>
+      <c r="B1363" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1363" t="str">
+        <v>05:06 p. m.</v>
+      </c>
+      <c r="D1363" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1363" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1363">
+        <v>5000</v>
+      </c>
+      <c r="G1363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="str">
+        <v>V-1774649975559-4cgmi</v>
+      </c>
+      <c r="B1364" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1364" t="str">
+        <v>05:19 p. m.</v>
+      </c>
+      <c r="D1364" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1364" t="str">
+        <v>Agua Botella Grande (x2)</v>
+      </c>
+      <c r="F1364">
+        <v>10000</v>
+      </c>
+      <c r="G1364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="str">
+        <v>V-1774650083011-y9xuq</v>
+      </c>
+      <c r="B1365" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1365" t="str">
+        <v>05:21 p. m.</v>
+      </c>
+      <c r="D1365" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1365" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1365">
+        <v>10000</v>
+      </c>
+      <c r="G1365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="str">
+        <v>V-1774650369164-og6as</v>
+      </c>
+      <c r="B1366" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1366" t="str">
+        <v>05:26 p. m.</v>
+      </c>
+      <c r="D1366" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1366" t="str">
+        <v>Cerveza Club Colombia (x2), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1366">
+        <v>30000</v>
+      </c>
+      <c r="G1366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="str">
+        <v>V-1774650646701-ofv33</v>
+      </c>
+      <c r="B1367" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1367" t="str">
+        <v>05:30 p. m.</v>
+      </c>
+      <c r="D1367" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1367" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1367">
+        <v>10000</v>
+      </c>
+      <c r="G1367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="str">
+        <v>V-1774650881970-oip3s</v>
+      </c>
+      <c r="B1368" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1368" t="str">
+        <v>05:34 p. m.</v>
+      </c>
+      <c r="D1368" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1368" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1), Cerveza Club Colombia (x1), Soda (x1)</v>
+      </c>
+      <c r="F1368">
+        <v>35000</v>
+      </c>
+      <c r="G1368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="str">
+        <v>V-1774651270303-3ajvr</v>
+      </c>
+      <c r="B1369" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1369" t="str">
+        <v>05:41 p. m.</v>
+      </c>
+      <c r="D1369" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1369" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1369">
+        <v>10000</v>
+      </c>
+      <c r="G1369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="str">
+        <v>V-1774651361879-qs834</v>
+      </c>
+      <c r="B1370" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1370" t="str">
+        <v>05:42 p. m.</v>
+      </c>
+      <c r="D1370" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1370" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1370">
+        <v>10000</v>
+      </c>
+      <c r="G1370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="str">
+        <v>V-1774651843513-9i8t8</v>
+      </c>
+      <c r="B1371" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1371" t="str">
+        <v>05:50 p. m.</v>
+      </c>
+      <c r="D1371" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1371" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1371">
+        <v>10000</v>
+      </c>
+      <c r="G1371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="str">
+        <v>V-1774652208828-me081</v>
+      </c>
+      <c r="B1372" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1372" t="str">
+        <v>05:56 p. m.</v>
+      </c>
+      <c r="D1372" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1372" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1372">
+        <v>10000</v>
+      </c>
+      <c r="G1372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="str">
+        <v>V-1774652304881-7kw29</v>
+      </c>
+      <c r="B1373" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1373" t="str">
+        <v>05:58 p. m.</v>
+      </c>
+      <c r="D1373" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1373" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1373">
+        <v>10000</v>
+      </c>
+      <c r="G1373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="str">
+        <v>V-1774652737531-lu2fz</v>
+      </c>
+      <c r="B1374" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1374" t="str">
+        <v>06:05 p. m.</v>
+      </c>
+      <c r="D1374" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1374" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1374">
+        <v>10000</v>
+      </c>
+      <c r="G1374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="str">
+        <v>V-1774652920379-ewmsb</v>
+      </c>
+      <c r="B1375" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1375" t="str">
+        <v>06:08 p. m.</v>
+      </c>
+      <c r="D1375" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1375" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1375">
+        <v>10000</v>
+      </c>
+      <c r="G1375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="str">
+        <v>V-1774652999474-ylltg</v>
+      </c>
+      <c r="B1376" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1376" t="str">
+        <v>06:10 p. m.</v>
+      </c>
+      <c r="D1376" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1376" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1376">
+        <v>10000</v>
+      </c>
+      <c r="G1376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="str">
+        <v>V-1774653119687-qy86y</v>
+      </c>
+      <c r="B1377" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1377" t="str">
+        <v>06:12 p. m.</v>
+      </c>
+      <c r="D1377" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1377" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1377">
+        <v>10000</v>
+      </c>
+      <c r="G1377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="str">
+        <v>V-1774653326843-mjzq5</v>
+      </c>
+      <c r="B1378" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1378" t="str">
+        <v>06:15 p. m.</v>
+      </c>
+      <c r="D1378" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1378" t="str">
+        <v>Cerveza Poker (x1), Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1378">
+        <v>30000</v>
+      </c>
+      <c r="G1378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="str">
+        <v>V-1774653512081-j4h9q</v>
+      </c>
+      <c r="B1379" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1379" t="str">
+        <v>06:18 p. m.</v>
+      </c>
+      <c r="D1379" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1379" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1379">
+        <v>5000</v>
+      </c>
+      <c r="G1379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="str">
+        <v>V-1774653557303-gkjch</v>
+      </c>
+      <c r="B1380" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1380" t="str">
+        <v>06:19 p. m.</v>
+      </c>
+      <c r="D1380" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1380" t="str">
+        <v>Agua Botella Grande (x1)</v>
+      </c>
+      <c r="F1380">
+        <v>5000</v>
+      </c>
+      <c r="G1380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="str">
+        <v>V-1774653709755-n7d3x</v>
+      </c>
+      <c r="B1381" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1381" t="str">
+        <v>06:21 p. m.</v>
+      </c>
+      <c r="D1381" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1381" t="str">
+        <v>Cerveza Poker (x4)</v>
+      </c>
+      <c r="F1381">
+        <v>40000</v>
+      </c>
+      <c r="G1381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="str">
+        <v>V-1774653927137-shkfx</v>
+      </c>
+      <c r="B1382" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1382" t="str">
+        <v>06:25 p. m.</v>
+      </c>
+      <c r="D1382" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1382" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1382">
+        <v>20000</v>
+      </c>
+      <c r="G1382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="str">
+        <v>V-1774654083675-01s6q</v>
+      </c>
+      <c r="B1383" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1383" t="str">
+        <v>06:28 p. m.</v>
+      </c>
+      <c r="D1383" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1383" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1383">
+        <v>20000</v>
+      </c>
+      <c r="G1383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="str">
+        <v>V-1774654190380-0mchw</v>
+      </c>
+      <c r="B1384" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1384" t="str">
+        <v>06:29 p. m.</v>
+      </c>
+      <c r="D1384" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1384" t="str">
+        <v>Cerveza Poker (x2), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1384">
+        <v>30000</v>
+      </c>
+      <c r="G1384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="str">
+        <v>V-1774654469340-31flj</v>
+      </c>
+      <c r="B1385" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1385" t="str">
+        <v>06:34 p. m.</v>
+      </c>
+      <c r="D1385" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1385" t="str">
+        <v>Cerveza Club Colombia (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1385">
+        <v>20000</v>
+      </c>
+      <c r="G1385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="str">
+        <v>V-1774654674398-c2h1n</v>
+      </c>
+      <c r="B1386" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1386" t="str">
+        <v>06:37 p. m.</v>
+      </c>
+      <c r="D1386" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1386" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1386">
+        <v>5000</v>
+      </c>
+      <c r="G1386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="str">
+        <v>V-1774654759436-3jlfq</v>
+      </c>
+      <c r="B1387" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1387" t="str">
+        <v>06:39 p. m.</v>
+      </c>
+      <c r="D1387" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1387" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1387">
+        <v>10000</v>
+      </c>
+      <c r="G1387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="str">
+        <v>V-1774655025319-d5o5n</v>
+      </c>
+      <c r="B1388" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1388" t="str">
+        <v>06:43 p. m.</v>
+      </c>
+      <c r="D1388" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1388" t="str">
+        <v>Agua Botella Pequeña (x1)</v>
+      </c>
+      <c r="F1388">
+        <v>3000</v>
+      </c>
+      <c r="G1388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="str">
+        <v>V-1774655441037-wjun5</v>
+      </c>
+      <c r="B1389" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1389" t="str">
+        <v>06:50 p. m.</v>
+      </c>
+      <c r="D1389" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1389" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1389">
+        <v>10000</v>
+      </c>
+      <c r="G1389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="str">
+        <v>V-1774655590700-b1fkq</v>
+      </c>
+      <c r="B1390" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1390" t="str">
+        <v>06:53 p. m.</v>
+      </c>
+      <c r="D1390" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1390" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1390">
+        <v>20000</v>
+      </c>
+      <c r="G1390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="str">
+        <v>V-1774655933271-lgflf</v>
+      </c>
+      <c r="B1391" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1391" t="str">
+        <v>06:58 p. m.</v>
+      </c>
+      <c r="D1391" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1391" t="str">
+        <v>Soda (x2), Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1391">
+        <v>88000</v>
+      </c>
+      <c r="G1391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="str">
+        <v>V-1774656595694-ob0h3</v>
+      </c>
+      <c r="B1392" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1392" t="str">
+        <v>07:09 p. m.</v>
+      </c>
+      <c r="D1392" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1392" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1392">
+        <v>10000</v>
+      </c>
+      <c r="G1392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="str">
+        <v>V-1774656713302-6du9s</v>
+      </c>
+      <c r="B1393" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1393" t="str">
+        <v>07:11 p. m.</v>
+      </c>
+      <c r="D1393" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1393" t="str">
+        <v>Buchanans Media (x1)</v>
+      </c>
+      <c r="F1393">
+        <v>130000</v>
+      </c>
+      <c r="G1393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="str">
+        <v>V-1774656984312-710x6</v>
+      </c>
+      <c r="B1394" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1394" t="str">
+        <v>07:16 p. m.</v>
+      </c>
+      <c r="D1394" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1394" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1394">
+        <v>10000</v>
+      </c>
+      <c r="G1394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="str">
+        <v>V-1774657421961-e1m9c</v>
+      </c>
+      <c r="B1395" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1395" t="str">
+        <v>07:23 p. m.</v>
+      </c>
+      <c r="D1395" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1395" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1395">
+        <v>10000</v>
+      </c>
+      <c r="G1395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="str">
+        <v>V-1774657429732-aw9xc</v>
+      </c>
+      <c r="B1396" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1396" t="str">
+        <v>07:23 p. m.</v>
+      </c>
+      <c r="D1396" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1396" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1396">
+        <v>10000</v>
+      </c>
+      <c r="G1396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="str">
+        <v>V-1774657879798-b38ag</v>
+      </c>
+      <c r="B1397" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1397" t="str">
+        <v>07:31 p. m.</v>
+      </c>
+      <c r="D1397" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1397" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1397">
+        <v>20000</v>
+      </c>
+      <c r="G1397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="str">
+        <v>V-1774660046210-aarpt</v>
+      </c>
+      <c r="B1398" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1398" t="str">
+        <v>08:07 p. m.</v>
+      </c>
+      <c r="D1398" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1398" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1398">
+        <v>10000</v>
+      </c>
+      <c r="G1398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="str">
+        <v>V-1774660310381-0orvj</v>
+      </c>
+      <c r="B1399" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1399" t="str">
+        <v>08:11 p. m.</v>
+      </c>
+      <c r="D1399" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1399" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1399">
+        <v>10000</v>
+      </c>
+      <c r="G1399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="str">
+        <v>V-1774661186118-0mgnp</v>
+      </c>
+      <c r="B1400" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1400" t="str">
+        <v>08:26 p. m.</v>
+      </c>
+      <c r="D1400" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1400" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1400">
+        <v>10000</v>
+      </c>
+      <c r="G1400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="str">
+        <v>V-1774663225749-a62oy</v>
+      </c>
+      <c r="B1401" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1401" t="str">
+        <v>09:00 p. m.</v>
+      </c>
+      <c r="D1401" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1401" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1401">
+        <v>10000</v>
+      </c>
+      <c r="G1401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="str">
+        <v>V-1774665818963-uy0ot</v>
+      </c>
+      <c r="B1402" t="str">
+        <v>27/3/2026</v>
+      </c>
+      <c r="C1402" t="str">
+        <v>09:43 p. m.</v>
+      </c>
+      <c r="D1402" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1402" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1402">
+        <v>10000</v>
+      </c>
+      <c r="G1402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="str">
+        <v>V-1774744011347-u40fd</v>
+      </c>
+      <c r="B1403" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1403" t="str">
+        <v>07:26 p. m.</v>
+      </c>
+      <c r="D1403" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1403" t="str">
+        <v>Ron 5 años Media (x1), Ginger Canada Dry (x2)</v>
+      </c>
+      <c r="F1403">
+        <v>88000</v>
+      </c>
+      <c r="G1403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="str">
+        <v>V-1774744606389-svut3</v>
+      </c>
+      <c r="B1404" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1404" t="str">
+        <v>07:36 p. m.</v>
+      </c>
+      <c r="D1404" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1404" t="str">
+        <v>Ron Tradicional Botella (x1)</v>
+      </c>
+      <c r="F1404">
+        <v>104000</v>
+      </c>
+      <c r="G1404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="str">
+        <v>V-1774744614063-x4pbu</v>
+      </c>
+      <c r="B1405" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1405" t="str">
+        <v>07:36 p. m.</v>
+      </c>
+      <c r="D1405" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1405" t="str">
+        <v>Ron Tradicional Media (x1)</v>
+      </c>
+      <c r="F1405">
+        <v>68000</v>
+      </c>
+      <c r="G1405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="str">
+        <v>V-1774744803438-nremn</v>
+      </c>
+      <c r="B1406" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1406" t="str">
+        <v>07:40 p. m.</v>
+      </c>
+      <c r="D1406" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1406" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1406">
+        <v>20000</v>
+      </c>
+      <c r="G1406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="str">
+        <v>V-1774744852376-tbtet</v>
+      </c>
+      <c r="B1407" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1407" t="str">
+        <v>07:40 p. m.</v>
+      </c>
+      <c r="D1407" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1407" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1407">
+        <v>110000</v>
+      </c>
+      <c r="G1407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="str">
+        <v>V-1774744868037-lzaa8</v>
+      </c>
+      <c r="B1408" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1408" t="str">
+        <v>07:41 p. m.</v>
+      </c>
+      <c r="D1408" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1408" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1408">
+        <v>20000</v>
+      </c>
+      <c r="G1408">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="str">
+        <v>V-1774745164185-wnsne</v>
+      </c>
+      <c r="B1409" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1409" t="str">
+        <v>07:46 p. m.</v>
+      </c>
+      <c r="D1409" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1409" t="str">
+        <v>Ron 8 años Botella (x1)</v>
+      </c>
+      <c r="F1409">
+        <v>156000</v>
+      </c>
+      <c r="G1409">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="str">
+        <v>V-1774745174165-0lg1o</v>
+      </c>
+      <c r="B1410" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1410" t="str">
+        <v>07:46 p. m.</v>
+      </c>
+      <c r="D1410" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1410" t="str">
+        <v>Soda (x2)</v>
+      </c>
+      <c r="F1410">
+        <v>10000</v>
+      </c>
+      <c r="G1410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="str">
+        <v>V-1774745331229-c9baw</v>
+      </c>
+      <c r="B1411" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1411" t="str">
+        <v>07:48 p. m.</v>
+      </c>
+      <c r="D1411" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1411" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1411">
+        <v>110000</v>
+      </c>
+      <c r="G1411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="str">
+        <v>V-1774745537178-frqmd</v>
+      </c>
+      <c r="B1412" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1412" t="str">
+        <v>07:52 p. m.</v>
+      </c>
+      <c r="D1412" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1412" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1412">
+        <v>10000</v>
+      </c>
+      <c r="G1412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="str">
+        <v>V-1774746094172-3pgag</v>
+      </c>
+      <c r="B1413" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1413" t="str">
+        <v>08:01 p. m.</v>
+      </c>
+      <c r="D1413" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1413" t="str">
+        <v>Aguardiente Cristal Media (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1413">
+        <v>64000</v>
+      </c>
+      <c r="G1413">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="str">
+        <v>V-1774746246506-hhaxs</v>
+      </c>
+      <c r="B1414" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1414" t="str">
+        <v>08:04 p. m.</v>
+      </c>
+      <c r="D1414" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1414" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1414">
+        <v>70000</v>
+      </c>
+      <c r="G1414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="str">
+        <v>V-1774746253939-6id62</v>
+      </c>
+      <c r="B1415" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1415" t="str">
+        <v>08:04 p. m.</v>
+      </c>
+      <c r="D1415" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1415" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F1415">
+        <v>88000</v>
+      </c>
+      <c r="G1415">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="str">
+        <v>V-1774746425811-dsqp8</v>
+      </c>
+      <c r="B1416" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1416" t="str">
+        <v>08:07 p. m.</v>
+      </c>
+      <c r="D1416" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1416" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1416">
+        <v>10000</v>
+      </c>
+      <c r="G1416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="str">
+        <v>V-1774746446128-0cjv6</v>
+      </c>
+      <c r="B1417" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1417" t="str">
+        <v>08:07 p. m.</v>
+      </c>
+      <c r="D1417" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1417" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1417">
+        <v>70000</v>
+      </c>
+      <c r="G1417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="str">
+        <v>V-1774746496414-m3ljr</v>
+      </c>
+      <c r="B1418" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1418" t="str">
+        <v>08:08 p. m.</v>
+      </c>
+      <c r="D1418" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1418" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1418">
+        <v>132000</v>
+      </c>
+      <c r="G1418">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="str">
+        <v>V-1774746557677-dzk0b</v>
+      </c>
+      <c r="B1419" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1419" t="str">
+        <v>08:09 p. m.</v>
+      </c>
+      <c r="D1419" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1419" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F1419">
+        <v>108000</v>
+      </c>
+      <c r="G1419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="str">
+        <v>V-1774746777710-ti8mz</v>
+      </c>
+      <c r="B1420" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1420" t="str">
+        <v>08:12 p. m.</v>
+      </c>
+      <c r="D1420" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1420" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1420">
+        <v>70000</v>
+      </c>
+      <c r="G1420">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="str">
+        <v>V-1774746887899-uoo6a</v>
+      </c>
+      <c r="B1421" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1421" t="str">
+        <v>08:14 p. m.</v>
+      </c>
+      <c r="D1421" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1421" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F1421">
+        <v>108000</v>
+      </c>
+      <c r="G1421">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="str">
+        <v>V-1774746894146-5q4qr</v>
+      </c>
+      <c r="B1422" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1422" t="str">
+        <v>08:14 p. m.</v>
+      </c>
+      <c r="D1422" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1422" t="str">
+        <v>Aguardiente Ligth Media (x1), Gatorade (x1)</v>
+      </c>
+      <c r="F1422">
+        <v>62000</v>
+      </c>
+      <c r="G1422">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="str">
+        <v>V-1774747014703-dbgr8</v>
+      </c>
+      <c r="B1423" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1423" t="str">
+        <v>08:16 p. m.</v>
+      </c>
+      <c r="D1423" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1423" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1423">
+        <v>78000</v>
+      </c>
+      <c r="G1423">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="str">
+        <v>V-1774747091000-gb6oh</v>
+      </c>
+      <c r="B1424" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1424" t="str">
+        <v>08:18 p. m.</v>
+      </c>
+      <c r="D1424" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1424" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1424">
+        <v>132000</v>
+      </c>
+      <c r="G1424">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="str">
+        <v>V-1774747127616-xk9cx</v>
+      </c>
+      <c r="B1425" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1425" t="str">
+        <v>08:18 p. m.</v>
+      </c>
+      <c r="D1425" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1425" t="str">
+        <v>Ron Tradicional Caja (x1)</v>
+      </c>
+      <c r="F1425">
+        <v>110000</v>
+      </c>
+      <c r="G1425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="str">
+        <v>V-1774747162757-htwl2</v>
+      </c>
+      <c r="B1426" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1426" t="str">
+        <v>08:19 p. m.</v>
+      </c>
+      <c r="D1426" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1426" t="str">
+        <v>Aguardiente Ligth Botella (x1), Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1426">
+        <v>174000</v>
+      </c>
+      <c r="G1426">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="str">
+        <v>V-1774747256924-f6xyh</v>
+      </c>
+      <c r="B1427" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1427" t="str">
+        <v>08:20 p. m.</v>
+      </c>
+      <c r="D1427" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1427" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1427">
+        <v>78000</v>
+      </c>
+      <c r="G1427">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="str">
+        <v>V-1774747328285-unpjg</v>
+      </c>
+      <c r="B1428" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1428" t="str">
+        <v>08:22 p. m.</v>
+      </c>
+      <c r="D1428" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1428" t="str">
+        <v>Ron Tradicional Media (x1)</v>
+      </c>
+      <c r="F1428">
+        <v>68000</v>
+      </c>
+      <c r="G1428">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="str">
+        <v>V-1774747343965-q9llx</v>
+      </c>
+      <c r="B1429" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1429" t="str">
+        <v>08:22 p. m.</v>
+      </c>
+      <c r="D1429" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1429" t="str">
+        <v>Coca Cola (x2)</v>
+      </c>
+      <c r="F1429">
+        <v>10000</v>
+      </c>
+      <c r="G1429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="str">
+        <v>V-1774747454739-4yoqw</v>
+      </c>
+      <c r="B1430" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1430" t="str">
+        <v>08:24 p. m.</v>
+      </c>
+      <c r="D1430" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1430" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1430">
+        <v>56000</v>
+      </c>
+      <c r="G1430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="str">
+        <v>V-1774747461050-oengv</v>
+      </c>
+      <c r="B1431" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1431" t="str">
+        <v>08:24 p. m.</v>
+      </c>
+      <c r="D1431" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1431" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1431">
+        <v>70000</v>
+      </c>
+      <c r="G1431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="str">
+        <v>V-1774747552046-o6mme</v>
+      </c>
+      <c r="B1432" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1432" t="str">
+        <v>08:25 p. m.</v>
+      </c>
+      <c r="D1432" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1432" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1432">
+        <v>86000</v>
+      </c>
+      <c r="G1432">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="str">
+        <v>V-1774747785162-fdzga</v>
+      </c>
+      <c r="B1433" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1433" t="str">
+        <v>08:29 p. m.</v>
+      </c>
+      <c r="D1433" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1433" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1433">
+        <v>100000</v>
+      </c>
+      <c r="G1433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="str">
+        <v>V-1774747858545-c3di0</v>
+      </c>
+      <c r="B1434" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1434" t="str">
+        <v>08:30 p. m.</v>
+      </c>
+      <c r="D1434" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1434" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1434">
+        <v>70000</v>
+      </c>
+      <c r="G1434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="str">
+        <v>V-1774747897490-k6viv</v>
+      </c>
+      <c r="B1435" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1435" t="str">
+        <v>08:31 p. m.</v>
+      </c>
+      <c r="D1435" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1435" t="str">
+        <v>Aguardiente Cristal Media (x1), Cerveza Poker (x1), Soda (x1)</v>
+      </c>
+      <c r="F1435">
+        <v>69000</v>
+      </c>
+      <c r="G1435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="str">
+        <v>V-1774747915263-lpapj</v>
+      </c>
+      <c r="B1436" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1436" t="str">
+        <v>08:31 p. m.</v>
+      </c>
+      <c r="D1436" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1436" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1436">
+        <v>20000</v>
+      </c>
+      <c r="G1436">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="str">
+        <v>V-1774747987830-siwqp</v>
+      </c>
+      <c r="B1437" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1437" t="str">
+        <v>08:33 p. m.</v>
+      </c>
+      <c r="D1437" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1437" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1437">
+        <v>20000</v>
+      </c>
+      <c r="G1437">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="str">
+        <v>V-1774748080778-tbd9g</v>
+      </c>
+      <c r="B1438" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1438" t="str">
+        <v>08:34 p. m.</v>
+      </c>
+      <c r="D1438" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1438" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1438">
+        <v>86000</v>
+      </c>
+      <c r="G1438">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="str">
+        <v>V-1774748161463-53pu7</v>
+      </c>
+      <c r="B1439" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1439" t="str">
+        <v>08:36 p. m.</v>
+      </c>
+      <c r="D1439" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1439" t="str">
+        <v>Ron 5 años Media (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1439">
+        <v>88000</v>
+      </c>
+      <c r="G1439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="str">
+        <v>V-1774748183400-l171n</v>
+      </c>
+      <c r="B1440" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1440" t="str">
+        <v>08:36 p. m.</v>
+      </c>
+      <c r="D1440" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1440" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1440">
+        <v>114000</v>
+      </c>
+      <c r="G1440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="str">
+        <v>V-1774748189541-kxf8v</v>
+      </c>
+      <c r="B1441" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1441" t="str">
+        <v>08:36 p. m.</v>
+      </c>
+      <c r="D1441" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1441" t="str">
+        <v>Ron 8 años Media (x1), Ginger Canada Dry (x1)</v>
+      </c>
+      <c r="F1441">
+        <v>93000</v>
+      </c>
+      <c r="G1441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="str">
+        <v>V-1774748285592-xml38</v>
+      </c>
+      <c r="B1442" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1442" t="str">
+        <v>08:38 p. m.</v>
+      </c>
+      <c r="D1442" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1442" t="str">
+        <v>Aguardiente Amarillo Botella (x1), Electrolit (x1), Bonfiest Bomba (x1)</v>
+      </c>
+      <c r="F1442">
+        <v>121000</v>
+      </c>
+      <c r="G1442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="str">
+        <v>V-1774748412234-06mw1</v>
+      </c>
+      <c r="B1443" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1443" t="str">
+        <v>08:40 p. m.</v>
+      </c>
+      <c r="D1443" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1443" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1443">
+        <v>110000</v>
+      </c>
+      <c r="G1443">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="str">
+        <v>V-1774748427037-vhg4m</v>
+      </c>
+      <c r="B1444" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1444" t="str">
+        <v>08:40 p. m.</v>
+      </c>
+      <c r="D1444" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1444" t="str">
+        <v>Aguardiente Amarillo Media (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1444">
+        <v>80000</v>
+      </c>
+      <c r="G1444">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="str">
+        <v>V-1774748540445-6cwi0</v>
+      </c>
+      <c r="B1445" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1445" t="str">
+        <v>08:42 p. m.</v>
+      </c>
+      <c r="D1445" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1445" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1445">
+        <v>70000</v>
+      </c>
+      <c r="G1445">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="str">
+        <v>V-1774748553858-pof3x</v>
+      </c>
+      <c r="B1446" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1446" t="str">
+        <v>08:42 p. m.</v>
+      </c>
+      <c r="D1446" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1446" t="str">
+        <v>Ginger Canada Dry (x1)</v>
+      </c>
+      <c r="F1446">
+        <v>5000</v>
+      </c>
+      <c r="G1446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="str">
+        <v>V-1774748688480-zplyq</v>
+      </c>
+      <c r="B1447" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1447" t="str">
+        <v>08:44 p. m.</v>
+      </c>
+      <c r="D1447" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1447" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F1447">
+        <v>54000</v>
+      </c>
+      <c r="G1447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="str">
+        <v>V-1774748722901-f12ic</v>
+      </c>
+      <c r="B1448" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1448" t="str">
+        <v>08:45 p. m.</v>
+      </c>
+      <c r="D1448" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1448" t="str">
+        <v>Aguardiente Ligth Caja (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1448">
+        <v>120000</v>
+      </c>
+      <c r="G1448">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="str">
+        <v>V-1774749192571-kdjuv</v>
+      </c>
+      <c r="B1449" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1449" t="str">
+        <v>08:53 p. m.</v>
+      </c>
+      <c r="D1449" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1449" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1449">
+        <v>10000</v>
+      </c>
+      <c r="G1449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="str">
+        <v>V-1774749237958-0bro4</v>
+      </c>
+      <c r="B1450" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1450" t="str">
+        <v>08:53 p. m.</v>
+      </c>
+      <c r="D1450" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1450" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1), Soda (x1)</v>
+      </c>
+      <c r="F1450">
+        <v>25000</v>
+      </c>
+      <c r="G1450">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="str">
+        <v>V-1774749380966-bvb9w</v>
+      </c>
+      <c r="B1451" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1451" t="str">
+        <v>08:56 p. m.</v>
+      </c>
+      <c r="D1451" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1451" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1451">
+        <v>10000</v>
+      </c>
+      <c r="G1451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="str">
+        <v>V-1774749512772-g9je0</v>
+      </c>
+      <c r="B1452" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1452" t="str">
+        <v>08:58 p. m.</v>
+      </c>
+      <c r="D1452" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1452" t="str">
+        <v>Cerveza Poker (x3)</v>
+      </c>
+      <c r="F1452">
+        <v>30000</v>
+      </c>
+      <c r="G1452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="str">
+        <v>V-1774749643182-bkx2h</v>
+      </c>
+      <c r="B1453" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1453" t="str">
+        <v>09:00 p. m.</v>
+      </c>
+      <c r="D1453" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1453" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1453">
+        <v>10000</v>
+      </c>
+      <c r="G1453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="str">
+        <v>V-1774749716423-tsqpp</v>
+      </c>
+      <c r="B1454" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1454" t="str">
+        <v>09:01 p. m.</v>
+      </c>
+      <c r="D1454" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1454" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1454">
+        <v>86000</v>
+      </c>
+      <c r="G1454">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="str">
+        <v>V-1774749740453-h2524</v>
+      </c>
+      <c r="B1455" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1455" t="str">
+        <v>09:02 p. m.</v>
+      </c>
+      <c r="D1455" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1455" t="str">
+        <v>Aguardiente Cristal Cuarto (x1)</v>
+      </c>
+      <c r="F1455">
+        <v>36000</v>
+      </c>
+      <c r="G1455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="str">
+        <v>V-1774749778170-iwe70</v>
+      </c>
+      <c r="B1456" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1456" t="str">
+        <v>09:02 p. m.</v>
+      </c>
+      <c r="D1456" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1456" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1456">
+        <v>100000</v>
+      </c>
+      <c r="G1456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="str">
+        <v>V-1774750051677-lld0r</v>
+      </c>
+      <c r="B1457" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1457" t="str">
+        <v>09:07 p. m.</v>
+      </c>
+      <c r="D1457" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1457" t="str">
+        <v>Aguardiente Ligth Media (x1), Cerveza Aguila Ligth (x1), Soda (x1)</v>
+      </c>
+      <c r="F1457">
+        <v>71000</v>
+      </c>
+      <c r="G1457">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="str">
+        <v>V-1774750241652-yhq9c</v>
+      </c>
+      <c r="B1458" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1458" t="str">
+        <v>09:10 p. m.</v>
+      </c>
+      <c r="D1458" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1458" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1458">
+        <v>132000</v>
+      </c>
+      <c r="G1458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="str">
+        <v>V-1774750487382-2s88n</v>
+      </c>
+      <c r="B1459" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1459" t="str">
+        <v>09:14 p. m.</v>
+      </c>
+      <c r="D1459" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1459" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1459">
+        <v>6000</v>
+      </c>
+      <c r="G1459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="str">
+        <v>V-1774750558360-wry9u</v>
+      </c>
+      <c r="B1460" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1460" t="str">
+        <v>09:15 p. m.</v>
+      </c>
+      <c r="D1460" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1460" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1460">
+        <v>70000</v>
+      </c>
+      <c r="G1460">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="str">
+        <v>V-1774750626106-2auuu</v>
+      </c>
+      <c r="B1461" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1461" t="str">
+        <v>09:17 p. m.</v>
+      </c>
+      <c r="D1461" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1461" t="str">
+        <v>Cerveza Club Colombia (x1), Gatorade (x1)</v>
+      </c>
+      <c r="F1461">
+        <v>16000</v>
+      </c>
+      <c r="G1461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="str">
+        <v>V-1774750652257-fqsiq</v>
+      </c>
+      <c r="B1462" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1462" t="str">
+        <v>09:17 p. m.</v>
+      </c>
+      <c r="D1462" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1462" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F1462">
+        <v>108000</v>
+      </c>
+      <c r="G1462">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="str">
+        <v>V-1774750855198-0bj07</v>
+      </c>
+      <c r="B1463" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1463" t="str">
+        <v>09:20 p. m.</v>
+      </c>
+      <c r="D1463" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1463" t="str">
+        <v>Aguardiente Ligth Caja (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1463">
+        <v>120000</v>
+      </c>
+      <c r="G1463">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="str">
+        <v>V-1774751145053-wekgi</v>
+      </c>
+      <c r="B1464" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1464" t="str">
+        <v>09:25 p. m.</v>
+      </c>
+      <c r="D1464" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1464" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1464">
+        <v>10000</v>
+      </c>
+      <c r="G1464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="str">
+        <v>V-1774751173266-mewac</v>
+      </c>
+      <c r="B1465" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1465" t="str">
+        <v>09:26 p. m.</v>
+      </c>
+      <c r="D1465" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1465" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1465">
+        <v>56000</v>
+      </c>
+      <c r="G1465">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="str">
+        <v>V-1774751181204-6fblf</v>
+      </c>
+      <c r="B1466" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1466" t="str">
+        <v>09:26 p. m.</v>
+      </c>
+      <c r="D1466" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1466" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1466">
+        <v>110000</v>
+      </c>
+      <c r="G1466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="str">
+        <v>V-1774751257376-wspqi</v>
+      </c>
+      <c r="B1467" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1467" t="str">
+        <v>09:27 p. m.</v>
+      </c>
+      <c r="D1467" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1467" t="str">
+        <v>Black and White (x1)</v>
+      </c>
+      <c r="F1467">
+        <v>74000</v>
+      </c>
+      <c r="G1467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="str">
+        <v>V-1774751268413-h70yz</v>
+      </c>
+      <c r="B1468" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1468" t="str">
+        <v>09:27 p. m.</v>
+      </c>
+      <c r="D1468" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1468" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1468">
+        <v>56000</v>
+      </c>
+      <c r="G1468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="str">
+        <v>V-1774751304629-0g6kj</v>
+      </c>
+      <c r="B1469" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1469" t="str">
+        <v>09:28 p. m.</v>
+      </c>
+      <c r="D1469" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1469" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1469">
+        <v>86000</v>
+      </c>
+      <c r="G1469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="str">
+        <v>V-1774751306272-10kgz</v>
+      </c>
+      <c r="B1470" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1470" t="str">
+        <v>09:28 p. m.</v>
+      </c>
+      <c r="D1470" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1470" t="str">
+        <v>Ron 5 años Media (x1), Coca Cola (x1)</v>
+      </c>
+      <c r="F1470">
+        <v>83000</v>
+      </c>
+      <c r="G1470">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="str">
+        <v>V-1774751402820-xdq6d</v>
+      </c>
+      <c r="B1471" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1471" t="str">
+        <v>09:30 p. m.</v>
+      </c>
+      <c r="D1471" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1471" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1471">
+        <v>100000</v>
+      </c>
+      <c r="G1471">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="str">
+        <v>V-1774751407259-bxik2</v>
+      </c>
+      <c r="B1472" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1472" t="str">
+        <v>09:30 p. m.</v>
+      </c>
+      <c r="D1472" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1472" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1472">
+        <v>10000</v>
+      </c>
+      <c r="G1472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="str">
+        <v>V-1774751647282-rspn8</v>
+      </c>
+      <c r="B1473" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1473" t="str">
+        <v>09:34 p. m.</v>
+      </c>
+      <c r="D1473" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1473" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1473">
+        <v>86000</v>
+      </c>
+      <c r="G1473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="str">
+        <v>V-1774752062814-y2duc</v>
+      </c>
+      <c r="B1474" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1474" t="str">
+        <v>09:41 p. m.</v>
+      </c>
+      <c r="D1474" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1474" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F1474">
+        <v>5000</v>
+      </c>
+      <c r="G1474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="str">
+        <v>V-1774752129684-u1ci5</v>
+      </c>
+      <c r="B1475" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1475" t="str">
+        <v>09:42 p. m.</v>
+      </c>
+      <c r="D1475" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1475" t="str">
+        <v>Ron 8 años Botella (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1475">
+        <v>166000</v>
+      </c>
+      <c r="G1475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="str">
+        <v>V-1774752139580-gkei3</v>
+      </c>
+      <c r="B1476" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1476" t="str">
+        <v>09:42 p. m.</v>
+      </c>
+      <c r="D1476" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1476" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F1476">
+        <v>5000</v>
+      </c>
+      <c r="G1476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="str">
+        <v>V-1774752265381-6wsdk</v>
+      </c>
+      <c r="B1477" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1477" t="str">
+        <v>09:44 p. m.</v>
+      </c>
+      <c r="D1477" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1477" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F1477">
+        <v>88000</v>
+      </c>
+      <c r="G1477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="str">
+        <v>V-1774752344122-9pptk</v>
+      </c>
+      <c r="B1478" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1478" t="str">
+        <v>09:45 p. m.</v>
+      </c>
+      <c r="D1478" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1478" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1478">
+        <v>5000</v>
+      </c>
+      <c r="G1478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="str">
+        <v>V-1774752367526-1qtdy</v>
+      </c>
+      <c r="B1479" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1479" t="str">
+        <v>09:46 p. m.</v>
+      </c>
+      <c r="D1479" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1479" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1479">
+        <v>10000</v>
+      </c>
+      <c r="G1479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="str">
+        <v>V-1774752588114-vsf8d</v>
+      </c>
+      <c r="B1480" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1480" t="str">
+        <v>09:49 p. m.</v>
+      </c>
+      <c r="D1480" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1480" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1480">
+        <v>56000</v>
+      </c>
+      <c r="G1480">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="str">
+        <v>V-1774752870557-q3g1d</v>
+      </c>
+      <c r="B1481" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1481" t="str">
+        <v>09:54 p. m.</v>
+      </c>
+      <c r="D1481" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1481" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1481">
+        <v>20000</v>
+      </c>
+      <c r="G1481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="str">
+        <v>V-1774753070550-ajqiz</v>
+      </c>
+      <c r="B1482" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1482" t="str">
+        <v>09:57 p. m.</v>
+      </c>
+      <c r="D1482" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1482" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1482">
+        <v>78000</v>
+      </c>
+      <c r="G1482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="str">
+        <v>V-1774753351236-yxtk5</v>
+      </c>
+      <c r="B1483" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1483" t="str">
+        <v>10:02 p. m.</v>
+      </c>
+      <c r="D1483" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1483" t="str">
+        <v>Cerveza Poker (x2), Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1483">
+        <v>30000</v>
+      </c>
+      <c r="G1483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="str">
+        <v>V-1774753397246-9krqo</v>
+      </c>
+      <c r="B1484" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1484" t="str">
+        <v>10:03 p. m.</v>
+      </c>
+      <c r="D1484" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1484" t="str">
+        <v>Cerveza Club Colombia Lata (x1)</v>
+      </c>
+      <c r="F1484">
+        <v>12000</v>
+      </c>
+      <c r="G1484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="str">
+        <v>V-1774753455431-5o8pd</v>
+      </c>
+      <c r="B1485" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1485" t="str">
+        <v>10:04 p. m.</v>
+      </c>
+      <c r="D1485" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1485" t="str">
+        <v>Cerveza Corona (x1), Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1485">
+        <v>90000</v>
+      </c>
+      <c r="G1485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="str">
+        <v>V-1774753549203-3ffkb</v>
+      </c>
+      <c r="B1486" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1486" t="str">
+        <v>10:05 p. m.</v>
+      </c>
+      <c r="D1486" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1486" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1486">
+        <v>20000</v>
+      </c>
+      <c r="G1486">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="str">
+        <v>V-1774753550298-c5mqj</v>
+      </c>
+      <c r="B1487" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1487" t="str">
+        <v>10:05 p. m.</v>
+      </c>
+      <c r="D1487" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1487" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1487">
+        <v>20000</v>
+      </c>
+      <c r="G1487">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="str">
+        <v>V-1774753762129-0izdp</v>
+      </c>
+      <c r="B1488" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1488" t="str">
+        <v>10:09 p. m.</v>
+      </c>
+      <c r="D1488" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1488" t="str">
+        <v>Gatorade (x2)</v>
+      </c>
+      <c r="F1488">
+        <v>12000</v>
+      </c>
+      <c r="G1488">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="str">
+        <v>V-1774754010375-amcwe</v>
+      </c>
+      <c r="B1489" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1489" t="str">
+        <v>10:13 p. m.</v>
+      </c>
+      <c r="D1489" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1489" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1489">
+        <v>70000</v>
+      </c>
+      <c r="G1489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="str">
+        <v>V-1774754034781-4ezxz</v>
+      </c>
+      <c r="B1490" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1490" t="str">
+        <v>10:13 p. m.</v>
+      </c>
+      <c r="D1490" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1490" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1490">
+        <v>5000</v>
+      </c>
+      <c r="G1490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="str">
+        <v>V-1774754132983-hnajj</v>
+      </c>
+      <c r="B1491" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1491" t="str">
+        <v>10:15 p. m.</v>
+      </c>
+      <c r="D1491" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1491" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1491">
+        <v>70000</v>
+      </c>
+      <c r="G1491">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="str">
+        <v>V-1774754146788-qqvh7</v>
+      </c>
+      <c r="B1492" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1492" t="str">
+        <v>10:15 p. m.</v>
+      </c>
+      <c r="D1492" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1492" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1492">
+        <v>10000</v>
+      </c>
+      <c r="G1492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="str">
+        <v>V-1774754187074-ycvcj</v>
+      </c>
+      <c r="B1493" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1493" t="str">
+        <v>10:16 p. m.</v>
+      </c>
+      <c r="D1493" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1493" t="str">
+        <v>Ron Tradicional Caja (x1)</v>
+      </c>
+      <c r="F1493">
+        <v>110000</v>
+      </c>
+      <c r="G1493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="str">
+        <v>V-1774754267444-xcihz</v>
+      </c>
+      <c r="B1494" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1494" t="str">
+        <v>10:17 p. m.</v>
+      </c>
+      <c r="D1494" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1494" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1494">
+        <v>10000</v>
+      </c>
+      <c r="G1494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="str">
+        <v>V-1774754512964-4ltct</v>
+      </c>
+      <c r="B1495" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1495" t="str">
+        <v>10:21 p. m.</v>
+      </c>
+      <c r="D1495" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1495" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1495">
+        <v>20000</v>
+      </c>
+      <c r="G1495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="str">
+        <v>V-1774754513596-u8edg</v>
+      </c>
+      <c r="B1496" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1496" t="str">
+        <v>10:21 p. m.</v>
+      </c>
+      <c r="D1496" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1496" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1496">
+        <v>20000</v>
+      </c>
+      <c r="G1496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="str">
+        <v>V-1774754758908-mob6e</v>
+      </c>
+      <c r="B1497" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1497" t="str">
+        <v>10:25 p. m.</v>
+      </c>
+      <c r="D1497" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1497" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1497">
+        <v>20000</v>
+      </c>
+      <c r="G1497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="str">
+        <v>V-1774755097232-2fqty</v>
+      </c>
+      <c r="B1498" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1498" t="str">
+        <v>10:31 p. m.</v>
+      </c>
+      <c r="D1498" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1498" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F1498">
+        <v>54000</v>
+      </c>
+      <c r="G1498">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="str">
+        <v>V-1774755353849-5w8nt</v>
+      </c>
+      <c r="B1499" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1499" t="str">
+        <v>10:35 p. m.</v>
+      </c>
+      <c r="D1499" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1499" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1499">
+        <v>20000</v>
+      </c>
+      <c r="G1499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="str">
+        <v>V-1774755503889-zo3rb</v>
+      </c>
+      <c r="B1500" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1500" t="str">
+        <v>10:38 p. m.</v>
+      </c>
+      <c r="D1500" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1500" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1500">
+        <v>86000</v>
+      </c>
+      <c r="G1500">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="str">
+        <v>V-1774756069634-div94</v>
+      </c>
+      <c r="B1501" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1501" t="str">
+        <v>10:47 p. m.</v>
+      </c>
+      <c r="D1501" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1501" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1501">
+        <v>5000</v>
+      </c>
+      <c r="G1501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="str">
+        <v>V-1774756310434-gvlv6</v>
+      </c>
+      <c r="B1502" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1502" t="str">
+        <v>10:51 p. m.</v>
+      </c>
+      <c r="D1502" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1502" t="str">
+        <v>Postobon y Pepsi (x2)</v>
+      </c>
+      <c r="F1502">
+        <v>10000</v>
+      </c>
+      <c r="G1502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="str">
+        <v>V-1774756442729-xzgzx</v>
+      </c>
+      <c r="B1503" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1503" t="str">
+        <v>10:54 p. m.</v>
+      </c>
+      <c r="D1503" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1503" t="str">
+        <v>Soda (x2)</v>
+      </c>
+      <c r="F1503">
+        <v>10000</v>
+      </c>
+      <c r="G1503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="str">
+        <v>V-1774756573242-ydym6</v>
+      </c>
+      <c r="B1504" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1504" t="str">
+        <v>10:56 p. m.</v>
+      </c>
+      <c r="D1504" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1504" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1504">
+        <v>10000</v>
+      </c>
+      <c r="G1504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="str">
+        <v>V-1774756714145-v9pl8</v>
+      </c>
+      <c r="B1505" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1505" t="str">
+        <v>10:58 p. m.</v>
+      </c>
+      <c r="D1505" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1505" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1505">
+        <v>10000</v>
+      </c>
+      <c r="G1505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="str">
+        <v>V-1774756828066-hjcsz</v>
+      </c>
+      <c r="B1506" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1506" t="str">
+        <v>11:00 p. m.</v>
+      </c>
+      <c r="D1506" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1506" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1506">
+        <v>20000</v>
+      </c>
+      <c r="G1506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="str">
+        <v>V-1774756850430-84p1q</v>
+      </c>
+      <c r="B1507" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1507" t="str">
+        <v>11:00 p. m.</v>
+      </c>
+      <c r="D1507" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1507" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1507">
+        <v>10000</v>
+      </c>
+      <c r="G1507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="str">
+        <v>V-1774756897104-payvt</v>
+      </c>
+      <c r="B1508" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1508" t="str">
+        <v>11:01 p. m.</v>
+      </c>
+      <c r="D1508" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1508" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1508">
+        <v>86000</v>
+      </c>
+      <c r="G1508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="str">
+        <v>V-1774756987798-e0fgy</v>
+      </c>
+      <c r="B1509" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1509" t="str">
+        <v>11:03 p. m.</v>
+      </c>
+      <c r="D1509" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1509" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1509">
+        <v>56000</v>
+      </c>
+      <c r="G1509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="str">
+        <v>V-1774757092980-d0gil</v>
+      </c>
+      <c r="B1510" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1510" t="str">
+        <v>11:04 p. m.</v>
+      </c>
+      <c r="D1510" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1510" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1510">
+        <v>6000</v>
+      </c>
+      <c r="G1510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="str">
+        <v>V-1774757132728-zghxb</v>
+      </c>
+      <c r="B1511" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1511" t="str">
+        <v>11:05 p. m.</v>
+      </c>
+      <c r="D1511" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1511" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1511">
+        <v>10000</v>
+      </c>
+      <c r="G1511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="str">
+        <v>V-1774757315703-3g63l</v>
+      </c>
+      <c r="B1512" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1512" t="str">
+        <v>11:08 p. m.</v>
+      </c>
+      <c r="D1512" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1512" t="str">
+        <v>Ron 5 años Botella (x1), Gatorade (x1)</v>
+      </c>
+      <c r="F1512">
+        <v>138000</v>
+      </c>
+      <c r="G1512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="str">
+        <v>V-1774757476480-im6ln</v>
+      </c>
+      <c r="B1513" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1513" t="str">
+        <v>11:11 p. m.</v>
+      </c>
+      <c r="D1513" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1513" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1513">
+        <v>110000</v>
+      </c>
+      <c r="G1513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="str">
+        <v>V-1774757752113-vabf9</v>
+      </c>
+      <c r="B1514" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1514" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1514" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1514" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1514">
+        <v>114000</v>
+      </c>
+      <c r="G1514">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="str">
+        <v>V-1774757755928-h6sxz</v>
+      </c>
+      <c r="B1515" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1515" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1515" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1515" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1515">
+        <v>114000</v>
+      </c>
+      <c r="G1515">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="str">
+        <v>V-1774757754942-z7qr4</v>
+      </c>
+      <c r="B1516" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1516" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1516" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1516" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1516">
+        <v>114000</v>
+      </c>
+      <c r="G1516">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="str">
+        <v>V-1774757755514-nvob1</v>
+      </c>
+      <c r="B1517" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1517" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1517" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1517" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1517">
+        <v>114000</v>
+      </c>
+      <c r="G1517">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="str">
+        <v>V-1774757755663-v7tf9</v>
+      </c>
+      <c r="B1518" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1518" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1518" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1518" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1518">
+        <v>114000</v>
+      </c>
+      <c r="G1518">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="str">
+        <v>V-1774757743101-b726m</v>
+      </c>
+      <c r="B1519" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1519" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1519" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1519" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1519">
+        <v>114000</v>
+      </c>
+      <c r="G1519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="str">
+        <v>V-1774757755812-0qqpw</v>
+      </c>
+      <c r="B1520" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1520" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1520" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1520" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1520">
+        <v>114000</v>
+      </c>
+      <c r="G1520">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="str">
+        <v>V-1774757816310-deeoe</v>
+      </c>
+      <c r="B1521" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1521" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D1521" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1521" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1521">
+        <v>10000</v>
+      </c>
+      <c r="G1521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="str">
+        <v>V-1774757970871-te2qs</v>
+      </c>
+      <c r="B1522" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1522" t="str">
+        <v>11:19 p. m.</v>
+      </c>
+      <c r="D1522" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1522" t="str">
+        <v>Postobon y Pepsi (x2)</v>
+      </c>
+      <c r="F1522">
+        <v>10000</v>
+      </c>
+      <c r="G1522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="str">
+        <v>V-1774758008640-6987c</v>
+      </c>
+      <c r="B1523" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1523" t="str">
+        <v>11:20 p. m.</v>
+      </c>
+      <c r="D1523" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1523" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1523">
+        <v>10000</v>
+      </c>
+      <c r="G1523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="str">
+        <v>V-1774758125893-rld57</v>
+      </c>
+      <c r="B1524" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1524" t="str">
+        <v>11:22 p. m.</v>
+      </c>
+      <c r="D1524" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1524" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1524">
+        <v>56000</v>
+      </c>
+      <c r="G1524">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="str">
+        <v>V-1774758311787-0j6p9</v>
+      </c>
+      <c r="B1525" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1525" t="str">
+        <v>11:25 p. m.</v>
+      </c>
+      <c r="D1525" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1525" t="str">
+        <v>Aguardiente Cristal Botella (x1), Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1525">
+        <v>196000</v>
+      </c>
+      <c r="G1525">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="str">
+        <v>V-1774758320719-faf74</v>
+      </c>
+      <c r="B1526" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1526" t="str">
+        <v>11:25 p. m.</v>
+      </c>
+      <c r="D1526" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1526" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1526">
+        <v>110000</v>
+      </c>
+      <c r="G1526">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="str">
+        <v>V-1774758377182-btuvm</v>
+      </c>
+      <c r="B1527" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1527" t="str">
+        <v>11:26 p. m.</v>
+      </c>
+      <c r="D1527" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1527" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1527">
+        <v>70000</v>
+      </c>
+      <c r="G1527">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="str">
+        <v>V-1774758487449-hexvo</v>
+      </c>
+      <c r="B1528" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1528" t="str">
+        <v>11:28 p. m.</v>
+      </c>
+      <c r="D1528" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1528" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1528">
+        <v>56000</v>
+      </c>
+      <c r="G1528">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="str">
+        <v>V-1774758672797-jfi6s</v>
+      </c>
+      <c r="B1529" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1529" t="str">
+        <v>11:31 p. m.</v>
+      </c>
+      <c r="D1529" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1529" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1529">
+        <v>5000</v>
+      </c>
+      <c r="G1529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="str">
+        <v>V-1774758779481-x7vgx</v>
+      </c>
+      <c r="B1530" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1530" t="str">
+        <v>11:32 p. m.</v>
+      </c>
+      <c r="D1530" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1530" t="str">
+        <v>Ron 5 años Botella (x1), Soda (x3)</v>
+      </c>
+      <c r="F1530">
+        <v>147000</v>
+      </c>
+      <c r="G1530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="str">
+        <v>V-1774759004962-822a1</v>
+      </c>
+      <c r="B1531" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1531" t="str">
+        <v>11:36 p. m.</v>
+      </c>
+      <c r="D1531" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1531" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1531">
+        <v>10000</v>
+      </c>
+      <c r="G1531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="str">
+        <v>V-1774759006753-rg2n0</v>
+      </c>
+      <c r="B1532" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1532" t="str">
+        <v>11:36 p. m.</v>
+      </c>
+      <c r="D1532" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1532" t="str">
+        <v>Aguardiente Amarillo Botella (x1), Electrolit (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1532">
+        <v>128000</v>
+      </c>
+      <c r="G1532">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="str">
+        <v>V-1774759492967-ptz6d</v>
+      </c>
+      <c r="B1533" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1533" t="str">
+        <v>11:44 p. m.</v>
+      </c>
+      <c r="D1533" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1533" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1533">
+        <v>20000</v>
+      </c>
+      <c r="G1533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="str">
+        <v>V-1774759606827-5oosp</v>
+      </c>
+      <c r="B1534" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1534" t="str">
+        <v>11:46 p. m.</v>
+      </c>
+      <c r="D1534" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1534" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1534">
+        <v>10000</v>
+      </c>
+      <c r="G1534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="str">
+        <v>V-1774759973075-chevn</v>
+      </c>
+      <c r="B1535" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1535" t="str">
+        <v>11:52 p. m.</v>
+      </c>
+      <c r="D1535" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1535" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1535">
+        <v>10000</v>
+      </c>
+      <c r="G1535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="str">
+        <v>V-1774760129622-w278m</v>
+      </c>
+      <c r="B1536" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1536" t="str">
+        <v>11:55 p. m.</v>
+      </c>
+      <c r="D1536" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1536" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F1536">
+        <v>88000</v>
+      </c>
+      <c r="G1536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="str">
+        <v>V-1774760277088-rajcg</v>
+      </c>
+      <c r="B1537" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1537" t="str">
+        <v>11:57 p. m.</v>
+      </c>
+      <c r="D1537" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1537" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1537">
+        <v>20000</v>
+      </c>
+      <c r="G1537">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="str">
+        <v>V-1774760277490-fqsxw</v>
+      </c>
+      <c r="B1538" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1538" t="str">
+        <v>11:57 p. m.</v>
+      </c>
+      <c r="D1538" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1538" t="str">
+        <v>Ron 5 años Media (x1), Cerveza Corona (x1)</v>
+      </c>
+      <c r="F1538">
+        <v>90000</v>
+      </c>
+      <c r="G1538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="str">
+        <v>V-1774760336738-f0b7c</v>
+      </c>
+      <c r="B1539" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1539" t="str">
+        <v>11:58 p. m.</v>
+      </c>
+      <c r="D1539" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1539" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1539">
+        <v>5000</v>
+      </c>
+      <c r="G1539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="str">
+        <v>V-1774760400515-hv5bb</v>
+      </c>
+      <c r="B1540" t="str">
+        <v>28/3/2026</v>
+      </c>
+      <c r="C1540" t="str">
+        <v>11:59 p. m.</v>
+      </c>
+      <c r="D1540" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1540" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1540">
+        <v>132000</v>
+      </c>
+      <c r="G1540">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="str">
+        <v>V-1774760438815-sgag3</v>
+      </c>
+      <c r="B1541" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1541" t="str">
+        <v>12:00 a. m.</v>
+      </c>
+      <c r="D1541" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1541" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F1541">
+        <v>122000</v>
+      </c>
+      <c r="G1541">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="str">
+        <v>V-1774760886198-4kcpw</v>
+      </c>
+      <c r="B1542" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1542" t="str">
+        <v>12:08 a. m.</v>
+      </c>
+      <c r="D1542" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1542" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1542">
+        <v>10000</v>
+      </c>
+      <c r="G1542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="str">
+        <v>V-1774760952745-il8ve</v>
+      </c>
+      <c r="B1543" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1543" t="str">
+        <v>12:09 a. m.</v>
+      </c>
+      <c r="D1543" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1543" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1543">
+        <v>5000</v>
+      </c>
+      <c r="G1543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="str">
+        <v>V-1774761179899-zzdwm</v>
+      </c>
+      <c r="B1544" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1544" t="str">
+        <v>12:13 a. m.</v>
+      </c>
+      <c r="D1544" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1544" t="str">
+        <v>Ron Tradicional Caja (x1)</v>
+      </c>
+      <c r="F1544">
+        <v>110000</v>
+      </c>
+      <c r="G1544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="str">
+        <v>V-1774761193119-mdia3</v>
+      </c>
+      <c r="B1545" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1545" t="str">
+        <v>12:13 a. m.</v>
+      </c>
+      <c r="D1545" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1545" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1545">
+        <v>56000</v>
+      </c>
+      <c r="G1545">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="str">
+        <v>V-1774761199046-qyazg</v>
+      </c>
+      <c r="B1546" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1546" t="str">
+        <v>12:13 a. m.</v>
+      </c>
+      <c r="D1546" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1546" t="str">
+        <v>Bonfiest Bomba (x1)</v>
+      </c>
+      <c r="F1546">
+        <v>3000</v>
+      </c>
+      <c r="G1546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="str">
+        <v>V-1774761445564-d9yni</v>
+      </c>
+      <c r="B1547" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1547" t="str">
+        <v>12:17 a. m.</v>
+      </c>
+      <c r="D1547" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1547" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1547">
+        <v>20000</v>
+      </c>
+      <c r="G1547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="str">
+        <v>V-1774761735332-ybrch</v>
+      </c>
+      <c r="B1548" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1548" t="str">
+        <v>12:22 a. m.</v>
+      </c>
+      <c r="D1548" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1548" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1548">
+        <v>10000</v>
+      </c>
+      <c r="G1548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="str">
+        <v>V-1774762019616-4870e</v>
+      </c>
+      <c r="B1549" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1549" t="str">
+        <v>12:27 a. m.</v>
+      </c>
+      <c r="D1549" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1549" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1549">
+        <v>110000</v>
+      </c>
+      <c r="G1549">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="str">
+        <v>V-1774762075020-o9yg0</v>
+      </c>
+      <c r="B1550" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1550" t="str">
+        <v>12:27 a. m.</v>
+      </c>
+      <c r="D1550" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1550" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F1550">
+        <v>54000</v>
+      </c>
+      <c r="G1550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="str">
+        <v>V-1774762158663-6b7wc</v>
+      </c>
+      <c r="B1551" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1551" t="str">
+        <v>12:29 a. m.</v>
+      </c>
+      <c r="D1551" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1551" t="str">
+        <v>Gatorade (x1), Bonfiest Bomba (x1)</v>
+      </c>
+      <c r="F1551">
+        <v>9000</v>
+      </c>
+      <c r="G1551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="str">
+        <v>V-1774762160986-0bbhb</v>
+      </c>
+      <c r="B1552" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1552" t="str">
+        <v>12:29 a. m.</v>
+      </c>
+      <c r="D1552" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1552" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1552">
+        <v>20000</v>
+      </c>
+      <c r="G1552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="str">
+        <v>V-1774762284391-knhrn</v>
+      </c>
+      <c r="B1553" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1553" t="str">
+        <v>12:31 a. m.</v>
+      </c>
+      <c r="D1553" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1553" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1553">
+        <v>20000</v>
+      </c>
+      <c r="G1553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="str">
+        <v>V-1774762399999-usk73</v>
+      </c>
+      <c r="B1554" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1554" t="str">
+        <v>12:33 a. m.</v>
+      </c>
+      <c r="D1554" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1554" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1554">
+        <v>20000</v>
+      </c>
+      <c r="G1554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="str">
+        <v>V-1774762560141-3jd6u</v>
+      </c>
+      <c r="B1555" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1555" t="str">
+        <v>12:36 a. m.</v>
+      </c>
+      <c r="D1555" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1555" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1555">
+        <v>100000</v>
+      </c>
+      <c r="G1555">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="str">
+        <v>V-1774762665894-02azt</v>
+      </c>
+      <c r="B1556" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1556" t="str">
+        <v>12:37 a. m.</v>
+      </c>
+      <c r="D1556" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1556" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1556">
+        <v>10000</v>
+      </c>
+      <c r="G1556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="str">
+        <v>V-1774762695155-z3xgp</v>
+      </c>
+      <c r="B1557" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1557" t="str">
+        <v>12:38 a. m.</v>
+      </c>
+      <c r="D1557" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1557" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1557">
+        <v>6000</v>
+      </c>
+      <c r="G1557">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="str">
+        <v>V-1774762783989-lnsiq</v>
+      </c>
+      <c r="B1558" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1558" t="str">
+        <v>12:39 a. m.</v>
+      </c>
+      <c r="D1558" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1558" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1558">
+        <v>20000</v>
+      </c>
+      <c r="G1558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="str">
+        <v>V-1774762955714-92fws</v>
+      </c>
+      <c r="B1559" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1559" t="str">
+        <v>12:42 a. m.</v>
+      </c>
+      <c r="D1559" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1559" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1559">
+        <v>110000</v>
+      </c>
+      <c r="G1559">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="str">
+        <v>V-1774763481970-cauxl</v>
+      </c>
+      <c r="B1560" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1560" t="str">
+        <v>12:51 a. m.</v>
+      </c>
+      <c r="D1560" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1560" t="str">
+        <v>Cerveza Poker (x2), Postobon y Pepsi (x2)</v>
+      </c>
+      <c r="F1560">
+        <v>30000</v>
+      </c>
+      <c r="G1560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="str">
+        <v>V-1774763592083-fwecn</v>
+      </c>
+      <c r="B1561" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1561" t="str">
+        <v>12:53 a. m.</v>
+      </c>
+      <c r="D1561" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1561" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1561">
+        <v>5000</v>
+      </c>
+      <c r="G1561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="str">
+        <v>V-1774763731101-gynio</v>
+      </c>
+      <c r="B1562" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1562" t="str">
+        <v>12:55 a. m.</v>
+      </c>
+      <c r="D1562" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1562" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1562">
+        <v>20000</v>
+      </c>
+      <c r="G1562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="str">
+        <v>V-1774763786168-9iufw</v>
+      </c>
+      <c r="B1563" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1563" t="str">
+        <v>12:56 a. m.</v>
+      </c>
+      <c r="D1563" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1563" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1563">
+        <v>6000</v>
+      </c>
+      <c r="G1563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="str">
+        <v>V-1774763984337-py638</v>
+      </c>
+      <c r="B1564" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1564" t="str">
+        <v>12:59 a. m.</v>
+      </c>
+      <c r="D1564" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1564" t="str">
+        <v>Cerveza Aguila Ligth (x1), Soda (x1)</v>
+      </c>
+      <c r="F1564">
+        <v>15000</v>
+      </c>
+      <c r="G1564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="str">
+        <v>V-1774764048457-mz19q</v>
+      </c>
+      <c r="B1565" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1565" t="str">
+        <v>01:00 a. m.</v>
+      </c>
+      <c r="D1565" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1565" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1565">
+        <v>10000</v>
+      </c>
+      <c r="G1565">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="str">
+        <v>V-1774764049542-j7q81</v>
+      </c>
+      <c r="B1566" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1566" t="str">
+        <v>01:00 a. m.</v>
+      </c>
+      <c r="D1566" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1566" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1566">
+        <v>78000</v>
+      </c>
+      <c r="G1566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="str">
+        <v>V-1774764428730-kke6i</v>
+      </c>
+      <c r="B1567" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1567" t="str">
+        <v>01:07 a. m.</v>
+      </c>
+      <c r="D1567" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1567" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F1567">
+        <v>20000</v>
+      </c>
+      <c r="G1567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="str">
+        <v>V-1774764443982-wr6b6</v>
+      </c>
+      <c r="B1568" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1568" t="str">
+        <v>01:07 a. m.</v>
+      </c>
+      <c r="D1568" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1568" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1568">
+        <v>10000</v>
+      </c>
+      <c r="G1568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="str">
+        <v>V-1774764588266-mv9ev</v>
+      </c>
+      <c r="B1569" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1569" t="str">
+        <v>01:09 a. m.</v>
+      </c>
+      <c r="D1569" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1569" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1569">
+        <v>70000</v>
+      </c>
+      <c r="G1569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="str">
+        <v>V-1774764600552-zstx5</v>
+      </c>
+      <c r="B1570" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1570" t="str">
+        <v>01:10 a. m.</v>
+      </c>
+      <c r="D1570" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1570" t="str">
+        <v>Ron 8 años Media (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F1570">
+        <v>98000</v>
+      </c>
+      <c r="G1570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="str">
+        <v>V-1774764767439-zuxj9</v>
+      </c>
+      <c r="B1571" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1571" t="str">
+        <v>01:12 a. m.</v>
+      </c>
+      <c r="D1571" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1571" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1571">
+        <v>110000</v>
+      </c>
+      <c r="G1571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="str">
+        <v>V-1774764857084-qhb17</v>
+      </c>
+      <c r="B1572" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1572" t="str">
+        <v>01:14 a. m.</v>
+      </c>
+      <c r="D1572" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1572" t="str">
+        <v>Ron Tradicional Media (x1)</v>
+      </c>
+      <c r="F1572">
+        <v>68000</v>
+      </c>
+      <c r="G1572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="str">
+        <v>V-1774764880910-mvixw</v>
+      </c>
+      <c r="B1573" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1573" t="str">
+        <v>01:14 a. m.</v>
+      </c>
+      <c r="D1573" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1573" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1573">
+        <v>5000</v>
+      </c>
+      <c r="G1573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="str">
+        <v>V-1774764935230-12ltr</v>
+      </c>
+      <c r="B1574" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1574" t="str">
+        <v>01:15 a. m.</v>
+      </c>
+      <c r="D1574" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1574" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1574">
+        <v>20000</v>
+      </c>
+      <c r="G1574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="str">
+        <v>V-1774764962792-bqn2u</v>
+      </c>
+      <c r="B1575" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1575" t="str">
+        <v>01:16 a. m.</v>
+      </c>
+      <c r="D1575" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1575" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F1575">
+        <v>88000</v>
+      </c>
+      <c r="G1575">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="str">
+        <v>V-1774765019282-jo4gp</v>
+      </c>
+      <c r="B1576" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1576" t="str">
+        <v>01:17 a. m.</v>
+      </c>
+      <c r="D1576" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1576" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1576">
+        <v>20000</v>
+      </c>
+      <c r="G1576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="str">
+        <v>V-1774765146398-3ldse</v>
+      </c>
+      <c r="B1577" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1577" t="str">
+        <v>01:19 a. m.</v>
+      </c>
+      <c r="D1577" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E1577" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1577">
+        <v>110000</v>
+      </c>
+      <c r="G1577">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="str">
+        <v>V-1774765563514-cskok</v>
+      </c>
+      <c r="B1578" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1578" t="str">
+        <v>01:26 a. m.</v>
+      </c>
+      <c r="D1578" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1578" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1578">
+        <v>20000</v>
+      </c>
+      <c r="G1578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="str">
+        <v>V-1774765898553-6l7j5</v>
+      </c>
+      <c r="B1579" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1579" t="str">
+        <v>01:31 a. m.</v>
+      </c>
+      <c r="D1579" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1579" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1579">
+        <v>10000</v>
+      </c>
+      <c r="G1579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="str">
+        <v>V-1774766166948-2miwj</v>
+      </c>
+      <c r="B1580" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1580" t="str">
+        <v>01:36 a. m.</v>
+      </c>
+      <c r="D1580" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1580" t="str">
+        <v>Ron 5 años Media (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1580">
+        <v>88000</v>
+      </c>
+      <c r="G1580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="str">
+        <v>V-1774766749490-8rnxa</v>
+      </c>
+      <c r="B1581" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1581" t="str">
+        <v>01:45 a. m.</v>
+      </c>
+      <c r="D1581" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1581" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1581">
+        <v>10000</v>
+      </c>
+      <c r="G1581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="str">
+        <v>V-1774766776787-6osar</v>
+      </c>
+      <c r="B1582" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1582" t="str">
+        <v>01:46 a. m.</v>
+      </c>
+      <c r="D1582" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E1582" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1582">
+        <v>132000</v>
+      </c>
+      <c r="G1582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="str">
+        <v>V-1774767200503-v6p5v</v>
+      </c>
+      <c r="B1583" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1583" t="str">
+        <v>01:53 a. m.</v>
+      </c>
+      <c r="D1583" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1583" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1583">
+        <v>10000</v>
+      </c>
+      <c r="G1583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="str">
+        <v>V-1774767348621-m5qwk</v>
+      </c>
+      <c r="B1584" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1584" t="str">
+        <v>01:55 a. m.</v>
+      </c>
+      <c r="D1584" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1584" t="str">
+        <v>Cerveza Poker (x1), Cerveza Club Colombia (x5)</v>
+      </c>
+      <c r="F1584">
+        <v>60000</v>
+      </c>
+      <c r="G1584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="str">
+        <v>V-1774767842247-a88ym</v>
+      </c>
+      <c r="B1585" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1585" t="str">
+        <v>02:04 a. m.</v>
+      </c>
+      <c r="D1585" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1585" t="str">
+        <v>Cerveza Poker (x3)</v>
+      </c>
+      <c r="F1585">
+        <v>30000</v>
+      </c>
+      <c r="G1585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="str">
+        <v>V-1774768049246-nuhs9</v>
+      </c>
+      <c r="B1586" t="str">
+        <v>29/3/2026</v>
+      </c>
+      <c r="C1586" t="str">
+        <v>02:07 a. m.</v>
+      </c>
+      <c r="D1586" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E1586" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1586">
+        <v>10000</v>
+      </c>
+      <c r="G1586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="str">
+        <v>V-1775076045644-6zvk0</v>
+      </c>
+      <c r="B1587" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1587" t="str">
+        <v>03:40 p. m.</v>
+      </c>
+      <c r="D1587" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1587" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1587">
+        <v>5000</v>
+      </c>
+      <c r="G1587">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="str">
+        <v>V-1775076212397-92us6</v>
+      </c>
+      <c r="B1588" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1588" t="str">
+        <v>03:43 p. m.</v>
+      </c>
+      <c r="D1588" t="str">
+        <v>juan</v>
+      </c>
+      <c r="E1588" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1588">
+        <v>78000</v>
+      </c>
+      <c r="G1588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="str">
+        <v>V-1775076345898-lmgiv</v>
+      </c>
+      <c r="B1589" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1589" t="str">
+        <v>03:45 p. m.</v>
+      </c>
+      <c r="D1589" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1589" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1589">
+        <v>8000</v>
+      </c>
+      <c r="G1589">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="str">
+        <v>V-1775079005786-1sati</v>
+      </c>
+      <c r="B1590" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1590" t="str">
+        <v>04:30 p. m.</v>
+      </c>
+      <c r="D1590" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1590" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1590">
+        <v>8000</v>
+      </c>
+      <c r="G1590">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="str">
+        <v>V-1775079912232-4gc84</v>
+      </c>
+      <c r="B1591" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1591" t="str">
+        <v>04:45 p. m.</v>
+      </c>
+      <c r="D1591" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1591" t="str">
+        <v>Cerveza Poker (x2), Soda (x1)</v>
+      </c>
+      <c r="F1591">
+        <v>21000</v>
+      </c>
+      <c r="G1591">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="str">
+        <v>V-1775080306027-qy2xy</v>
+      </c>
+      <c r="B1592" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1592" t="str">
+        <v>04:51 p. m.</v>
+      </c>
+      <c r="D1592" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1592" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1592">
+        <v>8000</v>
+      </c>
+      <c r="G1592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="str">
+        <v>V-1775080916072-2509o</v>
+      </c>
+      <c r="B1593" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1593" t="str">
+        <v>05:01 p. m.</v>
+      </c>
+      <c r="D1593" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1593" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1593">
+        <v>8000</v>
+      </c>
+      <c r="G1593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="str">
+        <v>V-1775081904503-kq7i3</v>
+      </c>
+      <c r="B1594" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1594" t="str">
+        <v>05:18 p. m.</v>
+      </c>
+      <c r="D1594" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1594" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1594">
+        <v>8000</v>
+      </c>
+      <c r="G1594">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="str">
+        <v>V-1775081999758-iar7x</v>
+      </c>
+      <c r="B1595" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1595" t="str">
+        <v>05:19 p. m.</v>
+      </c>
+      <c r="D1595" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1595" t="str">
+        <v>Aguardiente Ligth Media (x1), Cerveza Aguila Ligth (x1), Soda (x1)</v>
+      </c>
+      <c r="F1595">
+        <v>69000</v>
+      </c>
+      <c r="G1595">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="str">
+        <v>V-1775082324473-lig9i</v>
+      </c>
+      <c r="B1596" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1596" t="str">
+        <v>05:25 p. m.</v>
+      </c>
+      <c r="D1596" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1596" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1596">
+        <v>132000</v>
+      </c>
+      <c r="G1596">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="str">
+        <v>V-1775082627162-z8uga</v>
+      </c>
+      <c r="B1597" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1597" t="str">
+        <v>05:30 p. m.</v>
+      </c>
+      <c r="D1597" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1597" t="str">
+        <v>Postobon y Pepsi (x2)</v>
+      </c>
+      <c r="F1597">
+        <v>10000</v>
+      </c>
+      <c r="G1597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="str">
+        <v>V-1775083648731-a41v5</v>
+      </c>
+      <c r="B1598" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1598" t="str">
+        <v>05:47 p. m.</v>
+      </c>
+      <c r="D1598" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1598" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1598">
+        <v>8000</v>
+      </c>
+      <c r="G1598">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="str">
+        <v>V-1775083715713-i4p1i</v>
+      </c>
+      <c r="B1599" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1599" t="str">
+        <v>05:48 p. m.</v>
+      </c>
+      <c r="D1599" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1599" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1599">
+        <v>8000</v>
+      </c>
+      <c r="G1599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="str">
+        <v>V-1775085437976-2e6gd</v>
+      </c>
+      <c r="B1600" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1600" t="str">
+        <v>06:17 p. m.</v>
+      </c>
+      <c r="D1600" t="str">
+        <v>juan</v>
+      </c>
+      <c r="E1600" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1600">
+        <v>5000</v>
+      </c>
+      <c r="G1600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="str">
+        <v>V-1775086354234-dmmrp</v>
+      </c>
+      <c r="B1601" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1601" t="str">
+        <v>06:32 p. m.</v>
+      </c>
+      <c r="D1601" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1601" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1601">
+        <v>8000</v>
+      </c>
+      <c r="G1601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="str">
+        <v>V-1775086665003-3gtqo</v>
+      </c>
+      <c r="B1602" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1602" t="str">
+        <v>06:37 p. m.</v>
+      </c>
+      <c r="D1602" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1602" t="str">
+        <v>Cerveza Aguila Ligth (x1), Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1602">
+        <v>13000</v>
+      </c>
+      <c r="G1602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="str">
+        <v>V-1775086911033-yq0vy</v>
+      </c>
+      <c r="B1603" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1603" t="str">
+        <v>06:41 p. m.</v>
+      </c>
+      <c r="D1603" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1603" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1603">
+        <v>8000</v>
+      </c>
+      <c r="G1603">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="str">
+        <v>V-1775087072904-2nr4e</v>
+      </c>
+      <c r="B1604" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1604" t="str">
+        <v>06:44 p. m.</v>
+      </c>
+      <c r="D1604" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1604" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1604">
+        <v>8000</v>
+      </c>
+      <c r="G1604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="str">
+        <v>V-1775087751845-hdnp6</v>
+      </c>
+      <c r="B1605" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1605" t="str">
+        <v>06:55 p. m.</v>
+      </c>
+      <c r="D1605" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1605" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1605">
+        <v>78000</v>
+      </c>
+      <c r="G1605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="str">
+        <v>V-1775087952194-b8grl</v>
+      </c>
+      <c r="B1606" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1606" t="str">
+        <v>06:59 p. m.</v>
+      </c>
+      <c r="D1606" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1606" t="str">
+        <v>Vinos (x1)</v>
+      </c>
+      <c r="F1606">
+        <v>60000</v>
+      </c>
+      <c r="G1606">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="str">
+        <v>V-1775088139927-wpb2b</v>
+      </c>
+      <c r="B1607" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1607" t="str">
+        <v>07:02 p. m.</v>
+      </c>
+      <c r="D1607" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1607" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1607">
+        <v>8000</v>
+      </c>
+      <c r="G1607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="str">
+        <v>V-1775088472041-khq2c</v>
+      </c>
+      <c r="B1608" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1608" t="str">
+        <v>07:07 p. m.</v>
+      </c>
+      <c r="D1608" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1608" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1), Soda (x1)</v>
+      </c>
+      <c r="F1608">
+        <v>21000</v>
+      </c>
+      <c r="G1608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="str">
+        <v>V-1775088658965-udnjy</v>
+      </c>
+      <c r="B1609" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1609" t="str">
+        <v>07:10 p. m.</v>
+      </c>
+      <c r="D1609" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1609" t="str">
+        <v>Cerveza Poker (x1), Cerveza Club Colombia (x1), Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F1609">
+        <v>21000</v>
+      </c>
+      <c r="G1609">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="str">
+        <v>V-1775090662902-9fpii</v>
+      </c>
+      <c r="B1610" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1610" t="str">
+        <v>07:44 p. m.</v>
+      </c>
+      <c r="D1610" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1610" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1610">
+        <v>8000</v>
+      </c>
+      <c r="G1610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="str">
+        <v>V-1775093639850-6cx25</v>
+      </c>
+      <c r="B1611" t="str">
+        <v>1/4/2026</v>
+      </c>
+      <c r="C1611" t="str">
+        <v>08:34 p. m.</v>
+      </c>
+      <c r="D1611" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E1611" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1611">
+        <v>8000</v>
+      </c>
+      <c r="G1611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="str">
+        <v>V-1775350544812-a1k2t</v>
+      </c>
+      <c r="B1612" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1612" t="str">
+        <v>07:55 p. m.</v>
+      </c>
+      <c r="D1612" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1612" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1612">
+        <v>78000</v>
+      </c>
+      <c r="G1612">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="str">
+        <v>V-1775350552534-m93wd</v>
+      </c>
+      <c r="B1613" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1613" t="str">
+        <v>07:55 p. m.</v>
+      </c>
+      <c r="D1613" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1613" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1613">
+        <v>56000</v>
+      </c>
+      <c r="G1613">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="str">
+        <v>V-1775351382465-e3s95</v>
+      </c>
+      <c r="B1614" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1614" t="str">
+        <v>08:09 p. m.</v>
+      </c>
+      <c r="D1614" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1614" t="str">
+        <v>Cerveza Poker (x3), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1614">
+        <v>40000</v>
+      </c>
+      <c r="G1614">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="str">
+        <v>V-1775352238871-576gi</v>
+      </c>
+      <c r="B1615" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1615" t="str">
+        <v>08:23 p. m.</v>
+      </c>
+      <c r="D1615" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1615" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F1615">
+        <v>54000</v>
+      </c>
+      <c r="G1615">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="str">
+        <v>V-1775352413709-3ih0z</v>
+      </c>
+      <c r="B1616" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1616" t="str">
+        <v>08:26 p. m.</v>
+      </c>
+      <c r="D1616" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1616" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1616">
+        <v>100000</v>
+      </c>
+      <c r="G1616">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="str">
+        <v>V-1775352487081-xgy1q</v>
+      </c>
+      <c r="B1617" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1617" t="str">
+        <v>08:28 p. m.</v>
+      </c>
+      <c r="D1617" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1617" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1617">
+        <v>10000</v>
+      </c>
+      <c r="G1617">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="str">
+        <v>V-1775352652861-m43ae</v>
+      </c>
+      <c r="B1618" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1618" t="str">
+        <v>08:30 p. m.</v>
+      </c>
+      <c r="D1618" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1618" t="str">
+        <v>Aguardiente Ligth Media (x1), Gatorade (x1)</v>
+      </c>
+      <c r="F1618">
+        <v>62000</v>
+      </c>
+      <c r="G1618">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="str">
+        <v>V-1775352745527-ra5ot</v>
+      </c>
+      <c r="B1619" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1619" t="str">
+        <v>08:32 p. m.</v>
+      </c>
+      <c r="D1619" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1619" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1619">
+        <v>10000</v>
+      </c>
+      <c r="G1619">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="str">
+        <v>V-1775353010702-ns4pt</v>
+      </c>
+      <c r="B1620" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1620" t="str">
+        <v>08:36 p. m.</v>
+      </c>
+      <c r="D1620" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1620" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1620">
+        <v>86000</v>
+      </c>
+      <c r="G1620">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="str">
+        <v>V-1775353127154-urt1c</v>
+      </c>
+      <c r="B1621" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1621" t="str">
+        <v>08:38 p. m.</v>
+      </c>
+      <c r="D1621" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1621" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1621">
+        <v>56000</v>
+      </c>
+      <c r="G1621">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="str">
+        <v>V-1775353421016-i4gjc</v>
+      </c>
+      <c r="B1622" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1622" t="str">
+        <v>08:43 p. m.</v>
+      </c>
+      <c r="D1622" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1622" t="str">
+        <v>Ron Tradicional Caja (x1)</v>
+      </c>
+      <c r="F1622">
+        <v>110000</v>
+      </c>
+      <c r="G1622">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="str">
+        <v>V-1775353533746-6mxgn</v>
+      </c>
+      <c r="B1623" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1623" t="str">
+        <v>08:45 p. m.</v>
+      </c>
+      <c r="D1623" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1623" t="str">
+        <v>Aguardiente Cristal Caja (x1), Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1623">
+        <v>210000</v>
+      </c>
+      <c r="G1623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="str">
+        <v>V-1775353610304-mxt0y</v>
+      </c>
+      <c r="B1624" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1624" t="str">
+        <v>08:46 p. m.</v>
+      </c>
+      <c r="D1624" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1624" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1624">
+        <v>86000</v>
+      </c>
+      <c r="G1624">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="str">
+        <v>V-1775353714478-75s3b</v>
+      </c>
+      <c r="B1625" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1625" t="str">
+        <v>08:48 p. m.</v>
+      </c>
+      <c r="D1625" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1625" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1625">
+        <v>100000</v>
+      </c>
+      <c r="G1625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="str">
+        <v>V-1775353868778-zl8cx</v>
+      </c>
+      <c r="B1626" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1626" t="str">
+        <v>08:51 p. m.</v>
+      </c>
+      <c r="D1626" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1626" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1626">
+        <v>86000</v>
+      </c>
+      <c r="G1626">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="str">
+        <v>V-1775353957043-rqua4</v>
+      </c>
+      <c r="B1627" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1627" t="str">
+        <v>08:52 p. m.</v>
+      </c>
+      <c r="D1627" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1627" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F1627">
+        <v>54000</v>
+      </c>
+      <c r="G1627">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="str">
+        <v>V-1775353963186-c65vf</v>
+      </c>
+      <c r="B1628" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1628" t="str">
+        <v>08:52 p. m.</v>
+      </c>
+      <c r="D1628" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1628" t="str">
+        <v>Aguardiente Amarillo Media (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1628">
+        <v>80000</v>
+      </c>
+      <c r="G1628">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="str">
+        <v>V-1775353987421-8spoq</v>
+      </c>
+      <c r="B1629" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1629" t="str">
+        <v>08:53 p. m.</v>
+      </c>
+      <c r="D1629" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1629" t="str">
+        <v>Ron 5 años Media (x1), Soda (x2)</v>
+      </c>
+      <c r="F1629">
+        <v>88000</v>
+      </c>
+      <c r="G1629">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="str">
+        <v>V-1775354127389-5lomd</v>
+      </c>
+      <c r="B1630" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1630" t="str">
+        <v>08:55 p. m.</v>
+      </c>
+      <c r="D1630" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1630" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1630">
+        <v>10000</v>
+      </c>
+      <c r="G1630">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="str">
+        <v>V-1775354259172-9rb0f</v>
+      </c>
+      <c r="B1631" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1631" t="str">
+        <v>08:57 p. m.</v>
+      </c>
+      <c r="D1631" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1631" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1631">
+        <v>5000</v>
+      </c>
+      <c r="G1631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="str">
+        <v>V-1775354573752-4pjzz</v>
+      </c>
+      <c r="B1632" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1632" t="str">
+        <v>09:02 p. m.</v>
+      </c>
+      <c r="D1632" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1632" t="str">
+        <v>Aguardiente Cristal Caja (x1), Soda (x1)</v>
+      </c>
+      <c r="F1632">
+        <v>105000</v>
+      </c>
+      <c r="G1632">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="str">
+        <v>V-1775354684295-bjopf</v>
+      </c>
+      <c r="B1633" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1633" t="str">
+        <v>09:04 p. m.</v>
+      </c>
+      <c r="D1633" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1633" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1633">
+        <v>10000</v>
+      </c>
+      <c r="G1633">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="str">
+        <v>V-1775355394949-t2mk1</v>
+      </c>
+      <c r="B1634" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1634" t="str">
+        <v>09:16 p. m.</v>
+      </c>
+      <c r="D1634" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1634" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1634">
+        <v>100000</v>
+      </c>
+      <c r="G1634">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="str">
+        <v>V-1775355577542-u5nqo</v>
+      </c>
+      <c r="B1635" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1635" t="str">
+        <v>09:19 p. m.</v>
+      </c>
+      <c r="D1635" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1635" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F1635">
+        <v>54000</v>
+      </c>
+      <c r="G1635">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="str">
+        <v>V-1775355650126-v8g80</v>
+      </c>
+      <c r="B1636" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1636" t="str">
+        <v>09:20 p. m.</v>
+      </c>
+      <c r="D1636" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1636" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1636">
+        <v>20000</v>
+      </c>
+      <c r="G1636">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="str">
+        <v>V-1775355894641-qoku7</v>
+      </c>
+      <c r="B1637" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1637" t="str">
+        <v>09:24 p. m.</v>
+      </c>
+      <c r="D1637" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1637" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1637">
+        <v>20000</v>
+      </c>
+      <c r="G1637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="str">
+        <v>V-1775356224898-kw8jq</v>
+      </c>
+      <c r="B1638" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1638" t="str">
+        <v>09:30 p. m.</v>
+      </c>
+      <c r="D1638" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1638" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1638">
+        <v>20000</v>
+      </c>
+      <c r="G1638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="str">
+        <v>V-1775356299469-x631n</v>
+      </c>
+      <c r="B1639" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1639" t="str">
+        <v>09:31 p. m.</v>
+      </c>
+      <c r="D1639" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1639" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F1639">
+        <v>86000</v>
+      </c>
+      <c r="G1639">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="str">
+        <v>V-1775356459593-r0li6</v>
+      </c>
+      <c r="B1640" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1640" t="str">
+        <v>09:34 p. m.</v>
+      </c>
+      <c r="D1640" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1640" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1640">
+        <v>10000</v>
+      </c>
+      <c r="G1640">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="str">
+        <v>V-1775356507117-9w7m6</v>
+      </c>
+      <c r="B1641" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1641" t="str">
+        <v>09:35 p. m.</v>
+      </c>
+      <c r="D1641" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1641" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1641">
+        <v>10000</v>
+      </c>
+      <c r="G1641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="str">
+        <v>V-1775356571552-lat36</v>
+      </c>
+      <c r="B1642" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1642" t="str">
+        <v>09:36 p. m.</v>
+      </c>
+      <c r="D1642" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1642" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1642">
+        <v>70000</v>
+      </c>
+      <c r="G1642">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="str">
+        <v>V-1775356881773-kysko</v>
+      </c>
+      <c r="B1643" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1643" t="str">
+        <v>09:41 p. m.</v>
+      </c>
+      <c r="D1643" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1643" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1643">
+        <v>10000</v>
+      </c>
+      <c r="G1643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="str">
+        <v>V-1775356900839-5hji6</v>
+      </c>
+      <c r="B1644" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1644" t="str">
+        <v>09:41 p. m.</v>
+      </c>
+      <c r="D1644" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1644" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1644">
+        <v>56000</v>
+      </c>
+      <c r="G1644">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="str">
+        <v>V-1775356978718-94sqh</v>
+      </c>
+      <c r="B1645" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1645" t="str">
+        <v>09:42 p. m.</v>
+      </c>
+      <c r="D1645" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1645" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F1645">
+        <v>132000</v>
+      </c>
+      <c r="G1645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="str">
+        <v>V-1775357207319-z4kpp</v>
+      </c>
+      <c r="B1646" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1646" t="str">
+        <v>09:46 p. m.</v>
+      </c>
+      <c r="D1646" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1646" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1646">
+        <v>56000</v>
+      </c>
+      <c r="G1646">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="str">
+        <v>V-1775357278440-bj9q5</v>
+      </c>
+      <c r="B1647" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1647" t="str">
+        <v>09:47 p. m.</v>
+      </c>
+      <c r="D1647" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1647" t="str">
+        <v>Ron 8 años Media (x1)</v>
+      </c>
+      <c r="F1647">
+        <v>88000</v>
+      </c>
+      <c r="G1647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="str">
+        <v>V-1775357457846-c9v53</v>
+      </c>
+      <c r="B1648" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1648" t="str">
+        <v>09:50 p. m.</v>
+      </c>
+      <c r="D1648" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1648" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1648">
+        <v>78000</v>
+      </c>
+      <c r="G1648">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="str">
+        <v>V-1775357523775-48ebm</v>
+      </c>
+      <c r="B1649" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1649" t="str">
+        <v>09:52 p. m.</v>
+      </c>
+      <c r="D1649" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1649" t="str">
+        <v>Ginger Canada Dry (x1)</v>
+      </c>
+      <c r="F1649">
+        <v>5000</v>
+      </c>
+      <c r="G1649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="str">
+        <v>V-1775357621091-uayv4</v>
+      </c>
+      <c r="B1650" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1650" t="str">
+        <v>09:53 p. m.</v>
+      </c>
+      <c r="D1650" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1650" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F1650">
+        <v>5000</v>
+      </c>
+      <c r="G1650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="str">
+        <v>V-1775357723658-5azfo</v>
+      </c>
+      <c r="B1651" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1651" t="str">
+        <v>09:55 p. m.</v>
+      </c>
+      <c r="D1651" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1651" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1651">
+        <v>10000</v>
+      </c>
+      <c r="G1651">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="str">
+        <v>V-1775358061083-wfzrj</v>
+      </c>
+      <c r="B1652" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1652" t="str">
+        <v>10:01 p. m.</v>
+      </c>
+      <c r="D1652" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1652" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1652">
+        <v>20000</v>
+      </c>
+      <c r="G1652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="str">
+        <v>V-1775358100631-v8cqv</v>
+      </c>
+      <c r="B1653" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1653" t="str">
+        <v>10:01 p. m.</v>
+      </c>
+      <c r="D1653" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1653" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F1653">
+        <v>88000</v>
+      </c>
+      <c r="G1653">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="str">
+        <v>V-1775358577144-tdomv</v>
+      </c>
+      <c r="B1654" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1654" t="str">
+        <v>10:09 p. m.</v>
+      </c>
+      <c r="D1654" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1654" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1654">
+        <v>6000</v>
+      </c>
+      <c r="G1654">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="str">
+        <v>V-1775359300043-keuca</v>
+      </c>
+      <c r="B1655" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1655" t="str">
+        <v>10:21 p. m.</v>
+      </c>
+      <c r="D1655" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1655" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1655">
+        <v>10000</v>
+      </c>
+      <c r="G1655">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="str">
+        <v>V-1775359355833-ae1ui</v>
+      </c>
+      <c r="B1656" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1656" t="str">
+        <v>10:22 p. m.</v>
+      </c>
+      <c r="D1656" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1656" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1656">
+        <v>10000</v>
+      </c>
+      <c r="G1656">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="str">
+        <v>V-1775359768513-omofi</v>
+      </c>
+      <c r="B1657" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1657" t="str">
+        <v>10:29 p. m.</v>
+      </c>
+      <c r="D1657" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1657" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1657">
+        <v>10000</v>
+      </c>
+      <c r="G1657">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="str">
+        <v>V-1775359806386-9tn5z</v>
+      </c>
+      <c r="B1658" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1658" t="str">
+        <v>10:30 p. m.</v>
+      </c>
+      <c r="D1658" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1658" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F1658">
+        <v>10000</v>
+      </c>
+      <c r="G1658">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="str">
+        <v>V-1775359997053-9u1v6</v>
+      </c>
+      <c r="B1659" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1659" t="str">
+        <v>10:33 p. m.</v>
+      </c>
+      <c r="D1659" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1659" t="str">
+        <v>Ron Tradicional Botella (x1)</v>
+      </c>
+      <c r="F1659">
+        <v>104000</v>
+      </c>
+      <c r="G1659">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="str">
+        <v>V-1775360180203-7tgvs</v>
+      </c>
+      <c r="B1660" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1660" t="str">
+        <v>10:36 p. m.</v>
+      </c>
+      <c r="D1660" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1660" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1660">
+        <v>10000</v>
+      </c>
+      <c r="G1660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="str">
+        <v>V-1775360676454-y5dzj</v>
+      </c>
+      <c r="B1661" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1661" t="str">
+        <v>10:44 p. m.</v>
+      </c>
+      <c r="D1661" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1661" t="str">
+        <v>Aguardiente Cristal Caja (x1), Soda (x1)</v>
+      </c>
+      <c r="F1661">
+        <v>105000</v>
+      </c>
+      <c r="G1661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="str">
+        <v>V-1775360748617-zmlvz</v>
+      </c>
+      <c r="B1662" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1662" t="str">
+        <v>10:45 p. m.</v>
+      </c>
+      <c r="D1662" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1662" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1662">
+        <v>20000</v>
+      </c>
+      <c r="G1662">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="str">
+        <v>V-1775361119364-wurn2</v>
+      </c>
+      <c r="B1663" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1663" t="str">
+        <v>10:52 p. m.</v>
+      </c>
+      <c r="D1663" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1663" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F1663">
+        <v>70000</v>
+      </c>
+      <c r="G1663">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="str">
+        <v>V-1775361138826-ecr2e</v>
+      </c>
+      <c r="B1664" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1664" t="str">
+        <v>10:52 p. m.</v>
+      </c>
+      <c r="D1664" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1664" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1664">
+        <v>20000</v>
+      </c>
+      <c r="G1664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="str">
+        <v>V-1775361156005-8rzo0</v>
+      </c>
+      <c r="B1665" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1665" t="str">
+        <v>10:52 p. m.</v>
+      </c>
+      <c r="D1665" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1665" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1665">
+        <v>10000</v>
+      </c>
+      <c r="G1665">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="str">
+        <v>V-1775361644870-9w17m</v>
+      </c>
+      <c r="B1666" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1666" t="str">
+        <v>11:00 p. m.</v>
+      </c>
+      <c r="D1666" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1666" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1666">
+        <v>10000</v>
+      </c>
+      <c r="G1666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="str">
+        <v>V-1775361697236-ffe6c</v>
+      </c>
+      <c r="B1667" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1667" t="str">
+        <v>11:01 p. m.</v>
+      </c>
+      <c r="D1667" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1667" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1667">
+        <v>100000</v>
+      </c>
+      <c r="G1667">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="str">
+        <v>V-1775361839669-18dso</v>
+      </c>
+      <c r="B1668" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1668" t="str">
+        <v>11:04 p. m.</v>
+      </c>
+      <c r="D1668" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1668" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1668">
+        <v>10000</v>
+      </c>
+      <c r="G1668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="str">
+        <v>V-1775361846410-8zps7</v>
+      </c>
+      <c r="B1669" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1669" t="str">
+        <v>11:04 p. m.</v>
+      </c>
+      <c r="D1669" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1669" t="str">
+        <v>Cerveza Club Colombia Lata (x1)</v>
+      </c>
+      <c r="F1669">
+        <v>12000</v>
+      </c>
+      <c r="G1669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="str">
+        <v>V-1775361915216-imior</v>
+      </c>
+      <c r="B1670" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1670" t="str">
+        <v>11:05 p. m.</v>
+      </c>
+      <c r="D1670" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1670" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1670">
+        <v>6000</v>
+      </c>
+      <c r="G1670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="str">
+        <v>V-1775362121796-yavci</v>
+      </c>
+      <c r="B1671" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1671" t="str">
+        <v>11:08 p. m.</v>
+      </c>
+      <c r="D1671" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1671" t="str">
+        <v>Descorche (x1)</v>
+      </c>
+      <c r="F1671">
+        <v>0</v>
+      </c>
+      <c r="G1671">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="str">
+        <v>V-1775362342761-mpkl5</v>
+      </c>
+      <c r="B1672" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1672" t="str">
+        <v>11:12 p. m.</v>
+      </c>
+      <c r="D1672" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1672" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F1672">
+        <v>5000</v>
+      </c>
+      <c r="G1672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="str">
+        <v>V-1775362637585-z1j17</v>
+      </c>
+      <c r="B1673" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1673" t="str">
+        <v>11:17 p. m.</v>
+      </c>
+      <c r="D1673" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1673" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1673">
+        <v>20000</v>
+      </c>
+      <c r="G1673">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="str">
+        <v>V-1775362846927-90mdt</v>
+      </c>
+      <c r="B1674" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1674" t="str">
+        <v>11:20 p. m.</v>
+      </c>
+      <c r="D1674" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1674" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1674">
+        <v>6000</v>
+      </c>
+      <c r="G1674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="str">
+        <v>V-1775363247521-k6ivt</v>
+      </c>
+      <c r="B1675" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1675" t="str">
+        <v>11:27 p. m.</v>
+      </c>
+      <c r="D1675" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1675" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1675">
+        <v>10000</v>
+      </c>
+      <c r="G1675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="str">
+        <v>V-1775363712804-yebdl</v>
+      </c>
+      <c r="B1676" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1676" t="str">
+        <v>11:35 p. m.</v>
+      </c>
+      <c r="D1676" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1676" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1676">
+        <v>10000</v>
+      </c>
+      <c r="G1676">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="str">
+        <v>V-1775364085275-3wzpz</v>
+      </c>
+      <c r="B1677" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1677" t="str">
+        <v>11:41 p. m.</v>
+      </c>
+      <c r="D1677" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1677" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1677">
+        <v>10000</v>
+      </c>
+      <c r="G1677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="str">
+        <v>V-1775364134887-zpuok</v>
+      </c>
+      <c r="B1678" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1678" t="str">
+        <v>11:42 p. m.</v>
+      </c>
+      <c r="D1678" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1678" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1678">
+        <v>6000</v>
+      </c>
+      <c r="G1678">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="str">
+        <v>V-1775364377413-o1pvi</v>
+      </c>
+      <c r="B1679" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1679" t="str">
+        <v>11:46 p. m.</v>
+      </c>
+      <c r="D1679" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1679" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1679">
+        <v>78000</v>
+      </c>
+      <c r="G1679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="str">
+        <v>V-1775364479377-9xasr</v>
+      </c>
+      <c r="B1680" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1680" t="str">
+        <v>11:48 p. m.</v>
+      </c>
+      <c r="D1680" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1680" t="str">
+        <v>Ron Tradicional Media (x1)</v>
+      </c>
+      <c r="F1680">
+        <v>68000</v>
+      </c>
+      <c r="G1680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="str">
+        <v>V-1775364613356-99ukd</v>
+      </c>
+      <c r="B1681" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1681" t="str">
+        <v>11:50 p. m.</v>
+      </c>
+      <c r="D1681" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1681" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F1681">
+        <v>56000</v>
+      </c>
+      <c r="G1681">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="str">
+        <v>V-1775364820477-80vqq</v>
+      </c>
+      <c r="B1682" t="str">
+        <v>4/4/2026</v>
+      </c>
+      <c r="C1682" t="str">
+        <v>11:53 p. m.</v>
+      </c>
+      <c r="D1682" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1682" t="str">
+        <v>Cerveza Club Colombia Lata (x1)</v>
+      </c>
+      <c r="F1682">
+        <v>12000</v>
+      </c>
+      <c r="G1682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="str">
+        <v>V-1775365333992-5tsgm</v>
+      </c>
+      <c r="B1683" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1683" t="str">
+        <v>12:02 a. m.</v>
+      </c>
+      <c r="D1683" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1683" t="str">
+        <v>Cerveza Club Colombia Lata (x1)</v>
+      </c>
+      <c r="F1683">
+        <v>12000</v>
+      </c>
+      <c r="G1683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="str">
+        <v>V-1775365358389-nr0eo</v>
+      </c>
+      <c r="B1684" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1684" t="str">
+        <v>12:02 a. m.</v>
+      </c>
+      <c r="D1684" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1684" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F1684">
+        <v>20000</v>
+      </c>
+      <c r="G1684">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="str">
+        <v>V-1775365468753-6vx4p</v>
+      </c>
+      <c r="B1685" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1685" t="str">
+        <v>12:04 a. m.</v>
+      </c>
+      <c r="D1685" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1685" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1685">
+        <v>10000</v>
+      </c>
+      <c r="G1685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="str">
+        <v>V-1775365675459-x8xsv</v>
+      </c>
+      <c r="B1686" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1686" t="str">
+        <v>12:07 a. m.</v>
+      </c>
+      <c r="D1686" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1686" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1686">
+        <v>6000</v>
+      </c>
+      <c r="G1686">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="str">
+        <v>V-1775366478910-4cno0</v>
+      </c>
+      <c r="B1687" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1687" t="str">
+        <v>12:21 a. m.</v>
+      </c>
+      <c r="D1687" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1687" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1687">
+        <v>10000</v>
+      </c>
+      <c r="G1687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="str">
+        <v>V-1775367458815-rtmlr</v>
+      </c>
+      <c r="B1688" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1688" t="str">
+        <v>12:37 a. m.</v>
+      </c>
+      <c r="D1688" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1688" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F1688">
+        <v>20000</v>
+      </c>
+      <c r="G1688">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="str">
+        <v>V-1775367717526-yrvkn</v>
+      </c>
+      <c r="B1689" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1689" t="str">
+        <v>12:41 a. m.</v>
+      </c>
+      <c r="D1689" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1689" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1689">
+        <v>78000</v>
+      </c>
+      <c r="G1689">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="str">
+        <v>V-1775367760506-i3q4b</v>
+      </c>
+      <c r="B1690" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1690" t="str">
+        <v>12:42 a. m.</v>
+      </c>
+      <c r="D1690" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1690" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1690">
+        <v>10000</v>
+      </c>
+      <c r="G1690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="str">
+        <v>V-1775367913453-g0tdj</v>
+      </c>
+      <c r="B1691" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1691" t="str">
+        <v>12:45 a. m.</v>
+      </c>
+      <c r="D1691" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="E1691" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F1691">
+        <v>78000</v>
+      </c>
+      <c r="G1691">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="str">
+        <v>V-1775367952852-ewmjv</v>
+      </c>
+      <c r="B1692" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1692" t="str">
+        <v>12:45 a. m.</v>
+      </c>
+      <c r="D1692" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1692" t="str">
+        <v>Ron Tradicional Media (x1)</v>
+      </c>
+      <c r="F1692">
+        <v>68000</v>
+      </c>
+      <c r="G1692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="str">
+        <v>V-1775368068822-d12j0</v>
+      </c>
+      <c r="B1693" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1693" t="str">
+        <v>12:47 a. m.</v>
+      </c>
+      <c r="D1693" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1693" t="str">
+        <v>Ron Tradicional Botella (x1)</v>
+      </c>
+      <c r="F1693">
+        <v>104000</v>
+      </c>
+      <c r="G1693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="str">
+        <v>V-1775368393220-2lgm5</v>
+      </c>
+      <c r="B1694" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1694" t="str">
+        <v>12:53 a. m.</v>
+      </c>
+      <c r="D1694" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1694" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F1694">
+        <v>110000</v>
+      </c>
+      <c r="G1694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="str">
+        <v>V-1775368864849-myfrg</v>
+      </c>
+      <c r="B1695" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1695" t="str">
+        <v>01:01 a. m.</v>
+      </c>
+      <c r="D1695" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1695" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1695">
+        <v>6000</v>
+      </c>
+      <c r="G1695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="str">
+        <v>V-1775369221360-stgw8</v>
+      </c>
+      <c r="B1696" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1696" t="str">
+        <v>01:07 a. m.</v>
+      </c>
+      <c r="D1696" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1696" t="str">
+        <v>Aguardiente Ligth Caja (x1), Soda (x1)</v>
+      </c>
+      <c r="F1696">
+        <v>115000</v>
+      </c>
+      <c r="G1696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="str">
+        <v>V-1775369240610-wq56f</v>
+      </c>
+      <c r="B1697" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1697" t="str">
+        <v>01:07 a. m.</v>
+      </c>
+      <c r="D1697" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1697" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1697">
+        <v>10000</v>
+      </c>
+      <c r="G1697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="str">
+        <v>V-1775369276528-fcplb</v>
+      </c>
+      <c r="B1698" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1698" t="str">
+        <v>01:07 a. m.</v>
+      </c>
+      <c r="D1698" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1698" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F1698">
+        <v>100000</v>
+      </c>
+      <c r="G1698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="str">
+        <v>V-1775370017159-5akrf</v>
+      </c>
+      <c r="B1699" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1699" t="str">
+        <v>01:20 a. m.</v>
+      </c>
+      <c r="D1699" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1699" t="str">
+        <v>Descorche (x1)</v>
+      </c>
+      <c r="F1699">
+        <v>0</v>
+      </c>
+      <c r="G1699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="str">
+        <v>V-1775370442018-9ixs3</v>
+      </c>
+      <c r="B1700" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1700" t="str">
+        <v>01:27 a. m.</v>
+      </c>
+      <c r="D1700" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E1700" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F1700">
+        <v>10000</v>
+      </c>
+      <c r="G1700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="str">
+        <v>V-1775370606473-qxu8d</v>
+      </c>
+      <c r="B1701" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1701" t="str">
+        <v>01:30 a. m.</v>
+      </c>
+      <c r="D1701" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E1701" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F1701">
+        <v>5000</v>
+      </c>
+      <c r="G1701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="str">
+        <v>V-1775371123707-va440</v>
+      </c>
+      <c r="B1702" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1702" t="str">
+        <v>01:38 a. m.</v>
+      </c>
+      <c r="D1702" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1702" t="str">
+        <v>Aguardiente Cristal Cuarto (x1)</v>
+      </c>
+      <c r="F1702">
+        <v>36000</v>
+      </c>
+      <c r="G1702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="str">
+        <v>V-1775371763142-p7b8y</v>
+      </c>
+      <c r="B1703" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1703" t="str">
+        <v>01:49 a. m.</v>
+      </c>
+      <c r="D1703" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1703" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1703">
+        <v>10000</v>
+      </c>
+      <c r="G1703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="str">
+        <v>V-1775372676965-6nk2u</v>
+      </c>
+      <c r="B1704" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1704" t="str">
+        <v>02:04 a. m.</v>
+      </c>
+      <c r="D1704" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="E1704" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F1704">
+        <v>10000</v>
+      </c>
+      <c r="G1704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="str">
+        <v>V-1775372997794-3f9y2</v>
+      </c>
+      <c r="B1705" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1705" t="str">
+        <v>02:09 a. m.</v>
+      </c>
+      <c r="D1705" t="str">
+        <v>Dianis</v>
+      </c>
+      <c r="E1705" t="str">
+        <v>Aguardiente Cristal Cuarto (x1)</v>
+      </c>
+      <c r="F1705">
+        <v>36000</v>
+      </c>
+      <c r="G1705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="str">
+        <v>V-1775373017381-f64kg</v>
+      </c>
+      <c r="B1706" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1706" t="str">
+        <v>02:10 a. m.</v>
+      </c>
+      <c r="D1706" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1706" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1706">
+        <v>6000</v>
+      </c>
+      <c r="G1706">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="str">
+        <v>V-1775373082541-g08s3</v>
+      </c>
+      <c r="B1707" t="str">
+        <v>5/4/2026</v>
+      </c>
+      <c r="C1707" t="str">
+        <v>02:11 a. m.</v>
+      </c>
+      <c r="D1707" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E1707" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F1707">
+        <v>6000</v>
+      </c>
+      <c r="G1707">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1350"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1707"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2192"/>
+  <dimension ref="A1:G2259"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -50815,9 +50815,1550 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2193">
+      <c r="A2193" t="str">
+        <v>V-1777061445209-4ochr</v>
+      </c>
+      <c r="B2193" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2193" t="str">
+        <v>03:10 p. m.</v>
+      </c>
+      <c r="D2193" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2193" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2193">
+        <v>5000</v>
+      </c>
+      <c r="G2193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="str">
+        <v>V-1777061791959-bz3bj</v>
+      </c>
+      <c r="B2194" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2194" t="str">
+        <v>03:16 p. m.</v>
+      </c>
+      <c r="D2194" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2194" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2194">
+        <v>5000</v>
+      </c>
+      <c r="G2194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="str">
+        <v>V-1777061792288-2hww9</v>
+      </c>
+      <c r="B2195" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2195" t="str">
+        <v>03:16 p. m.</v>
+      </c>
+      <c r="D2195" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2195" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2195">
+        <v>5000</v>
+      </c>
+      <c r="G2195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="str">
+        <v>V-1777063317124-o5med</v>
+      </c>
+      <c r="B2196" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2196" t="str">
+        <v>03:41 p. m.</v>
+      </c>
+      <c r="D2196" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2196" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2196">
+        <v>108000</v>
+      </c>
+      <c r="G2196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="str">
+        <v>V-1777063934289-7nax9</v>
+      </c>
+      <c r="B2197" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2197" t="str">
+        <v>03:52 p. m.</v>
+      </c>
+      <c r="D2197" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2197" t="str">
+        <v>Cerveza Club Colombia (x3)</v>
+      </c>
+      <c r="F2197">
+        <v>30000</v>
+      </c>
+      <c r="G2197">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="str">
+        <v>V-1777065550562-iz6g7</v>
+      </c>
+      <c r="B2198" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2198" t="str">
+        <v>04:19 p. m.</v>
+      </c>
+      <c r="D2198" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2198" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2198">
+        <v>20000</v>
+      </c>
+      <c r="G2198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="str">
+        <v>V-1777065820113-u5db0</v>
+      </c>
+      <c r="B2199" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2199" t="str">
+        <v>04:23 p. m.</v>
+      </c>
+      <c r="D2199" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2199" t="str">
+        <v>Cerveza Poker (x2), Soda (x1)</v>
+      </c>
+      <c r="F2199">
+        <v>21000</v>
+      </c>
+      <c r="G2199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="str">
+        <v>V-1777065954915-70rqo</v>
+      </c>
+      <c r="B2200" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2200" t="str">
+        <v>04:25 p. m.</v>
+      </c>
+      <c r="D2200" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2200" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2200">
+        <v>8000</v>
+      </c>
+      <c r="G2200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="str">
+        <v>V-1777066690296-gfagz</v>
+      </c>
+      <c r="B2201" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2201" t="str">
+        <v>04:38 p. m.</v>
+      </c>
+      <c r="D2201" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2201" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2201">
+        <v>8000</v>
+      </c>
+      <c r="G2201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="str">
+        <v>V-1777066994335-9lvrd</v>
+      </c>
+      <c r="B2202" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2202" t="str">
+        <v>04:43 p. m.</v>
+      </c>
+      <c r="D2202" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2202" t="str">
+        <v>Coca Cola (x1), Agua Botella Grande (x1), Ron 8 años Media (x1)</v>
+      </c>
+      <c r="F2202">
+        <v>98000</v>
+      </c>
+      <c r="G2202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="str">
+        <v>V-1777067515663-75n1q</v>
+      </c>
+      <c r="B2203" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2203" t="str">
+        <v>04:51 p. m.</v>
+      </c>
+      <c r="D2203" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2203" t="str">
+        <v>Ron 5 años Media (x1), Coca Cola (x1)</v>
+      </c>
+      <c r="F2203">
+        <v>83000</v>
+      </c>
+      <c r="G2203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="str">
+        <v>V-1777067874189-rqufb</v>
+      </c>
+      <c r="B2204" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2204" t="str">
+        <v>04:57 p. m.</v>
+      </c>
+      <c r="D2204" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2204" t="str">
+        <v>Cerveza Club Colombia (x3), Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F2204">
+        <v>29000</v>
+      </c>
+      <c r="G2204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="str">
+        <v>V-1777068114399-a50ni</v>
+      </c>
+      <c r="B2205" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2205" t="str">
+        <v>05:01 p. m.</v>
+      </c>
+      <c r="D2205" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2205" t="str">
+        <v>Cerveza Poker (x3), Soda (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2205">
+        <v>37000</v>
+      </c>
+      <c r="G2205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="str">
+        <v>V-1777068407070-fe219</v>
+      </c>
+      <c r="B2206" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2206" t="str">
+        <v>05:06 p. m.</v>
+      </c>
+      <c r="D2206" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2206" t="str">
+        <v>Aguardiente Cristal Caja (x2)</v>
+      </c>
+      <c r="F2206">
+        <v>200000</v>
+      </c>
+      <c r="G2206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="str">
+        <v>V-1777068627434-zswfq</v>
+      </c>
+      <c r="B2207" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2207" t="str">
+        <v>05:10 p. m.</v>
+      </c>
+      <c r="D2207" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2207" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2207">
+        <v>100000</v>
+      </c>
+      <c r="G2207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="str">
+        <v>V-1777068905948-cmyow</v>
+      </c>
+      <c r="B2208" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2208" t="str">
+        <v>05:15 p. m.</v>
+      </c>
+      <c r="D2208" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2208" t="str">
+        <v>Agua Botella Grande (x1), Soda (x1)</v>
+      </c>
+      <c r="F2208">
+        <v>10000</v>
+      </c>
+      <c r="G2208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="str">
+        <v>V-1777068907420-tdht8</v>
+      </c>
+      <c r="B2209" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2209" t="str">
+        <v>05:15 p. m.</v>
+      </c>
+      <c r="D2209" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2209" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2209">
+        <v>122000</v>
+      </c>
+      <c r="G2209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="str">
+        <v>V-1777068965396-va18m</v>
+      </c>
+      <c r="B2210" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2210" t="str">
+        <v>05:16 p. m.</v>
+      </c>
+      <c r="D2210" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2210" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2210">
+        <v>122000</v>
+      </c>
+      <c r="G2210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="str">
+        <v>V-1777068979526-uyji3</v>
+      </c>
+      <c r="B2211" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2211" t="str">
+        <v>05:16 p. m.</v>
+      </c>
+      <c r="D2211" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2211" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F2211">
+        <v>70000</v>
+      </c>
+      <c r="G2211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="str">
+        <v>V-1777069415120-z071e</v>
+      </c>
+      <c r="B2212" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2212" t="str">
+        <v>05:23 p. m.</v>
+      </c>
+      <c r="D2212" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2212" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2212">
+        <v>122000</v>
+      </c>
+      <c r="G2212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="str">
+        <v>V-1777069449021-6x5y0</v>
+      </c>
+      <c r="B2213" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2213" t="str">
+        <v>05:24 p. m.</v>
+      </c>
+      <c r="D2213" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2213" t="str">
+        <v>Cerveza Corona (x1)</v>
+      </c>
+      <c r="F2213">
+        <v>12000</v>
+      </c>
+      <c r="G2213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="str">
+        <v>V-1777069486378-wln4q</v>
+      </c>
+      <c r="B2214" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2214" t="str">
+        <v>05:24 p. m.</v>
+      </c>
+      <c r="D2214" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2214" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2214">
+        <v>8000</v>
+      </c>
+      <c r="G2214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="str">
+        <v>V-1777069810748-oiqox</v>
+      </c>
+      <c r="B2215" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2215" t="str">
+        <v>05:30 p. m.</v>
+      </c>
+      <c r="D2215" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2215" t="str">
+        <v>Soda (x2)</v>
+      </c>
+      <c r="F2215">
+        <v>10000</v>
+      </c>
+      <c r="G2215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="str">
+        <v>V-1777070036143-ew1ai</v>
+      </c>
+      <c r="B2216" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2216" t="str">
+        <v>05:33 p. m.</v>
+      </c>
+      <c r="D2216" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2216" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2216">
+        <v>8000</v>
+      </c>
+      <c r="G2216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="str">
+        <v>V-1777070143216-v1csm</v>
+      </c>
+      <c r="B2217" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2217" t="str">
+        <v>05:35 p. m.</v>
+      </c>
+      <c r="D2217" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2217" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2217">
+        <v>5000</v>
+      </c>
+      <c r="G2217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="str">
+        <v>V-1777070277152-5hve8</v>
+      </c>
+      <c r="B2218" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2218" t="str">
+        <v>05:37 p. m.</v>
+      </c>
+      <c r="D2218" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2218" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2218">
+        <v>5000</v>
+      </c>
+      <c r="G2218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="str">
+        <v>V-1777070418086-6lknf</v>
+      </c>
+      <c r="B2219" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2219" t="str">
+        <v>05:40 p. m.</v>
+      </c>
+      <c r="D2219" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2219" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2219">
+        <v>16000</v>
+      </c>
+      <c r="G2219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="str">
+        <v>V-1777070586849-j9a7w</v>
+      </c>
+      <c r="B2220" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2220" t="str">
+        <v>05:43 p. m.</v>
+      </c>
+      <c r="D2220" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2220" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2220">
+        <v>8000</v>
+      </c>
+      <c r="G2220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="str">
+        <v>V-1777070839457-gvjlf</v>
+      </c>
+      <c r="B2221" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2221" t="str">
+        <v>05:47 p. m.</v>
+      </c>
+      <c r="D2221" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2221" t="str">
+        <v>Cerveza Poker (x1), Soda (x1)</v>
+      </c>
+      <c r="F2221">
+        <v>13000</v>
+      </c>
+      <c r="G2221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="str">
+        <v>V-1777071032205-xme39</v>
+      </c>
+      <c r="B2222" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2222" t="str">
+        <v>05:50 p. m.</v>
+      </c>
+      <c r="D2222" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2222" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2222">
+        <v>5000</v>
+      </c>
+      <c r="G2222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="str">
+        <v>V-1777071175711-7j8wc</v>
+      </c>
+      <c r="B2223" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2223" t="str">
+        <v>05:52 p. m.</v>
+      </c>
+      <c r="D2223" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2223" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2223">
+        <v>5000</v>
+      </c>
+      <c r="G2223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="str">
+        <v>V-1777071419774-knews</v>
+      </c>
+      <c r="B2224" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2224" t="str">
+        <v>05:56 p. m.</v>
+      </c>
+      <c r="D2224" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2224" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2224">
+        <v>5000</v>
+      </c>
+      <c r="G2224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="str">
+        <v>V-1777071547930-1v5yp</v>
+      </c>
+      <c r="B2225" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2225" t="str">
+        <v>05:59 p. m.</v>
+      </c>
+      <c r="D2225" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2225" t="str">
+        <v>Gatorade (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2225">
+        <v>14000</v>
+      </c>
+      <c r="G2225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="str">
+        <v>V-1777071779577-q1z5b</v>
+      </c>
+      <c r="B2226" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2226" t="str">
+        <v>06:02 p. m.</v>
+      </c>
+      <c r="D2226" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2226" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2226">
+        <v>16000</v>
+      </c>
+      <c r="G2226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="str">
+        <v>V-1777072143944-rsxar</v>
+      </c>
+      <c r="B2227" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2227" t="str">
+        <v>06:09 p. m.</v>
+      </c>
+      <c r="D2227" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2227" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2227">
+        <v>56000</v>
+      </c>
+      <c r="G2227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="str">
+        <v>V-1777072455139-zuynm</v>
+      </c>
+      <c r="B2228" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2228" t="str">
+        <v>06:14 p. m.</v>
+      </c>
+      <c r="D2228" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2228" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2228">
+        <v>8000</v>
+      </c>
+      <c r="G2228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="str">
+        <v>V-1777072533064-9b5up</v>
+      </c>
+      <c r="B2229" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2229" t="str">
+        <v>06:15 p. m.</v>
+      </c>
+      <c r="D2229" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2229" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2229">
+        <v>8000</v>
+      </c>
+      <c r="G2229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="str">
+        <v>V-1777073068499-flk13</v>
+      </c>
+      <c r="B2230" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2230" t="str">
+        <v>06:24 p. m.</v>
+      </c>
+      <c r="D2230" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2230" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2230">
+        <v>8000</v>
+      </c>
+      <c r="G2230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="str">
+        <v>V-1777073127514-y86jy</v>
+      </c>
+      <c r="B2231" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2231" t="str">
+        <v>06:25 p. m.</v>
+      </c>
+      <c r="D2231" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2231" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2231">
+        <v>8000</v>
+      </c>
+      <c r="G2231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="str">
+        <v>V-1777073301913-0efr0</v>
+      </c>
+      <c r="B2232" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2232" t="str">
+        <v>06:28 p. m.</v>
+      </c>
+      <c r="D2232" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2232" t="str">
+        <v>Cerveza Aguila Ligth (x2), Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2232">
+        <v>94000</v>
+      </c>
+      <c r="G2232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="str">
+        <v>V-1777073689606-haiw2</v>
+      </c>
+      <c r="B2233" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2233" t="str">
+        <v>06:34 p. m.</v>
+      </c>
+      <c r="D2233" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2233" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2233">
+        <v>16000</v>
+      </c>
+      <c r="G2233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="str">
+        <v>V-1777073846006-ohb8z</v>
+      </c>
+      <c r="B2234" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2234" t="str">
+        <v>06:37 p. m.</v>
+      </c>
+      <c r="D2234" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2234" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2234">
+        <v>16000</v>
+      </c>
+      <c r="G2234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="str">
+        <v>V-1777074002824-zampn</v>
+      </c>
+      <c r="B2235" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2235" t="str">
+        <v>06:40 p. m.</v>
+      </c>
+      <c r="D2235" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2235" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2235">
+        <v>5000</v>
+      </c>
+      <c r="G2235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="str">
+        <v>V-1777074105095-dal56</v>
+      </c>
+      <c r="B2236" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2236" t="str">
+        <v>06:41 p. m.</v>
+      </c>
+      <c r="D2236" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2236" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2236">
+        <v>8000</v>
+      </c>
+      <c r="G2236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="str">
+        <v>V-1777074337753-r7nob</v>
+      </c>
+      <c r="B2237" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2237" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2237" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2237" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2237">
+        <v>8000</v>
+      </c>
+      <c r="G2237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="str">
+        <v>V-1777074453295-qr4n9</v>
+      </c>
+      <c r="B2238" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2238" t="str">
+        <v>06:47 p. m.</v>
+      </c>
+      <c r="D2238" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2238" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2238">
+        <v>16000</v>
+      </c>
+      <c r="G2238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="str">
+        <v>V-1777074594376-axso9</v>
+      </c>
+      <c r="B2239" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2239" t="str">
+        <v>06:49 p. m.</v>
+      </c>
+      <c r="D2239" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2239" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2239">
+        <v>5000</v>
+      </c>
+      <c r="G2239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="str">
+        <v>V-1777074773207-thmb1</v>
+      </c>
+      <c r="B2240" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2240" t="str">
+        <v>06:52 p. m.</v>
+      </c>
+      <c r="D2240" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2240" t="str">
+        <v>Soda (x1), Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2240">
+        <v>13000</v>
+      </c>
+      <c r="G2240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="str">
+        <v>V-1777074954429-vt942</v>
+      </c>
+      <c r="B2241" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2241" t="str">
+        <v>06:55 p. m.</v>
+      </c>
+      <c r="D2241" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2241" t="str">
+        <v>Cerveza Poker (x2), Soda (x1)</v>
+      </c>
+      <c r="F2241">
+        <v>21000</v>
+      </c>
+      <c r="G2241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="str">
+        <v>V-1777075518680-7xldv</v>
+      </c>
+      <c r="B2242" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2242" t="str">
+        <v>07:05 p. m.</v>
+      </c>
+      <c r="D2242" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2242" t="str">
+        <v>Cerveza Club Colombia (x3)</v>
+      </c>
+      <c r="F2242">
+        <v>24000</v>
+      </c>
+      <c r="G2242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="str">
+        <v>V-1777075730261-kuneg</v>
+      </c>
+      <c r="B2243" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2243" t="str">
+        <v>07:08 p. m.</v>
+      </c>
+      <c r="D2243" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2243" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F2243">
+        <v>6000</v>
+      </c>
+      <c r="G2243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="str">
+        <v>V-1777076967998-qteh9</v>
+      </c>
+      <c r="B2244" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2244" t="str">
+        <v>07:29 p. m.</v>
+      </c>
+      <c r="D2244" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2244" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2244">
+        <v>8000</v>
+      </c>
+      <c r="G2244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="str">
+        <v>V-1777077553410-3bz4l</v>
+      </c>
+      <c r="B2245" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2245" t="str">
+        <v>07:39 p. m.</v>
+      </c>
+      <c r="D2245" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2245" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2245">
+        <v>16000</v>
+      </c>
+      <c r="G2245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="str">
+        <v>V-1777078158511-oyvre</v>
+      </c>
+      <c r="B2246" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2246" t="str">
+        <v>07:49 p. m.</v>
+      </c>
+      <c r="D2246" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2246" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2246">
+        <v>24000</v>
+      </c>
+      <c r="G2246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="str">
+        <v>V-1777078334067-5p1ma</v>
+      </c>
+      <c r="B2247" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2247" t="str">
+        <v>07:52 p. m.</v>
+      </c>
+      <c r="D2247" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2247" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2247">
+        <v>16000</v>
+      </c>
+      <c r="G2247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="str">
+        <v>V-1777079809525-omu1c</v>
+      </c>
+      <c r="B2248" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2248" t="str">
+        <v>08:16 p. m.</v>
+      </c>
+      <c r="D2248" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2248" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2248">
+        <v>8000</v>
+      </c>
+      <c r="G2248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="str">
+        <v>V-1777079931167-72vyp</v>
+      </c>
+      <c r="B2249" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2249" t="str">
+        <v>08:18 p. m.</v>
+      </c>
+      <c r="D2249" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2249" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2249">
+        <v>16000</v>
+      </c>
+      <c r="G2249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="str">
+        <v>V-1777080118183-w9uum</v>
+      </c>
+      <c r="B2250" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2250" t="str">
+        <v>08:21 p. m.</v>
+      </c>
+      <c r="D2250" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2250" t="str">
+        <v>Cerveza Poker (x2), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2250">
+        <v>24000</v>
+      </c>
+      <c r="G2250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="str">
+        <v>V-1777080328047-ed7tv</v>
+      </c>
+      <c r="B2251" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2251" t="str">
+        <v>08:25 p. m.</v>
+      </c>
+      <c r="D2251" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2251" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2251">
+        <v>8000</v>
+      </c>
+      <c r="G2251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="str">
+        <v>V-1777080375975-2biwy</v>
+      </c>
+      <c r="B2252" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2252" t="str">
+        <v>08:26 p. m.</v>
+      </c>
+      <c r="D2252" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2252" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F2252">
+        <v>5000</v>
+      </c>
+      <c r="G2252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="str">
+        <v>V-1777080748035-u58gp</v>
+      </c>
+      <c r="B2253" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2253" t="str">
+        <v>08:32 p. m.</v>
+      </c>
+      <c r="D2253" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2253" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2253">
+        <v>8000</v>
+      </c>
+      <c r="G2253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="str">
+        <v>V-1777082178877-7t7qo</v>
+      </c>
+      <c r="B2254" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2254" t="str">
+        <v>08:56 p. m.</v>
+      </c>
+      <c r="D2254" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2254" t="str">
+        <v>Cerveza Club Colombia (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2254">
+        <v>16000</v>
+      </c>
+      <c r="G2254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="str">
+        <v>V-1777082486294-xtb2n</v>
+      </c>
+      <c r="B2255" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2255" t="str">
+        <v>09:01 p. m.</v>
+      </c>
+      <c r="D2255" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2255" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2255">
+        <v>108000</v>
+      </c>
+      <c r="G2255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="str">
+        <v>V-1777082736750-27dse</v>
+      </c>
+      <c r="B2256" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2256" t="str">
+        <v>09:05 p. m.</v>
+      </c>
+      <c r="D2256" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2256" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2256">
+        <v>8000</v>
+      </c>
+      <c r="G2256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="str">
+        <v>V-1777082994713-ebm61</v>
+      </c>
+      <c r="B2257" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2257" t="str">
+        <v>09:09 p. m.</v>
+      </c>
+      <c r="D2257" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2257" t="str">
+        <v>Cerveza Aguila Ligth (x1), Ron 5 años Media (x1), Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2257">
+        <v>142000</v>
+      </c>
+      <c r="G2257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="str">
+        <v>V-1777083020236-zqf03</v>
+      </c>
+      <c r="B2258" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2258" t="str">
+        <v>09:10 p. m.</v>
+      </c>
+      <c r="D2258" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2258" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2258">
+        <v>16000</v>
+      </c>
+      <c r="G2258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="str">
+        <v>V-1777083406786-rme14</v>
+      </c>
+      <c r="B2259" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2259" t="str">
+        <v>09:16 p. m.</v>
+      </c>
+      <c r="D2259" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2259" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2259">
+        <v>5000</v>
+      </c>
+      <c r="G2259">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2259"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2259"/>
+  <dimension ref="A1:G2426"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -52356,9 +52356,3850 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2260">
+      <c r="A2260" t="str">
+        <v>V-1777091231492-33x4a</v>
+      </c>
+      <c r="B2260" t="str">
+        <v>24/4/2026</v>
+      </c>
+      <c r="C2260" t="str">
+        <v>11:27 p. m.</v>
+      </c>
+      <c r="D2260" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2260" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2260">
+        <v>122000</v>
+      </c>
+      <c r="G2260">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="str">
+        <v>V-1777163719044-i7kl7</v>
+      </c>
+      <c r="B2261" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2261" t="str">
+        <v>07:35 p. m.</v>
+      </c>
+      <c r="D2261" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2261" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2261">
+        <v>10000</v>
+      </c>
+      <c r="G2261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="str">
+        <v>V-1777164037906-2bs29</v>
+      </c>
+      <c r="B2262" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2262" t="str">
+        <v>07:40 p. m.</v>
+      </c>
+      <c r="D2262" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2262" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2262">
+        <v>78000</v>
+      </c>
+      <c r="G2262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="str">
+        <v>V-1777164468866-fzf3y</v>
+      </c>
+      <c r="B2263" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2263" t="str">
+        <v>07:47 p. m.</v>
+      </c>
+      <c r="D2263" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2263" t="str">
+        <v>Ron Tradicional Media (x1), Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2263">
+        <v>156000</v>
+      </c>
+      <c r="G2263">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="str">
+        <v>V-1777164744575-pgxz4</v>
+      </c>
+      <c r="B2264" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2264" t="str">
+        <v>07:52 p. m.</v>
+      </c>
+      <c r="D2264" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2264" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2264">
+        <v>10000</v>
+      </c>
+      <c r="G2264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="str">
+        <v>V-1777164857136-nmm52</v>
+      </c>
+      <c r="B2265" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2265" t="str">
+        <v>07:54 p. m.</v>
+      </c>
+      <c r="D2265" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2265" t="str">
+        <v>Aguardiente Ligth Media (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2265">
+        <v>66000</v>
+      </c>
+      <c r="G2265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="str">
+        <v>V-1777164861996-a1jtg</v>
+      </c>
+      <c r="B2266" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2266" t="str">
+        <v>07:54 p. m.</v>
+      </c>
+      <c r="D2266" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2266" t="str">
+        <v>Ron Tradicional Caja (x1)</v>
+      </c>
+      <c r="F2266">
+        <v>110000</v>
+      </c>
+      <c r="G2266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="str">
+        <v>V-1777165011122-c7una</v>
+      </c>
+      <c r="B2267" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2267" t="str">
+        <v>07:56 p. m.</v>
+      </c>
+      <c r="D2267" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2267" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2267">
+        <v>100000</v>
+      </c>
+      <c r="G2267">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="str">
+        <v>V-1777165172968-ijrvx</v>
+      </c>
+      <c r="B2268" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2268" t="str">
+        <v>07:59 p. m.</v>
+      </c>
+      <c r="D2268" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2268" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F2268">
+        <v>70000</v>
+      </c>
+      <c r="G2268">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="str">
+        <v>V-1777165347809-3hud8</v>
+      </c>
+      <c r="B2269" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2269" t="str">
+        <v>08:02 p. m.</v>
+      </c>
+      <c r="D2269" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2269" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2269">
+        <v>78000</v>
+      </c>
+      <c r="G2269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="str">
+        <v>V-1777165370462-vbuaj</v>
+      </c>
+      <c r="B2270" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2270" t="str">
+        <v>08:02 p. m.</v>
+      </c>
+      <c r="D2270" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2270" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2270">
+        <v>20000</v>
+      </c>
+      <c r="G2270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="str">
+        <v>V-1777165721735-ge90m</v>
+      </c>
+      <c r="B2271" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2271" t="str">
+        <v>08:08 p. m.</v>
+      </c>
+      <c r="D2271" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2271" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2271">
+        <v>100000</v>
+      </c>
+      <c r="G2271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="str">
+        <v>V-1777166023207-91z3m</v>
+      </c>
+      <c r="B2272" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2272" t="str">
+        <v>08:13 p. m.</v>
+      </c>
+      <c r="D2272" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2272" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2272">
+        <v>100000</v>
+      </c>
+      <c r="G2272">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="str">
+        <v>V-1777166096417-lnh9x</v>
+      </c>
+      <c r="B2273" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2273" t="str">
+        <v>08:14 p. m.</v>
+      </c>
+      <c r="D2273" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2273" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2273">
+        <v>20000</v>
+      </c>
+      <c r="G2273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="str">
+        <v>V-1777166100817-ewgkm</v>
+      </c>
+      <c r="B2274" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2274" t="str">
+        <v>08:15 p. m.</v>
+      </c>
+      <c r="D2274" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2274" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2274">
+        <v>100000</v>
+      </c>
+      <c r="G2274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="str">
+        <v>V-1777166123917-uxj17</v>
+      </c>
+      <c r="B2275" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2275" t="str">
+        <v>08:15 p. m.</v>
+      </c>
+      <c r="D2275" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2275" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2275">
+        <v>108000</v>
+      </c>
+      <c r="G2275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="str">
+        <v>V-1777166158568-128m1</v>
+      </c>
+      <c r="B2276" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2276" t="str">
+        <v>08:15 p. m.</v>
+      </c>
+      <c r="D2276" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2276" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2276">
+        <v>20000</v>
+      </c>
+      <c r="G2276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="str">
+        <v>V-1777166217469-e20o1</v>
+      </c>
+      <c r="B2277" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2277" t="str">
+        <v>08:16 p. m.</v>
+      </c>
+      <c r="D2277" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2277" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2277">
+        <v>5000</v>
+      </c>
+      <c r="G2277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="str">
+        <v>V-1777166250010-8pac6</v>
+      </c>
+      <c r="B2278" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2278" t="str">
+        <v>08:17 p. m.</v>
+      </c>
+      <c r="D2278" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2278" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2278">
+        <v>56000</v>
+      </c>
+      <c r="G2278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="str">
+        <v>V-1777166267550-ae13e</v>
+      </c>
+      <c r="B2279" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2279" t="str">
+        <v>08:17 p. m.</v>
+      </c>
+      <c r="D2279" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2279" t="str">
+        <v>Ginger Canada Dry (x1)</v>
+      </c>
+      <c r="F2279">
+        <v>5000</v>
+      </c>
+      <c r="G2279">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="str">
+        <v>V-1777166289075-i1cry</v>
+      </c>
+      <c r="B2280" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2280" t="str">
+        <v>08:18 p. m.</v>
+      </c>
+      <c r="D2280" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2280" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2280">
+        <v>122000</v>
+      </c>
+      <c r="G2280">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="str">
+        <v>V-1777166369069-6e5xw</v>
+      </c>
+      <c r="B2281" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2281" t="str">
+        <v>08:19 p. m.</v>
+      </c>
+      <c r="D2281" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2281" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2281">
+        <v>54000</v>
+      </c>
+      <c r="G2281">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="str">
+        <v>V-1777166372452-jh1na</v>
+      </c>
+      <c r="B2282" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2282" t="str">
+        <v>08:19 p. m.</v>
+      </c>
+      <c r="D2282" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2282" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2282">
+        <v>108000</v>
+      </c>
+      <c r="G2282">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="str">
+        <v>V-1777166646881-9vzyq</v>
+      </c>
+      <c r="B2283" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2283" t="str">
+        <v>08:24 p. m.</v>
+      </c>
+      <c r="D2283" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2283" t="str">
+        <v>Aguardiente Ligth Caja (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2283">
+        <v>120000</v>
+      </c>
+      <c r="G2283">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="str">
+        <v>V-1777166747065-vn0mb</v>
+      </c>
+      <c r="B2284" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2284" t="str">
+        <v>08:25 p. m.</v>
+      </c>
+      <c r="D2284" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2284" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F2284">
+        <v>114000</v>
+      </c>
+      <c r="G2284">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="str">
+        <v>V-1777166787431-1guep</v>
+      </c>
+      <c r="B2285" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2285" t="str">
+        <v>08:26 p. m.</v>
+      </c>
+      <c r="D2285" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2285" t="str">
+        <v>Aguardiente Amarillo Botella (x1), Aguardiente Ligth Media (x1), Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2285">
+        <v>218000</v>
+      </c>
+      <c r="G2285">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="str">
+        <v>V-1777166934223-kzf93</v>
+      </c>
+      <c r="B2286" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2286" t="str">
+        <v>08:28 p. m.</v>
+      </c>
+      <c r="D2286" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2286" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2286">
+        <v>78000</v>
+      </c>
+      <c r="G2286">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="str">
+        <v>V-1777166997235-8n95j</v>
+      </c>
+      <c r="B2287" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2287" t="str">
+        <v>08:29 p. m.</v>
+      </c>
+      <c r="D2287" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2287" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2287">
+        <v>122000</v>
+      </c>
+      <c r="G2287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="str">
+        <v>V-1777167026034-gd3z1</v>
+      </c>
+      <c r="B2288" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2288" t="str">
+        <v>08:30 p. m.</v>
+      </c>
+      <c r="D2288" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2288" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2288">
+        <v>20000</v>
+      </c>
+      <c r="G2288">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="str">
+        <v>V-1777167053474-vngno</v>
+      </c>
+      <c r="B2289" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2289" t="str">
+        <v>08:30 p. m.</v>
+      </c>
+      <c r="D2289" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2289" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2289">
+        <v>54000</v>
+      </c>
+      <c r="G2289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="str">
+        <v>V-1777167054861-kxskv</v>
+      </c>
+      <c r="B2290" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2290" t="str">
+        <v>08:30 p. m.</v>
+      </c>
+      <c r="D2290" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2290" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2290">
+        <v>54000</v>
+      </c>
+      <c r="G2290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="str">
+        <v>V-1777167179073-xrv9i</v>
+      </c>
+      <c r="B2291" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2291" t="str">
+        <v>08:32 p. m.</v>
+      </c>
+      <c r="D2291" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2291" t="str">
+        <v>Ron Tradicional Media (x1), Coca Cola (x1)</v>
+      </c>
+      <c r="F2291">
+        <v>73000</v>
+      </c>
+      <c r="G2291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="str">
+        <v>V-1777167298999-i7ow4</v>
+      </c>
+      <c r="B2292" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2292" t="str">
+        <v>08:34 p. m.</v>
+      </c>
+      <c r="D2292" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2292" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2292">
+        <v>110000</v>
+      </c>
+      <c r="G2292">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="str">
+        <v>V-1777167434032-qv2am</v>
+      </c>
+      <c r="B2293" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2293" t="str">
+        <v>08:37 p. m.</v>
+      </c>
+      <c r="D2293" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2293" t="str">
+        <v>Cerveza Aguila Ligth (x3), Cerveza Club Colombia (x1), Gatorade (x1)</v>
+      </c>
+      <c r="F2293">
+        <v>46000</v>
+      </c>
+      <c r="G2293">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="str">
+        <v>V-1777167492495-h73ho</v>
+      </c>
+      <c r="B2294" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2294" t="str">
+        <v>08:38 p. m.</v>
+      </c>
+      <c r="D2294" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2294" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2294">
+        <v>10000</v>
+      </c>
+      <c r="G2294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="str">
+        <v>V-1777167504150-hugpf</v>
+      </c>
+      <c r="B2295" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2295" t="str">
+        <v>08:38 p. m.</v>
+      </c>
+      <c r="D2295" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2295" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2295">
+        <v>10000</v>
+      </c>
+      <c r="G2295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="str">
+        <v>V-1777167608525-kru3q</v>
+      </c>
+      <c r="B2296" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2296" t="str">
+        <v>08:40 p. m.</v>
+      </c>
+      <c r="D2296" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2296" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2296">
+        <v>88000</v>
+      </c>
+      <c r="G2296">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="str">
+        <v>V-1777167701283-e4rff</v>
+      </c>
+      <c r="B2297" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2297" t="str">
+        <v>08:41 p. m.</v>
+      </c>
+      <c r="D2297" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2297" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2297">
+        <v>110000</v>
+      </c>
+      <c r="G2297">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="str">
+        <v>V-1777167724823-670t2</v>
+      </c>
+      <c r="B2298" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2298" t="str">
+        <v>08:42 p. m.</v>
+      </c>
+      <c r="D2298" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2298" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2298">
+        <v>100000</v>
+      </c>
+      <c r="G2298">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="str">
+        <v>V-1777168258010-fk7gl</v>
+      </c>
+      <c r="B2299" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2299" t="str">
+        <v>08:50 p. m.</v>
+      </c>
+      <c r="D2299" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2299" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F2299">
+        <v>86000</v>
+      </c>
+      <c r="G2299">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="str">
+        <v>V-1777168306462-hkn2b</v>
+      </c>
+      <c r="B2300" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2300" t="str">
+        <v>08:51 p. m.</v>
+      </c>
+      <c r="D2300" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2300" t="str">
+        <v>Aguardiente Cristal Caja (x1), Electrolit (x1), Soda (x1)</v>
+      </c>
+      <c r="F2300">
+        <v>115000</v>
+      </c>
+      <c r="G2300">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="str">
+        <v>V-1777168438807-r41gb</v>
+      </c>
+      <c r="B2301" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2301" t="str">
+        <v>08:53 p. m.</v>
+      </c>
+      <c r="D2301" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2301" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2301">
+        <v>100000</v>
+      </c>
+      <c r="G2301">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="str">
+        <v>V-1777168527684-86pq3</v>
+      </c>
+      <c r="B2302" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2302" t="str">
+        <v>08:55 p. m.</v>
+      </c>
+      <c r="D2302" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2302" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2302">
+        <v>10000</v>
+      </c>
+      <c r="G2302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="str">
+        <v>V-1777168903435-b3pmt</v>
+      </c>
+      <c r="B2303" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2303" t="str">
+        <v>09:01 p. m.</v>
+      </c>
+      <c r="D2303" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2303" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2303">
+        <v>10000</v>
+      </c>
+      <c r="G2303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="str">
+        <v>V-1777169006021-oa9g4</v>
+      </c>
+      <c r="B2304" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2304" t="str">
+        <v>09:03 p. m.</v>
+      </c>
+      <c r="D2304" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2304" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2304">
+        <v>78000</v>
+      </c>
+      <c r="G2304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="str">
+        <v>V-1777169133448-m4bfm</v>
+      </c>
+      <c r="B2305" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2305" t="str">
+        <v>09:05 p. m.</v>
+      </c>
+      <c r="D2305" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2305" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2305">
+        <v>100000</v>
+      </c>
+      <c r="G2305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="str">
+        <v>V-1777169385307-z2mm5</v>
+      </c>
+      <c r="B2306" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2306" t="str">
+        <v>09:09 p. m.</v>
+      </c>
+      <c r="D2306" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2306" t="str">
+        <v>Cerveza Poker (x1), Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2306">
+        <v>20000</v>
+      </c>
+      <c r="G2306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="str">
+        <v>V-1777169420513-dxmz1</v>
+      </c>
+      <c r="B2307" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2307" t="str">
+        <v>09:10 p. m.</v>
+      </c>
+      <c r="D2307" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2307" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F2307">
+        <v>132000</v>
+      </c>
+      <c r="G2307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="str">
+        <v>V-1777169470255-hm4kq</v>
+      </c>
+      <c r="B2308" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2308" t="str">
+        <v>09:11 p. m.</v>
+      </c>
+      <c r="D2308" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2308" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2308">
+        <v>10000</v>
+      </c>
+      <c r="G2308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="str">
+        <v>V-1777169599652-sjfue</v>
+      </c>
+      <c r="B2309" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2309" t="str">
+        <v>09:13 p. m.</v>
+      </c>
+      <c r="D2309" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2309" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2309">
+        <v>54000</v>
+      </c>
+      <c r="G2309">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="str">
+        <v>V-1777169734396-exm5t</v>
+      </c>
+      <c r="B2310" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2310" t="str">
+        <v>09:15 p. m.</v>
+      </c>
+      <c r="D2310" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2310" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2310">
+        <v>110000</v>
+      </c>
+      <c r="G2310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="str">
+        <v>V-1777169891002-5os43</v>
+      </c>
+      <c r="B2311" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2311" t="str">
+        <v>09:18 p. m.</v>
+      </c>
+      <c r="D2311" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2311" t="str">
+        <v>Aguardiente Ligth Caja (x1), Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2311">
+        <v>210000</v>
+      </c>
+      <c r="G2311">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="str">
+        <v>V-1777169962798-jc9gu</v>
+      </c>
+      <c r="B2312" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2312" t="str">
+        <v>09:19 p. m.</v>
+      </c>
+      <c r="D2312" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2312" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2312">
+        <v>88000</v>
+      </c>
+      <c r="G2312">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="str">
+        <v>V-1777170150337-g5opz</v>
+      </c>
+      <c r="B2313" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2313" t="str">
+        <v>09:22 p. m.</v>
+      </c>
+      <c r="D2313" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2313" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F2313">
+        <v>70000</v>
+      </c>
+      <c r="G2313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="str">
+        <v>V-1777170184063-sckxi</v>
+      </c>
+      <c r="B2314" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2314" t="str">
+        <v>09:23 p. m.</v>
+      </c>
+      <c r="D2314" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2314" t="str">
+        <v>Aguardiente Ligth Media (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2314">
+        <v>66000</v>
+      </c>
+      <c r="G2314">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="str">
+        <v>V-1777170237283-xjnwo</v>
+      </c>
+      <c r="B2315" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2315" t="str">
+        <v>09:23 p. m.</v>
+      </c>
+      <c r="D2315" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2315" t="str">
+        <v>Cerveza Poker (x1), Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F2315">
+        <v>15000</v>
+      </c>
+      <c r="G2315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="str">
+        <v>V-1777170365763-9a8cs</v>
+      </c>
+      <c r="B2316" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2316" t="str">
+        <v>09:26 p. m.</v>
+      </c>
+      <c r="D2316" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2316" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2316">
+        <v>56000</v>
+      </c>
+      <c r="G2316">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="str">
+        <v>V-1777170424094-9ib2r</v>
+      </c>
+      <c r="B2317" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2317" t="str">
+        <v>09:27 p. m.</v>
+      </c>
+      <c r="D2317" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2317" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2317">
+        <v>10000</v>
+      </c>
+      <c r="G2317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="str">
+        <v>V-1777170571644-cdokx</v>
+      </c>
+      <c r="B2318" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2318" t="str">
+        <v>09:29 p. m.</v>
+      </c>
+      <c r="D2318" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2318" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2318">
+        <v>122000</v>
+      </c>
+      <c r="G2318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="str">
+        <v>V-1777170587479-pxnpz</v>
+      </c>
+      <c r="B2319" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2319" t="str">
+        <v>09:29 p. m.</v>
+      </c>
+      <c r="D2319" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2319" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F2319">
+        <v>132000</v>
+      </c>
+      <c r="G2319">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="str">
+        <v>V-1777170589460-jwucq</v>
+      </c>
+      <c r="B2320" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2320" t="str">
+        <v>09:29 p. m.</v>
+      </c>
+      <c r="D2320" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2320" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2320">
+        <v>56000</v>
+      </c>
+      <c r="G2320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="str">
+        <v>V-1777170676223-svwd5</v>
+      </c>
+      <c r="B2321" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2321" t="str">
+        <v>09:31 p. m.</v>
+      </c>
+      <c r="D2321" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2321" t="str">
+        <v>Cerveza Poker (x1), Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2321">
+        <v>30000</v>
+      </c>
+      <c r="G2321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="str">
+        <v>V-1777170857872-77iob</v>
+      </c>
+      <c r="B2322" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2322" t="str">
+        <v>09:34 p. m.</v>
+      </c>
+      <c r="D2322" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2322" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2322">
+        <v>54000</v>
+      </c>
+      <c r="G2322">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="str">
+        <v>V-1777171048033-ojdmg</v>
+      </c>
+      <c r="B2323" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2323" t="str">
+        <v>09:37 p. m.</v>
+      </c>
+      <c r="D2323" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2323" t="str">
+        <v>Ron 5 años Media (x1), Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2323">
+        <v>88000</v>
+      </c>
+      <c r="G2323">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="str">
+        <v>V-1777171123468-m8c36</v>
+      </c>
+      <c r="B2324" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2324" t="str">
+        <v>09:38 p. m.</v>
+      </c>
+      <c r="D2324" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2324" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2324">
+        <v>20000</v>
+      </c>
+      <c r="G2324">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="str">
+        <v>V-1777171370065-ahl05</v>
+      </c>
+      <c r="B2325" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2325" t="str">
+        <v>09:42 p. m.</v>
+      </c>
+      <c r="D2325" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2325" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2325">
+        <v>54000</v>
+      </c>
+      <c r="G2325">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="str">
+        <v>V-1777171428256-vg3ty</v>
+      </c>
+      <c r="B2326" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2326" t="str">
+        <v>09:43 p. m.</v>
+      </c>
+      <c r="D2326" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2326" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2326">
+        <v>78000</v>
+      </c>
+      <c r="G2326">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="str">
+        <v>V-1777171440914-kv2x6</v>
+      </c>
+      <c r="B2327" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2327" t="str">
+        <v>09:44 p. m.</v>
+      </c>
+      <c r="D2327" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2327" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2327">
+        <v>10000</v>
+      </c>
+      <c r="G2327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="str">
+        <v>V-1777171451522-1u0g2</v>
+      </c>
+      <c r="B2328" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2328" t="str">
+        <v>09:44 p. m.</v>
+      </c>
+      <c r="D2328" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2328" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2328">
+        <v>5000</v>
+      </c>
+      <c r="G2328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="str">
+        <v>V-1777171520651-17jir</v>
+      </c>
+      <c r="B2329" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2329" t="str">
+        <v>09:45 p. m.</v>
+      </c>
+      <c r="D2329" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2329" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2329">
+        <v>88000</v>
+      </c>
+      <c r="G2329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="str">
+        <v>V-1777171703520-g8lif</v>
+      </c>
+      <c r="B2330" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2330" t="str">
+        <v>09:48 p. m.</v>
+      </c>
+      <c r="D2330" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2330" t="str">
+        <v>Cerveza Aguila Ligth (x3), Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2330">
+        <v>152000</v>
+      </c>
+      <c r="G2330">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="str">
+        <v>V-1777171747895-p84j3</v>
+      </c>
+      <c r="B2331" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2331" t="str">
+        <v>09:49 p. m.</v>
+      </c>
+      <c r="D2331" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2331" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2331">
+        <v>10000</v>
+      </c>
+      <c r="G2331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="str">
+        <v>V-1777171752450-bh65u</v>
+      </c>
+      <c r="B2332" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2332" t="str">
+        <v>09:49 p. m.</v>
+      </c>
+      <c r="D2332" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2332" t="str">
+        <v>Aguardiente Cristal Cuarto (x1)</v>
+      </c>
+      <c r="F2332">
+        <v>36000</v>
+      </c>
+      <c r="G2332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="str">
+        <v>V-1777171859627-fuhyw</v>
+      </c>
+      <c r="B2333" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2333" t="str">
+        <v>09:51 p. m.</v>
+      </c>
+      <c r="D2333" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2333" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2333">
+        <v>56000</v>
+      </c>
+      <c r="G2333">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="str">
+        <v>V-1777171885293-6j0tu</v>
+      </c>
+      <c r="B2334" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2334" t="str">
+        <v>09:51 p. m.</v>
+      </c>
+      <c r="D2334" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2334" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2334">
+        <v>78000</v>
+      </c>
+      <c r="G2334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="str">
+        <v>V-1777171938362-t4tnb</v>
+      </c>
+      <c r="B2335" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2335" t="str">
+        <v>09:52 p. m.</v>
+      </c>
+      <c r="D2335" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2335" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2335">
+        <v>5000</v>
+      </c>
+      <c r="G2335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="str">
+        <v>V-1777171995362-p36f2</v>
+      </c>
+      <c r="B2336" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2336" t="str">
+        <v>09:53 p. m.</v>
+      </c>
+      <c r="D2336" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2336" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F2336">
+        <v>6000</v>
+      </c>
+      <c r="G2336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="str">
+        <v>V-1777171999592-5xzvh</v>
+      </c>
+      <c r="B2337" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2337" t="str">
+        <v>09:53 p. m.</v>
+      </c>
+      <c r="D2337" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2337" t="str">
+        <v>Aguardiente Cristal Caja (x1), Soda (x1)</v>
+      </c>
+      <c r="F2337">
+        <v>105000</v>
+      </c>
+      <c r="G2337">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="str">
+        <v>V-1777172077790-z0ar3</v>
+      </c>
+      <c r="B2338" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2338" t="str">
+        <v>09:54 p. m.</v>
+      </c>
+      <c r="D2338" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2338" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2338">
+        <v>5000</v>
+      </c>
+      <c r="G2338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="str">
+        <v>V-1777172225841-lly7g</v>
+      </c>
+      <c r="B2339" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2339" t="str">
+        <v>09:57 p. m.</v>
+      </c>
+      <c r="D2339" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2339" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F2339">
+        <v>70000</v>
+      </c>
+      <c r="G2339">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="str">
+        <v>V-1777172249976-uzxp9</v>
+      </c>
+      <c r="B2340" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2340" t="str">
+        <v>09:57 p. m.</v>
+      </c>
+      <c r="D2340" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2340" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2340">
+        <v>10000</v>
+      </c>
+      <c r="G2340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="str">
+        <v>V-1777172288504-gwu8z</v>
+      </c>
+      <c r="B2341" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2341" t="str">
+        <v>09:58 p. m.</v>
+      </c>
+      <c r="D2341" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2341" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F2341">
+        <v>132000</v>
+      </c>
+      <c r="G2341">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="str">
+        <v>V-1777172288246-fqj6z</v>
+      </c>
+      <c r="B2342" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2342" t="str">
+        <v>09:58 p. m.</v>
+      </c>
+      <c r="D2342" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2342" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2342">
+        <v>10000</v>
+      </c>
+      <c r="G2342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="str">
+        <v>V-1777172313302-npt94</v>
+      </c>
+      <c r="B2343" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2343" t="str">
+        <v>09:58 p. m.</v>
+      </c>
+      <c r="D2343" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2343" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F2343">
+        <v>70000</v>
+      </c>
+      <c r="G2343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="str">
+        <v>V-1777172334451-99fee</v>
+      </c>
+      <c r="B2344" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2344" t="str">
+        <v>09:58 p. m.</v>
+      </c>
+      <c r="D2344" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2344" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2344">
+        <v>78000</v>
+      </c>
+      <c r="G2344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="str">
+        <v>V-1777172339902-ncf36</v>
+      </c>
+      <c r="B2345" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2345" t="str">
+        <v>09:58 p. m.</v>
+      </c>
+      <c r="D2345" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2345" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F2345">
+        <v>132000</v>
+      </c>
+      <c r="G2345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="str">
+        <v>V-1777172345314-g023e</v>
+      </c>
+      <c r="B2346" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2346" t="str">
+        <v>09:59 p. m.</v>
+      </c>
+      <c r="D2346" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2346" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2346">
+        <v>108000</v>
+      </c>
+      <c r="G2346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="str">
+        <v>V-1777172391690-ku1m2</v>
+      </c>
+      <c r="B2347" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2347" t="str">
+        <v>09:59 p. m.</v>
+      </c>
+      <c r="D2347" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2347" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2347">
+        <v>10000</v>
+      </c>
+      <c r="G2347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="str">
+        <v>V-1777172439352-779rc</v>
+      </c>
+      <c r="B2348" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2348" t="str">
+        <v>10:00 p. m.</v>
+      </c>
+      <c r="D2348" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2348" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2348">
+        <v>10000</v>
+      </c>
+      <c r="G2348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="str">
+        <v>V-1777172606941-x6x93</v>
+      </c>
+      <c r="B2349" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2349" t="str">
+        <v>10:03 p. m.</v>
+      </c>
+      <c r="D2349" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2349" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2349">
+        <v>78000</v>
+      </c>
+      <c r="G2349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="str">
+        <v>V-1777172662860-31kfc</v>
+      </c>
+      <c r="B2350" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2350" t="str">
+        <v>10:04 p. m.</v>
+      </c>
+      <c r="D2350" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2350" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2350">
+        <v>100000</v>
+      </c>
+      <c r="G2350">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="str">
+        <v>V-1777172792587-bun50</v>
+      </c>
+      <c r="B2351" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2351" t="str">
+        <v>10:06 p. m.</v>
+      </c>
+      <c r="D2351" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2351" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2351">
+        <v>10000</v>
+      </c>
+      <c r="G2351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="str">
+        <v>V-1777172917065-stzz5</v>
+      </c>
+      <c r="B2352" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2352" t="str">
+        <v>10:08 p. m.</v>
+      </c>
+      <c r="D2352" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2352" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2352">
+        <v>56000</v>
+      </c>
+      <c r="G2352">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="str">
+        <v>V-1777172977693-r3pke</v>
+      </c>
+      <c r="B2353" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2353" t="str">
+        <v>10:09 p. m.</v>
+      </c>
+      <c r="D2353" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2353" t="str">
+        <v>Ginger Canada Dry (x1)</v>
+      </c>
+      <c r="F2353">
+        <v>5000</v>
+      </c>
+      <c r="G2353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="str">
+        <v>V-1777173005596-onulr</v>
+      </c>
+      <c r="B2354" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2354" t="str">
+        <v>10:10 p. m.</v>
+      </c>
+      <c r="D2354" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2354" t="str">
+        <v>Gatorade (x1)</v>
+      </c>
+      <c r="F2354">
+        <v>6000</v>
+      </c>
+      <c r="G2354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="str">
+        <v>V-1777173167206-74bos</v>
+      </c>
+      <c r="B2355" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2355" t="str">
+        <v>10:12 p. m.</v>
+      </c>
+      <c r="D2355" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2355" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2355">
+        <v>110000</v>
+      </c>
+      <c r="G2355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="str">
+        <v>V-1777173270567-9le1r</v>
+      </c>
+      <c r="B2356" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2356" t="str">
+        <v>10:14 p. m.</v>
+      </c>
+      <c r="D2356" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2356" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2356">
+        <v>108000</v>
+      </c>
+      <c r="G2356">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="str">
+        <v>V-1777173356359-dza2b</v>
+      </c>
+      <c r="B2357" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2357" t="str">
+        <v>10:15 p. m.</v>
+      </c>
+      <c r="D2357" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2357" t="str">
+        <v>Aguardiente Ligth Botella (x1), Soda (x1)</v>
+      </c>
+      <c r="F2357">
+        <v>93000</v>
+      </c>
+      <c r="G2357">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="str">
+        <v>V-1777173765516-41x86</v>
+      </c>
+      <c r="B2358" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2358" t="str">
+        <v>10:22 p. m.</v>
+      </c>
+      <c r="D2358" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2358" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2358">
+        <v>54000</v>
+      </c>
+      <c r="G2358">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="str">
+        <v>V-1777173997913-oammw</v>
+      </c>
+      <c r="B2359" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2359" t="str">
+        <v>10:26 p. m.</v>
+      </c>
+      <c r="D2359" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2359" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2359">
+        <v>56000</v>
+      </c>
+      <c r="G2359">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="str">
+        <v>V-1777174152831-wb80o</v>
+      </c>
+      <c r="B2360" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2360" t="str">
+        <v>10:29 p. m.</v>
+      </c>
+      <c r="D2360" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2360" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2360">
+        <v>10000</v>
+      </c>
+      <c r="G2360">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="str">
+        <v>V-1777174185129-n7l7v</v>
+      </c>
+      <c r="B2361" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2361" t="str">
+        <v>10:29 p. m.</v>
+      </c>
+      <c r="D2361" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2361" t="str">
+        <v>Cerveza Poker (x4)</v>
+      </c>
+      <c r="F2361">
+        <v>40000</v>
+      </c>
+      <c r="G2361">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="str">
+        <v>V-1777174257199-y28vn</v>
+      </c>
+      <c r="B2362" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2362" t="str">
+        <v>10:30 p. m.</v>
+      </c>
+      <c r="D2362" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2362" t="str">
+        <v>Cerveza Club Colombia Lata (x1)</v>
+      </c>
+      <c r="F2362">
+        <v>12000</v>
+      </c>
+      <c r="G2362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="str">
+        <v>V-1777174610256-uqtfc</v>
+      </c>
+      <c r="B2363" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2363" t="str">
+        <v>10:36 p. m.</v>
+      </c>
+      <c r="D2363" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2363" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2363">
+        <v>56000</v>
+      </c>
+      <c r="G2363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="str">
+        <v>V-1777174609722-pskpi</v>
+      </c>
+      <c r="B2364" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2364" t="str">
+        <v>10:36 p. m.</v>
+      </c>
+      <c r="D2364" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2364" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2364">
+        <v>78000</v>
+      </c>
+      <c r="G2364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="str">
+        <v>V-1777174776682-06hmq</v>
+      </c>
+      <c r="B2365" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2365" t="str">
+        <v>10:39 p. m.</v>
+      </c>
+      <c r="D2365" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2365" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2365">
+        <v>10000</v>
+      </c>
+      <c r="G2365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="str">
+        <v>V-1777174870982-dsjdw</v>
+      </c>
+      <c r="B2366" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2366" t="str">
+        <v>10:41 p. m.</v>
+      </c>
+      <c r="D2366" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2366" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2366">
+        <v>10000</v>
+      </c>
+      <c r="G2366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="str">
+        <v>V-1777175227723-l91d0</v>
+      </c>
+      <c r="B2367" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2367" t="str">
+        <v>10:47 p. m.</v>
+      </c>
+      <c r="D2367" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2367" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2367">
+        <v>10000</v>
+      </c>
+      <c r="G2367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="str">
+        <v>V-1777175531762-kr6il</v>
+      </c>
+      <c r="B2368" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2368" t="str">
+        <v>10:52 p. m.</v>
+      </c>
+      <c r="D2368" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2368" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2368">
+        <v>10000</v>
+      </c>
+      <c r="G2368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="str">
+        <v>V-1777175648621-y2i8d</v>
+      </c>
+      <c r="B2369" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2369" t="str">
+        <v>10:54 p. m.</v>
+      </c>
+      <c r="D2369" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2369" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2369">
+        <v>78000</v>
+      </c>
+      <c r="G2369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="str">
+        <v>V-1777175730857-2wjf2</v>
+      </c>
+      <c r="B2370" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2370" t="str">
+        <v>10:55 p. m.</v>
+      </c>
+      <c r="D2370" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2370" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2370">
+        <v>20000</v>
+      </c>
+      <c r="G2370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="str">
+        <v>V-1777175897456-amd7a</v>
+      </c>
+      <c r="B2371" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2371" t="str">
+        <v>10:58 p. m.</v>
+      </c>
+      <c r="D2371" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2371" t="str">
+        <v>Ron Tradicional Botella (x1), Coca Cola (x2)</v>
+      </c>
+      <c r="F2371">
+        <v>114000</v>
+      </c>
+      <c r="G2371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="str">
+        <v>V-1777175980974-emo6g</v>
+      </c>
+      <c r="B2372" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2372" t="str">
+        <v>10:59 p. m.</v>
+      </c>
+      <c r="D2372" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2372" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2372">
+        <v>56000</v>
+      </c>
+      <c r="G2372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="str">
+        <v>V-1777176004340-aq0mv</v>
+      </c>
+      <c r="B2373" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2373" t="str">
+        <v>11:00 p. m.</v>
+      </c>
+      <c r="D2373" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2373" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2373">
+        <v>122000</v>
+      </c>
+      <c r="G2373">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="str">
+        <v>V-1777176028173-bdmku</v>
+      </c>
+      <c r="B2374" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2374" t="str">
+        <v>11:00 p. m.</v>
+      </c>
+      <c r="D2374" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2374" t="str">
+        <v>Aguardiente Ligth Media (x1), Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2374">
+        <v>76000</v>
+      </c>
+      <c r="G2374">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="str">
+        <v>V-1777176814534-m7gms</v>
+      </c>
+      <c r="B2375" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2375" t="str">
+        <v>11:13 p. m.</v>
+      </c>
+      <c r="D2375" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2375" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2375">
+        <v>10000</v>
+      </c>
+      <c r="G2375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="str">
+        <v>V-1777176855361-thm7a</v>
+      </c>
+      <c r="B2376" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2376" t="str">
+        <v>11:14 p. m.</v>
+      </c>
+      <c r="D2376" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2376" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2376">
+        <v>100000</v>
+      </c>
+      <c r="G2376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="str">
+        <v>V-1777177000651-bmom5</v>
+      </c>
+      <c r="B2377" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2377" t="str">
+        <v>11:16 p. m.</v>
+      </c>
+      <c r="D2377" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2377" t="str">
+        <v>Ron 5 años Botella (x1)</v>
+      </c>
+      <c r="F2377">
+        <v>132000</v>
+      </c>
+      <c r="G2377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="str">
+        <v>V-1777177140498-iquxb</v>
+      </c>
+      <c r="B2378" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2378" t="str">
+        <v>11:19 p. m.</v>
+      </c>
+      <c r="D2378" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2378" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2378">
+        <v>5000</v>
+      </c>
+      <c r="G2378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="str">
+        <v>V-1777177141361-qeo31</v>
+      </c>
+      <c r="B2379" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2379" t="str">
+        <v>11:19 p. m.</v>
+      </c>
+      <c r="D2379" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2379" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2379">
+        <v>5000</v>
+      </c>
+      <c r="G2379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="str">
+        <v>V-1777177211233-qejc2</v>
+      </c>
+      <c r="B2380" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2380" t="str">
+        <v>11:20 p. m.</v>
+      </c>
+      <c r="D2380" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2380" t="str">
+        <v>Gatorade (x1), Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2380">
+        <v>106000</v>
+      </c>
+      <c r="G2380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="str">
+        <v>V-1777177598657-yyuz9</v>
+      </c>
+      <c r="B2381" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2381" t="str">
+        <v>11:26 p. m.</v>
+      </c>
+      <c r="D2381" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2381" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2381">
+        <v>122000</v>
+      </c>
+      <c r="G2381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="str">
+        <v>V-1777177634634-7y68n</v>
+      </c>
+      <c r="B2382" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2382" t="str">
+        <v>11:27 p. m.</v>
+      </c>
+      <c r="D2382" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2382" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2382">
+        <v>20000</v>
+      </c>
+      <c r="G2382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="str">
+        <v>V-1777177671174-92qyj</v>
+      </c>
+      <c r="B2383" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2383" t="str">
+        <v>11:27 p. m.</v>
+      </c>
+      <c r="D2383" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2383" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2383">
+        <v>10000</v>
+      </c>
+      <c r="G2383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="str">
+        <v>V-1777177855052-nbqle</v>
+      </c>
+      <c r="B2384" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2384" t="str">
+        <v>11:30 p. m.</v>
+      </c>
+      <c r="D2384" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2384" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2384">
+        <v>110000</v>
+      </c>
+      <c r="G2384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="str">
+        <v>V-1777178120269-zcbff</v>
+      </c>
+      <c r="B2385" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2385" t="str">
+        <v>11:35 p. m.</v>
+      </c>
+      <c r="D2385" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2385" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2385">
+        <v>10000</v>
+      </c>
+      <c r="G2385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="str">
+        <v>V-1777178201377-jrpyj</v>
+      </c>
+      <c r="B2386" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2386" t="str">
+        <v>11:36 p. m.</v>
+      </c>
+      <c r="D2386" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2386" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2386">
+        <v>5000</v>
+      </c>
+      <c r="G2386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="str">
+        <v>V-1777178325287-3l4as</v>
+      </c>
+      <c r="B2387" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2387" t="str">
+        <v>11:38 p. m.</v>
+      </c>
+      <c r="D2387" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2387" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2387">
+        <v>10000</v>
+      </c>
+      <c r="G2387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="str">
+        <v>V-1777178409589-9hqon</v>
+      </c>
+      <c r="B2388" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2388" t="str">
+        <v>11:40 p. m.</v>
+      </c>
+      <c r="D2388" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2388" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2388">
+        <v>100000</v>
+      </c>
+      <c r="G2388">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="str">
+        <v>V-1777178547222-2lmjz</v>
+      </c>
+      <c r="B2389" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2389" t="str">
+        <v>11:42 p. m.</v>
+      </c>
+      <c r="D2389" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2389" t="str">
+        <v>Cerveza Club Colombia Lata (x1)</v>
+      </c>
+      <c r="F2389">
+        <v>12000</v>
+      </c>
+      <c r="G2389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="str">
+        <v>V-1777178742811-h4d9w</v>
+      </c>
+      <c r="B2390" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2390" t="str">
+        <v>11:45 p. m.</v>
+      </c>
+      <c r="D2390" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2390" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2390">
+        <v>56000</v>
+      </c>
+      <c r="G2390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="str">
+        <v>V-1777178966680-o7o99</v>
+      </c>
+      <c r="B2391" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2391" t="str">
+        <v>11:49 p. m.</v>
+      </c>
+      <c r="D2391" t="str">
+        <v>Alexander</v>
+      </c>
+      <c r="E2391" t="str">
+        <v>Aguardiente Amarillo Botella (x1)</v>
+      </c>
+      <c r="F2391">
+        <v>108000</v>
+      </c>
+      <c r="G2391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="str">
+        <v>V-1777179471029-62ao6</v>
+      </c>
+      <c r="B2392" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2392" t="str">
+        <v>11:57 p. m.</v>
+      </c>
+      <c r="D2392" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2392" t="str">
+        <v>Soda (x1), Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2392">
+        <v>15000</v>
+      </c>
+      <c r="G2392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="str">
+        <v>V-1777179511184-t8swl</v>
+      </c>
+      <c r="B2393" t="str">
+        <v>25/4/2026</v>
+      </c>
+      <c r="C2393" t="str">
+        <v>11:58 p. m.</v>
+      </c>
+      <c r="D2393" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2393" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2393">
+        <v>20000</v>
+      </c>
+      <c r="G2393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="str">
+        <v>V-1777180128651-yo7af</v>
+      </c>
+      <c r="B2394" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2394" t="str">
+        <v>12:08 a. m.</v>
+      </c>
+      <c r="D2394" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2394" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2394">
+        <v>10000</v>
+      </c>
+      <c r="G2394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="str">
+        <v>V-1777180271748-dr8fd</v>
+      </c>
+      <c r="B2395" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2395" t="str">
+        <v>12:11 a. m.</v>
+      </c>
+      <c r="D2395" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2395" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2395">
+        <v>10000</v>
+      </c>
+      <c r="G2395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="str">
+        <v>V-1777180351512-49kqy</v>
+      </c>
+      <c r="B2396" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2396" t="str">
+        <v>12:12 a. m.</v>
+      </c>
+      <c r="D2396" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2396" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2396">
+        <v>20000</v>
+      </c>
+      <c r="G2396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="str">
+        <v>V-1777180638293-5uo05</v>
+      </c>
+      <c r="B2397" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2397" t="str">
+        <v>12:17 a. m.</v>
+      </c>
+      <c r="D2397" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2397" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2397">
+        <v>20000</v>
+      </c>
+      <c r="G2397">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="str">
+        <v>V-1777180698103-c5iyj</v>
+      </c>
+      <c r="B2398" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2398" t="str">
+        <v>12:18 a. m.</v>
+      </c>
+      <c r="D2398" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2398" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2398">
+        <v>10000</v>
+      </c>
+      <c r="G2398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="str">
+        <v>V-1777180751425-gwl6d</v>
+      </c>
+      <c r="B2399" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2399" t="str">
+        <v>12:19 a. m.</v>
+      </c>
+      <c r="D2399" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2399" t="str">
+        <v>Aguardiente Cristal Botella (x1)</v>
+      </c>
+      <c r="F2399">
+        <v>86000</v>
+      </c>
+      <c r="G2399">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="str">
+        <v>V-1777180815812-ua7f3</v>
+      </c>
+      <c r="B2400" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2400" t="str">
+        <v>12:20 a. m.</v>
+      </c>
+      <c r="D2400" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2400" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2400">
+        <v>10000</v>
+      </c>
+      <c r="G2400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="str">
+        <v>V-1777181002890-at3oi</v>
+      </c>
+      <c r="B2401" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2401" t="str">
+        <v>12:23 a. m.</v>
+      </c>
+      <c r="D2401" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2401" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2401">
+        <v>10000</v>
+      </c>
+      <c r="G2401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="str">
+        <v>V-1777181110259-mfnjf</v>
+      </c>
+      <c r="B2402" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2402" t="str">
+        <v>12:25 a. m.</v>
+      </c>
+      <c r="D2402" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2402" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2402">
+        <v>10000</v>
+      </c>
+      <c r="G2402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="str">
+        <v>V-1777181178850-8i998</v>
+      </c>
+      <c r="B2403" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2403" t="str">
+        <v>12:26 a. m.</v>
+      </c>
+      <c r="D2403" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2403" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2403">
+        <v>110000</v>
+      </c>
+      <c r="G2403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="str">
+        <v>V-1777181271576-xpcb0</v>
+      </c>
+      <c r="B2404" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2404" t="str">
+        <v>12:27 a. m.</v>
+      </c>
+      <c r="D2404" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2404" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2404">
+        <v>78000</v>
+      </c>
+      <c r="G2404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="str">
+        <v>V-1777181319875-11n8w</v>
+      </c>
+      <c r="B2405" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2405" t="str">
+        <v>12:28 a. m.</v>
+      </c>
+      <c r="D2405" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2405" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2405">
+        <v>20000</v>
+      </c>
+      <c r="G2405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="str">
+        <v>V-1777181407896-14dl4</v>
+      </c>
+      <c r="B2406" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2406" t="str">
+        <v>12:30 a. m.</v>
+      </c>
+      <c r="D2406" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2406" t="str">
+        <v>Aguardiente Cristal Caja (x1)</v>
+      </c>
+      <c r="F2406">
+        <v>100000</v>
+      </c>
+      <c r="G2406">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="str">
+        <v>V-1777181853534-9cl3t</v>
+      </c>
+      <c r="B2407" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2407" t="str">
+        <v>12:37 a. m.</v>
+      </c>
+      <c r="D2407" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2407" t="str">
+        <v>Ron Tradicional Caja (x1)</v>
+      </c>
+      <c r="F2407">
+        <v>110000</v>
+      </c>
+      <c r="G2407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="str">
+        <v>V-1777181904176-ni0yj</v>
+      </c>
+      <c r="B2408" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2408" t="str">
+        <v>12:38 a. m.</v>
+      </c>
+      <c r="D2408" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2408" t="str">
+        <v>Ron 5 años Media (x1)</v>
+      </c>
+      <c r="F2408">
+        <v>78000</v>
+      </c>
+      <c r="G2408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="str">
+        <v>V-1777182288042-1yq7m</v>
+      </c>
+      <c r="B2409" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2409" t="str">
+        <v>12:44 a. m.</v>
+      </c>
+      <c r="D2409" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2409" t="str">
+        <v>Aguardiente Cristal Caja (x1), Soda (x1)</v>
+      </c>
+      <c r="F2409">
+        <v>105000</v>
+      </c>
+      <c r="G2409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="str">
+        <v>V-1777182289119-qd3h3</v>
+      </c>
+      <c r="B2410" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2410" t="str">
+        <v>12:44 a. m.</v>
+      </c>
+      <c r="D2410" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2410" t="str">
+        <v>Aguardiente Cristal Caja (x1), Soda (x1)</v>
+      </c>
+      <c r="F2410">
+        <v>105000</v>
+      </c>
+      <c r="G2410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="str">
+        <v>V-1777182332065-ls6pz</v>
+      </c>
+      <c r="B2411" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2411" t="str">
+        <v>12:45 a. m.</v>
+      </c>
+      <c r="D2411" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2411" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2411">
+        <v>20000</v>
+      </c>
+      <c r="G2411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="str">
+        <v>V-1777182860874-vzpt5</v>
+      </c>
+      <c r="B2412" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2412" t="str">
+        <v>12:54 a. m.</v>
+      </c>
+      <c r="D2412" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2412" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2412">
+        <v>10000</v>
+      </c>
+      <c r="G2412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="str">
+        <v>V-1777182883209-7nuu1</v>
+      </c>
+      <c r="B2413" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2413" t="str">
+        <v>12:54 a. m.</v>
+      </c>
+      <c r="D2413" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2413" t="str">
+        <v>Gatorade (x1), Bonfiest Bomba (x2)</v>
+      </c>
+      <c r="F2413">
+        <v>12000</v>
+      </c>
+      <c r="G2413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="str">
+        <v>V-1777182976745-a8iyk</v>
+      </c>
+      <c r="B2414" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2414" t="str">
+        <v>12:56 a. m.</v>
+      </c>
+      <c r="D2414" t="str">
+        <v>Juanita</v>
+      </c>
+      <c r="E2414" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2414">
+        <v>56000</v>
+      </c>
+      <c r="G2414">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="str">
+        <v>V-1777183394454-j6m65</v>
+      </c>
+      <c r="B2415" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2415" t="str">
+        <v>01:03 a. m.</v>
+      </c>
+      <c r="D2415" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2415" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F2415">
+        <v>5000</v>
+      </c>
+      <c r="G2415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="str">
+        <v>V-1777183600834-bya93</v>
+      </c>
+      <c r="B2416" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2416" t="str">
+        <v>01:06 a. m.</v>
+      </c>
+      <c r="D2416" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2416" t="str">
+        <v>Aguardiente Ligth Caja (x1)</v>
+      </c>
+      <c r="F2416">
+        <v>110000</v>
+      </c>
+      <c r="G2416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="str">
+        <v>V-1777183981342-1qa9a</v>
+      </c>
+      <c r="B2417" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2417" t="str">
+        <v>01:13 a. m.</v>
+      </c>
+      <c r="D2417" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2417" t="str">
+        <v>Aguardiente Amarillo Media (x1)</v>
+      </c>
+      <c r="F2417">
+        <v>70000</v>
+      </c>
+      <c r="G2417">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="str">
+        <v>V-1777184249044-3dqm1</v>
+      </c>
+      <c r="B2418" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2418" t="str">
+        <v>01:17 a. m.</v>
+      </c>
+      <c r="D2418" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2418" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2418">
+        <v>10000</v>
+      </c>
+      <c r="G2418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="str">
+        <v>V-1777184749589-dl6of</v>
+      </c>
+      <c r="B2419" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2419" t="str">
+        <v>01:25 a. m.</v>
+      </c>
+      <c r="D2419" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2419" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2419">
+        <v>5000</v>
+      </c>
+      <c r="G2419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="str">
+        <v>V-1777185104922-fg0gz</v>
+      </c>
+      <c r="B2420" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2420" t="str">
+        <v>01:31 a. m.</v>
+      </c>
+      <c r="D2420" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2420" t="str">
+        <v>Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2420">
+        <v>88000</v>
+      </c>
+      <c r="G2420">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="str">
+        <v>V-1777185142653-y1z2z</v>
+      </c>
+      <c r="B2421" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2421" t="str">
+        <v>01:32 a. m.</v>
+      </c>
+      <c r="D2421" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2421" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2421">
+        <v>10000</v>
+      </c>
+      <c r="G2421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="str">
+        <v>V-1777185956607-pxgrd</v>
+      </c>
+      <c r="B2422" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2422" t="str">
+        <v>01:45 a. m.</v>
+      </c>
+      <c r="D2422" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2422" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2422">
+        <v>10000</v>
+      </c>
+      <c r="G2422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="str">
+        <v>V-1777185961498-q41lu</v>
+      </c>
+      <c r="B2423" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2423" t="str">
+        <v>01:46 a. m.</v>
+      </c>
+      <c r="D2423" t="str">
+        <v>jhojan</v>
+      </c>
+      <c r="E2423" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2423">
+        <v>10000</v>
+      </c>
+      <c r="G2423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="str">
+        <v>V-1777186425247-quqdh</v>
+      </c>
+      <c r="B2424" t="str">
+        <v>26/4/2026</v>
+      </c>
+      <c r="C2424" t="str">
+        <v>01:53 a. m.</v>
+      </c>
+      <c r="D2424" t="str">
+        <v>Valeria</v>
+      </c>
+      <c r="E2424" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2424">
+        <v>10000</v>
+      </c>
+      <c r="G2424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="str">
+        <v>V-1777342079586-w7i46</v>
+      </c>
+      <c r="B2425" t="str">
+        <v>27/4/2026</v>
+      </c>
+      <c r="C2425" t="str">
+        <v>09:07 p. m.</v>
+      </c>
+      <c r="D2425" t="str">
+        <v>Stiven</v>
+      </c>
+      <c r="E2425" t="str">
+        <v>Ventas Cafeteria (x1)</v>
+      </c>
+      <c r="F2425">
+        <v>0</v>
+      </c>
+      <c r="G2425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="str">
+        <v>V-1777342192726-as6eb</v>
+      </c>
+      <c r="B2426" t="str">
+        <v>27/4/2026</v>
+      </c>
+      <c r="C2426" t="str">
+        <v>09:09 p. m.</v>
+      </c>
+      <c r="D2426" t="str">
+        <v>MarthaC</v>
+      </c>
+      <c r="E2426" t="str">
+        <v>Ventas Cafeteria (x1)</v>
+      </c>
+      <c r="F2426">
+        <v>0</v>
+      </c>
+      <c r="G2426">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2426"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2426"/>
+  <dimension ref="A1:G2517"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -56197,9 +56197,2102 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2427">
+      <c r="A2427" t="str">
+        <v>V-1777520184482-75v59</v>
+      </c>
+      <c r="B2427" t="str">
+        <v>29/4/2026</v>
+      </c>
+      <c r="C2427" t="str">
+        <v>10:36 p. m.</v>
+      </c>
+      <c r="D2427" t="str">
+        <v>MarthaC</v>
+      </c>
+      <c r="E2427" t="str">
+        <v>Ventas Cafeteria (x1)</v>
+      </c>
+      <c r="F2427">
+        <v>0</v>
+      </c>
+      <c r="G2427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="str">
+        <v>V-1777520227601-1vrvb</v>
+      </c>
+      <c r="B2428" t="str">
+        <v>29/4/2026</v>
+      </c>
+      <c r="C2428" t="str">
+        <v>10:37 p. m.</v>
+      </c>
+      <c r="D2428" t="str">
+        <v>MarthaC</v>
+      </c>
+      <c r="E2428" t="str">
+        <v>Ventas Barra (x1)</v>
+      </c>
+      <c r="F2428">
+        <v>0</v>
+      </c>
+      <c r="G2428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="str">
+        <v>V-1777520286362-z5o93</v>
+      </c>
+      <c r="B2429" t="str">
+        <v>29/4/2026</v>
+      </c>
+      <c r="C2429" t="str">
+        <v>10:38 p. m.</v>
+      </c>
+      <c r="D2429" t="str">
+        <v>MarthaC</v>
+      </c>
+      <c r="E2429" t="str">
+        <v>Ventas Cafeteria (x1), Ventas Barra (x1)</v>
+      </c>
+      <c r="F2429">
+        <v>0</v>
+      </c>
+      <c r="G2429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="str">
+        <v>V-1777664260570-h1bfm</v>
+      </c>
+      <c r="B2430" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2430" t="str">
+        <v>02:37 p. m.</v>
+      </c>
+      <c r="D2430" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2430" t="str">
+        <v>Coca Cola (x1)</v>
+      </c>
+      <c r="F2430">
+        <v>5000</v>
+      </c>
+      <c r="G2430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="str">
+        <v>V-1777667274338-1p8b4</v>
+      </c>
+      <c r="B2431" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2431" t="str">
+        <v>03:27 p. m.</v>
+      </c>
+      <c r="D2431" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2431" t="str">
+        <v>Cerveza Poker (x3), Ginger Canada Dry (x2)</v>
+      </c>
+      <c r="F2431">
+        <v>40000</v>
+      </c>
+      <c r="G2431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="str">
+        <v>V-1777667400391-79rsa</v>
+      </c>
+      <c r="B2432" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2432" t="str">
+        <v>03:30 p. m.</v>
+      </c>
+      <c r="D2432" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2432" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2432">
+        <v>10000</v>
+      </c>
+      <c r="G2432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="str">
+        <v>V-1777667401430-f3x9i</v>
+      </c>
+      <c r="B2433" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2433" t="str">
+        <v>03:30 p. m.</v>
+      </c>
+      <c r="D2433" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2433" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2433">
+        <v>10000</v>
+      </c>
+      <c r="G2433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="str">
+        <v>V-1777667497807-x39h5</v>
+      </c>
+      <c r="B2434" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2434" t="str">
+        <v>03:31 p. m.</v>
+      </c>
+      <c r="D2434" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2434" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2434">
+        <v>20000</v>
+      </c>
+      <c r="G2434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="str">
+        <v>V-1777667583098-9zpb7</v>
+      </c>
+      <c r="B2435" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2435" t="str">
+        <v>03:33 p. m.</v>
+      </c>
+      <c r="D2435" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2435" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2435">
+        <v>10000</v>
+      </c>
+      <c r="G2435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="str">
+        <v>V-1777667740540-g3ful</v>
+      </c>
+      <c r="B2436" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2436" t="str">
+        <v>03:35 p. m.</v>
+      </c>
+      <c r="D2436" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2436" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2436">
+        <v>5000</v>
+      </c>
+      <c r="G2436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="str">
+        <v>V-1777668196217-0arbk</v>
+      </c>
+      <c r="B2437" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2437" t="str">
+        <v>03:43 p. m.</v>
+      </c>
+      <c r="D2437" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2437" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2437">
+        <v>10000</v>
+      </c>
+      <c r="G2437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="str">
+        <v>V-1777668523089-ctz1i</v>
+      </c>
+      <c r="B2438" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2438" t="str">
+        <v>03:48 p. m.</v>
+      </c>
+      <c r="D2438" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2438" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2438">
+        <v>16000</v>
+      </c>
+      <c r="G2438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="str">
+        <v>V-1777668886934-gxzc9</v>
+      </c>
+      <c r="B2439" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2439" t="str">
+        <v>03:54 p. m.</v>
+      </c>
+      <c r="D2439" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2439" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2439">
+        <v>16000</v>
+      </c>
+      <c r="G2439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="str">
+        <v>V-1777669296907-bvqpf</v>
+      </c>
+      <c r="B2440" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2440" t="str">
+        <v>04:01 p. m.</v>
+      </c>
+      <c r="D2440" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2440" t="str">
+        <v>Aguardiente Amarillo Media (x1), Ginger Canada Dry (x1)</v>
+      </c>
+      <c r="F2440">
+        <v>75000</v>
+      </c>
+      <c r="G2440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="str">
+        <v>V-1777669333907-oghtu</v>
+      </c>
+      <c r="B2441" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2441" t="str">
+        <v>04:02 p. m.</v>
+      </c>
+      <c r="D2441" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2441" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2441">
+        <v>8000</v>
+      </c>
+      <c r="G2441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="str">
+        <v>V-1777669782991-8444i</v>
+      </c>
+      <c r="B2442" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2442" t="str">
+        <v>04:09 p. m.</v>
+      </c>
+      <c r="D2442" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2442" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2442">
+        <v>16000</v>
+      </c>
+      <c r="G2442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="str">
+        <v>V-1777669940475-myveu</v>
+      </c>
+      <c r="B2443" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2443" t="str">
+        <v>04:12 p. m.</v>
+      </c>
+      <c r="D2443" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2443" t="str">
+        <v>Soda (x1), Ron Tradicional Media (x1)</v>
+      </c>
+      <c r="F2443">
+        <v>73000</v>
+      </c>
+      <c r="G2443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="str">
+        <v>V-1777670223667-umctg</v>
+      </c>
+      <c r="B2444" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2444" t="str">
+        <v>04:17 p. m.</v>
+      </c>
+      <c r="D2444" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2444" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2444">
+        <v>8000</v>
+      </c>
+      <c r="G2444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="str">
+        <v>V-1777670557853-8tslx</v>
+      </c>
+      <c r="B2445" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2445" t="str">
+        <v>04:22 p. m.</v>
+      </c>
+      <c r="D2445" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2445" t="str">
+        <v>Aguardiente Amarillo Media (x1), Cerveza Poker (x1), Soda (x1)</v>
+      </c>
+      <c r="F2445">
+        <v>83000</v>
+      </c>
+      <c r="G2445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="str">
+        <v>V-1777671047980-vojv5</v>
+      </c>
+      <c r="B2446" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2446" t="str">
+        <v>04:30 p. m.</v>
+      </c>
+      <c r="D2446" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2446" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2446">
+        <v>5000</v>
+      </c>
+      <c r="G2446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="str">
+        <v>V-1777671075647-v14lc</v>
+      </c>
+      <c r="B2447" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2447" t="str">
+        <v>04:31 p. m.</v>
+      </c>
+      <c r="D2447" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2447" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2447">
+        <v>16000</v>
+      </c>
+      <c r="G2447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="str">
+        <v>V-1777671176746-d5rll</v>
+      </c>
+      <c r="B2448" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2448" t="str">
+        <v>04:32 p. m.</v>
+      </c>
+      <c r="D2448" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2448" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2448">
+        <v>8000</v>
+      </c>
+      <c r="G2448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="str">
+        <v>V-1777671267254-rfg7c</v>
+      </c>
+      <c r="B2449" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2449" t="str">
+        <v>04:34 p. m.</v>
+      </c>
+      <c r="D2449" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2449" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2449">
+        <v>8000</v>
+      </c>
+      <c r="G2449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="str">
+        <v>V-1777671695190-rr12s</v>
+      </c>
+      <c r="B2450" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2450" t="str">
+        <v>04:41 p. m.</v>
+      </c>
+      <c r="D2450" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2450" t="str">
+        <v>Cerveza Aguila Ligth (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2450">
+        <v>16000</v>
+      </c>
+      <c r="G2450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="str">
+        <v>V-1777672404214-w0avj</v>
+      </c>
+      <c r="B2451" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2451" t="str">
+        <v>04:53 p. m.</v>
+      </c>
+      <c r="D2451" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2451" t="str">
+        <v>Cerveza Club Colombia (x4)</v>
+      </c>
+      <c r="F2451">
+        <v>32000</v>
+      </c>
+      <c r="G2451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="str">
+        <v>V-1777672475206-a1d95</v>
+      </c>
+      <c r="B2452" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2452" t="str">
+        <v>04:54 p. m.</v>
+      </c>
+      <c r="D2452" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2452" t="str">
+        <v>Cerveza Poker (x3)</v>
+      </c>
+      <c r="F2452">
+        <v>24000</v>
+      </c>
+      <c r="G2452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="str">
+        <v>V-1777672528557-tol82</v>
+      </c>
+      <c r="B2453" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2453" t="str">
+        <v>04:55 p. m.</v>
+      </c>
+      <c r="D2453" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2453" t="str">
+        <v>Cerveza Poker (x1), Soda (x1)</v>
+      </c>
+      <c r="F2453">
+        <v>13000</v>
+      </c>
+      <c r="G2453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="str">
+        <v>V-1777672859051-zv7oi</v>
+      </c>
+      <c r="B2454" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2454" t="str">
+        <v>05:00 p. m.</v>
+      </c>
+      <c r="D2454" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2454" t="str">
+        <v>Cerveza Poker (x3)</v>
+      </c>
+      <c r="F2454">
+        <v>24000</v>
+      </c>
+      <c r="G2454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="str">
+        <v>V-1777673844268-hfu18</v>
+      </c>
+      <c r="B2455" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2455" t="str">
+        <v>05:17 p. m.</v>
+      </c>
+      <c r="D2455" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2455" t="str">
+        <v>Cerveza Aguila Ligth (x2), Soda (x4), Ginger Canada Dry (x1), Aguardiente Cristal Media (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2455">
+        <v>103000</v>
+      </c>
+      <c r="G2455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="str">
+        <v>V-1777673845643-z3egn</v>
+      </c>
+      <c r="B2456" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2456" t="str">
+        <v>05:17 p. m.</v>
+      </c>
+      <c r="D2456" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2456" t="str">
+        <v>Cerveza Aguila Ligth (x2), Soda (x4), Ginger Canada Dry (x1), Aguardiente Cristal Media (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2456">
+        <v>103000</v>
+      </c>
+      <c r="G2456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="str">
+        <v>V-1777674134357-7v97w</v>
+      </c>
+      <c r="B2457" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2457" t="str">
+        <v>05:22 p. m.</v>
+      </c>
+      <c r="D2457" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2457" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2457">
+        <v>8000</v>
+      </c>
+      <c r="G2457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="str">
+        <v>V-1777674290696-szl8f</v>
+      </c>
+      <c r="B2458" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2458" t="str">
+        <v>05:24 p. m.</v>
+      </c>
+      <c r="D2458" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2458" t="str">
+        <v>Postobon y Pepsi (x1), Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2458">
+        <v>21000</v>
+      </c>
+      <c r="G2458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="str">
+        <v>V-1777674397487-y8ste</v>
+      </c>
+      <c r="B2459" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2459" t="str">
+        <v>05:26 p. m.</v>
+      </c>
+      <c r="D2459" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2459" t="str">
+        <v>Cerveza Poker (x3)</v>
+      </c>
+      <c r="F2459">
+        <v>24000</v>
+      </c>
+      <c r="G2459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="str">
+        <v>V-1777675123517-yl6mz</v>
+      </c>
+      <c r="B2460" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2460" t="str">
+        <v>05:38 p. m.</v>
+      </c>
+      <c r="D2460" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2460" t="str">
+        <v>Soda (x1), Cerveza Club Colombia (x1), Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2460">
+        <v>101000</v>
+      </c>
+      <c r="G2460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="str">
+        <v>V-1777675124857-jm9pb</v>
+      </c>
+      <c r="B2461" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2461" t="str">
+        <v>05:38 p. m.</v>
+      </c>
+      <c r="D2461" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2461" t="str">
+        <v>Soda (x1), Cerveza Club Colombia (x1), Aguardiente Ligth Botella (x1)</v>
+      </c>
+      <c r="F2461">
+        <v>101000</v>
+      </c>
+      <c r="G2461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="str">
+        <v>V-1777675310671-ifw3y</v>
+      </c>
+      <c r="B2462" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2462" t="str">
+        <v>05:41 p. m.</v>
+      </c>
+      <c r="D2462" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2462" t="str">
+        <v>Aguardiente Amarillo Caja (x1)</v>
+      </c>
+      <c r="F2462">
+        <v>122000</v>
+      </c>
+      <c r="G2462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="str">
+        <v>V-1777675381774-zzljh</v>
+      </c>
+      <c r="B2463" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2463" t="str">
+        <v>05:43 p. m.</v>
+      </c>
+      <c r="D2463" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2463" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2463">
+        <v>8000</v>
+      </c>
+      <c r="G2463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="str">
+        <v>V-1777675489388-3muqq</v>
+      </c>
+      <c r="B2464" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2464" t="str">
+        <v>05:44 p. m.</v>
+      </c>
+      <c r="D2464" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2464" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2464">
+        <v>8000</v>
+      </c>
+      <c r="G2464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="str">
+        <v>V-1777675595197-6zqi4</v>
+      </c>
+      <c r="B2465" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2465" t="str">
+        <v>05:46 p. m.</v>
+      </c>
+      <c r="D2465" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2465" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2465">
+        <v>8000</v>
+      </c>
+      <c r="G2465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="str">
+        <v>V-1777675661648-ff2h0</v>
+      </c>
+      <c r="B2466" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2466" t="str">
+        <v>05:47 p. m.</v>
+      </c>
+      <c r="D2466" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2466" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2466">
+        <v>8000</v>
+      </c>
+      <c r="G2466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="str">
+        <v>V-1777675980980-qhm10</v>
+      </c>
+      <c r="B2467" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2467" t="str">
+        <v>05:53 p. m.</v>
+      </c>
+      <c r="D2467" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2467" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2467">
+        <v>8000</v>
+      </c>
+      <c r="G2467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="str">
+        <v>V-1777676106392-x9aui</v>
+      </c>
+      <c r="B2468" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2468" t="str">
+        <v>05:55 p. m.</v>
+      </c>
+      <c r="D2468" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2468" t="str">
+        <v>Cerveza Poker (x1), Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2468">
+        <v>16000</v>
+      </c>
+      <c r="G2468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="str">
+        <v>V-1777676307334-zin9o</v>
+      </c>
+      <c r="B2469" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2469" t="str">
+        <v>05:58 p. m.</v>
+      </c>
+      <c r="D2469" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2469" t="str">
+        <v>Soda (x1)</v>
+      </c>
+      <c r="F2469">
+        <v>5000</v>
+      </c>
+      <c r="G2469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="str">
+        <v>V-1777676685909-2suie</v>
+      </c>
+      <c r="B2470" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2470" t="str">
+        <v>06:04 p. m.</v>
+      </c>
+      <c r="D2470" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2470" t="str">
+        <v>Cerveza Poker (x4)</v>
+      </c>
+      <c r="F2470">
+        <v>32000</v>
+      </c>
+      <c r="G2470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="str">
+        <v>V-1777676756503-umznu</v>
+      </c>
+      <c r="B2471" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2471" t="str">
+        <v>06:05 p. m.</v>
+      </c>
+      <c r="D2471" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2471" t="str">
+        <v>Aguardiente Cristal Media (x1)</v>
+      </c>
+      <c r="F2471">
+        <v>54000</v>
+      </c>
+      <c r="G2471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="str">
+        <v>V-1777677038742-x9mtk</v>
+      </c>
+      <c r="B2472" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2472" t="str">
+        <v>06:10 p. m.</v>
+      </c>
+      <c r="D2472" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2472" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2472">
+        <v>16000</v>
+      </c>
+      <c r="G2472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="str">
+        <v>V-1777677073579-ohpbj</v>
+      </c>
+      <c r="B2473" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2473" t="str">
+        <v>06:11 p. m.</v>
+      </c>
+      <c r="D2473" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2473" t="str">
+        <v>Postobon y Pepsi (x1)</v>
+      </c>
+      <c r="F2473">
+        <v>5000</v>
+      </c>
+      <c r="G2473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="str">
+        <v>V-1777677251248-epzt1</v>
+      </c>
+      <c r="B2474" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2474" t="str">
+        <v>06:14 p. m.</v>
+      </c>
+      <c r="D2474" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2474" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2474">
+        <v>16000</v>
+      </c>
+      <c r="G2474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="str">
+        <v>V-1777677709192-6qvfh</v>
+      </c>
+      <c r="B2475" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2475" t="str">
+        <v>06:21 p. m.</v>
+      </c>
+      <c r="D2475" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2475" t="str">
+        <v>Aguardiente Ligth Cuarto (x1)</v>
+      </c>
+      <c r="F2475">
+        <v>36000</v>
+      </c>
+      <c r="G2475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="str">
+        <v>V-1777677872021-v468s</v>
+      </c>
+      <c r="B2476" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2476" t="str">
+        <v>06:24 p. m.</v>
+      </c>
+      <c r="D2476" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2476" t="str">
+        <v>Cerveza Poker (x4)</v>
+      </c>
+      <c r="F2476">
+        <v>32000</v>
+      </c>
+      <c r="G2476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="str">
+        <v>V-1777678368412-d5ri7</v>
+      </c>
+      <c r="B2477" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2477" t="str">
+        <v>06:32 p. m.</v>
+      </c>
+      <c r="D2477" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2477" t="str">
+        <v>Aguardiente Ligth Media (x1)</v>
+      </c>
+      <c r="F2477">
+        <v>56000</v>
+      </c>
+      <c r="G2477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="str">
+        <v>V-1777679142199-riro5</v>
+      </c>
+      <c r="B2478" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2478" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2478" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2478" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2478">
+        <v>16000</v>
+      </c>
+      <c r="G2478">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="str">
+        <v>V-1777679148175-jkiej</v>
+      </c>
+      <c r="B2479" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2479" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2479" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2479" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2479">
+        <v>16000</v>
+      </c>
+      <c r="G2479">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="str">
+        <v>V-1777679138738-oy72u</v>
+      </c>
+      <c r="B2480" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2480" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2480" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2480" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2480">
+        <v>16000</v>
+      </c>
+      <c r="G2480">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="str">
+        <v>V-1777679148343-rc0r5</v>
+      </c>
+      <c r="B2481" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2481" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2481" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2481" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2481">
+        <v>16000</v>
+      </c>
+      <c r="G2481">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="str">
+        <v>V-1777679141169-17ont</v>
+      </c>
+      <c r="B2482" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2482" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2482" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2482" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2482">
+        <v>16000</v>
+      </c>
+      <c r="G2482">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="str">
+        <v>V-1777679148804-t4rdy</v>
+      </c>
+      <c r="B2483" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2483" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2483" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2483" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2483">
+        <v>16000</v>
+      </c>
+      <c r="G2483">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="str">
+        <v>V-1777679143665-7cy6w</v>
+      </c>
+      <c r="B2484" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2484" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2484" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2484" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2484">
+        <v>16000</v>
+      </c>
+      <c r="G2484">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="str">
+        <v>V-1777679145658-58wlz</v>
+      </c>
+      <c r="B2485" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2485" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2485" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2485" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2485">
+        <v>16000</v>
+      </c>
+      <c r="G2485">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="str">
+        <v>V-1777679145157-kaui8</v>
+      </c>
+      <c r="B2486" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2486" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2486" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2486" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2486">
+        <v>16000</v>
+      </c>
+      <c r="G2486">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="str">
+        <v>V-1777679145810-rhwit</v>
+      </c>
+      <c r="B2487" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2487" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2487" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2487" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2487">
+        <v>16000</v>
+      </c>
+      <c r="G2487">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="str">
+        <v>V-1777679145963-a7t40</v>
+      </c>
+      <c r="B2488" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2488" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2488" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2488" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2488">
+        <v>16000</v>
+      </c>
+      <c r="G2488">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="str">
+        <v>V-1777679146115-zb3nh</v>
+      </c>
+      <c r="B2489" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2489" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2489" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2489" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2489">
+        <v>16000</v>
+      </c>
+      <c r="G2489">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="str">
+        <v>V-1777679149028-0wn6z</v>
+      </c>
+      <c r="B2490" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2490" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2490" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2490" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2490">
+        <v>16000</v>
+      </c>
+      <c r="G2490">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="str">
+        <v>V-1777679147622-plp38</v>
+      </c>
+      <c r="B2491" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2491" t="str">
+        <v>06:45 p. m.</v>
+      </c>
+      <c r="D2491" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2491" t="str">
+        <v>Cerveza Poker (x2)</v>
+      </c>
+      <c r="F2491">
+        <v>16000</v>
+      </c>
+      <c r="G2491">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="str">
+        <v>V-1777680433625-o1a27</v>
+      </c>
+      <c r="B2492" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2492" t="str">
+        <v>07:07 p. m.</v>
+      </c>
+      <c r="D2492" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2492" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2492">
+        <v>8000</v>
+      </c>
+      <c r="G2492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="str">
+        <v>V-1777680672366-sffl5</v>
+      </c>
+      <c r="B2493" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2493" t="str">
+        <v>07:11 p. m.</v>
+      </c>
+      <c r="D2493" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2493" t="str">
+        <v>Soda (x1), Bonfiest Bomba (x1)</v>
+      </c>
+      <c r="F2493">
+        <v>8000</v>
+      </c>
+      <c r="G2493">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="str">
+        <v>V-1777680857340-h6fzj</v>
+      </c>
+      <c r="B2494" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2494" t="str">
+        <v>07:14 p. m.</v>
+      </c>
+      <c r="D2494" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2494" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2494">
+        <v>16000</v>
+      </c>
+      <c r="G2494">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="str">
+        <v>V-1777680861851-ez053</v>
+      </c>
+      <c r="B2495" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2495" t="str">
+        <v>07:14 p. m.</v>
+      </c>
+      <c r="D2495" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2495" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2495">
+        <v>8000</v>
+      </c>
+      <c r="G2495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="str">
+        <v>V-1777681240475-1rs68</v>
+      </c>
+      <c r="B2496" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2496" t="str">
+        <v>07:20 p. m.</v>
+      </c>
+      <c r="D2496" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2496" t="str">
+        <v>Cerveza Aguila Ligth (x2)</v>
+      </c>
+      <c r="F2496">
+        <v>16000</v>
+      </c>
+      <c r="G2496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="str">
+        <v>V-1777681506547-c25ew</v>
+      </c>
+      <c r="B2497" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2497" t="str">
+        <v>07:25 p. m.</v>
+      </c>
+      <c r="D2497" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2497" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2497">
+        <v>8000</v>
+      </c>
+      <c r="G2497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="str">
+        <v>V-1777681962585-weedj</v>
+      </c>
+      <c r="B2498" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2498" t="str">
+        <v>07:32 p. m.</v>
+      </c>
+      <c r="D2498" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2498" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2498">
+        <v>8000</v>
+      </c>
+      <c r="G2498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="str">
+        <v>V-1777682123218-yt8wh</v>
+      </c>
+      <c r="B2499" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2499" t="str">
+        <v>07:35 p. m.</v>
+      </c>
+      <c r="D2499" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2499" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2499">
+        <v>8000</v>
+      </c>
+      <c r="G2499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="str">
+        <v>V-1777682331480-8gfv6</v>
+      </c>
+      <c r="B2500" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2500" t="str">
+        <v>07:38 p. m.</v>
+      </c>
+      <c r="D2500" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2500" t="str">
+        <v>Cerveza Club Colombia (x3)</v>
+      </c>
+      <c r="F2500">
+        <v>24000</v>
+      </c>
+      <c r="G2500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="str">
+        <v>V-1777682516485-a6nwy</v>
+      </c>
+      <c r="B2501" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2501" t="str">
+        <v>07:41 p. m.</v>
+      </c>
+      <c r="D2501" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2501" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2501">
+        <v>16000</v>
+      </c>
+      <c r="G2501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="str">
+        <v>V-1777682721600-67ml2</v>
+      </c>
+      <c r="B2502" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2502" t="str">
+        <v>07:45 p. m.</v>
+      </c>
+      <c r="D2502" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2502" t="str">
+        <v>Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2502">
+        <v>8000</v>
+      </c>
+      <c r="G2502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="str">
+        <v>V-1777683104026-gcauq</v>
+      </c>
+      <c r="B2503" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2503" t="str">
+        <v>07:51 p. m.</v>
+      </c>
+      <c r="D2503" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2503" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2503">
+        <v>16000</v>
+      </c>
+      <c r="G2503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="str">
+        <v>V-1777683523201-uj42a</v>
+      </c>
+      <c r="B2504" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2504" t="str">
+        <v>07:58 p. m.</v>
+      </c>
+      <c r="D2504" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2504" t="str">
+        <v>Aguardiente Ligth Botella (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2504">
+        <v>96000</v>
+      </c>
+      <c r="G2504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="str">
+        <v>V-1777683685046-akimv</v>
+      </c>
+      <c r="B2505" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2505" t="str">
+        <v>08:01 p. m.</v>
+      </c>
+      <c r="D2505" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2505" t="str">
+        <v>Aguardiente Ligth Media (x1), Soda (x1)</v>
+      </c>
+      <c r="F2505">
+        <v>61000</v>
+      </c>
+      <c r="G2505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="str">
+        <v>V-1777684095196-hclm2</v>
+      </c>
+      <c r="B2506" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2506" t="str">
+        <v>08:08 p. m.</v>
+      </c>
+      <c r="D2506" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2506" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2506">
+        <v>16000</v>
+      </c>
+      <c r="G2506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="str">
+        <v>V-1777684515902-q0ju9</v>
+      </c>
+      <c r="B2507" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2507" t="str">
+        <v>08:15 p. m.</v>
+      </c>
+      <c r="D2507" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2507" t="str">
+        <v>Ron 5 años Media (x1), Soda (x1)</v>
+      </c>
+      <c r="F2507">
+        <v>83000</v>
+      </c>
+      <c r="G2507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="str">
+        <v>V-1777685052685-2yblc</v>
+      </c>
+      <c r="B2508" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2508" t="str">
+        <v>08:24 p. m.</v>
+      </c>
+      <c r="D2508" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2508" t="str">
+        <v>Cerveza Aguila Ligth (x1)</v>
+      </c>
+      <c r="F2508">
+        <v>8000</v>
+      </c>
+      <c r="G2508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="str">
+        <v>V-1777685169644-3kv17</v>
+      </c>
+      <c r="B2509" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2509" t="str">
+        <v>08:26 p. m.</v>
+      </c>
+      <c r="D2509" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2509" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2509">
+        <v>8000</v>
+      </c>
+      <c r="G2509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="str">
+        <v>V-1777685284265-pux8l</v>
+      </c>
+      <c r="B2510" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2510" t="str">
+        <v>08:28 p. m.</v>
+      </c>
+      <c r="D2510" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2510" t="str">
+        <v>Cerveza Club Colombia (x3)</v>
+      </c>
+      <c r="F2510">
+        <v>24000</v>
+      </c>
+      <c r="G2510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="str">
+        <v>V-1777685664233-ey4gi</v>
+      </c>
+      <c r="B2511" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2511" t="str">
+        <v>08:34 p. m.</v>
+      </c>
+      <c r="D2511" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2511" t="str">
+        <v>Aguardiente Ligth Media (x1), Cerveza Poker (x1)</v>
+      </c>
+      <c r="F2511">
+        <v>64000</v>
+      </c>
+      <c r="G2511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="str">
+        <v>V-1777685774820-y8nyr</v>
+      </c>
+      <c r="B2512" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2512" t="str">
+        <v>08:36 p. m.</v>
+      </c>
+      <c r="D2512" t="str">
+        <v>Luisa-Dreisy</v>
+      </c>
+      <c r="E2512" t="str">
+        <v>Cerveza Corona (x2), Cerveza Poker (x1), Gatorade (x1)</v>
+      </c>
+      <c r="F2512">
+        <v>38000</v>
+      </c>
+      <c r="G2512">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="str">
+        <v>V-1777686320590-2bysg</v>
+      </c>
+      <c r="B2513" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2513" t="str">
+        <v>08:45 p. m.</v>
+      </c>
+      <c r="D2513" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2513" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2513">
+        <v>16000</v>
+      </c>
+      <c r="G2513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="str">
+        <v>V-1777688674556-7sj32</v>
+      </c>
+      <c r="B2514" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2514" t="str">
+        <v>09:24 p. m.</v>
+      </c>
+      <c r="D2514" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2514" t="str">
+        <v>Cerveza Club Colombia (x2)</v>
+      </c>
+      <c r="F2514">
+        <v>16000</v>
+      </c>
+      <c r="G2514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="str">
+        <v>V-1777688968212-h6rvo</v>
+      </c>
+      <c r="B2515" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2515" t="str">
+        <v>09:29 p. m.</v>
+      </c>
+      <c r="D2515" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2515" t="str">
+        <v>Ron 5 años Media (x1), Cerveza Aguila Ligth (x1), Soda (x2)</v>
+      </c>
+      <c r="F2515">
+        <v>96000</v>
+      </c>
+      <c r="G2515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="str">
+        <v>V-1777691896382-l8vhx</v>
+      </c>
+      <c r="B2516" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2516" t="str">
+        <v>10:18 p. m.</v>
+      </c>
+      <c r="D2516" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2516" t="str">
+        <v>Cerveza Club Colombia (x1)</v>
+      </c>
+      <c r="F2516">
+        <v>8000</v>
+      </c>
+      <c r="G2516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="str">
+        <v>V-1777692251928-adgcg</v>
+      </c>
+      <c r="B2517" t="str">
+        <v>1/5/2026</v>
+      </c>
+      <c r="C2517" t="str">
+        <v>10:24 p. m.</v>
+      </c>
+      <c r="D2517" t="str">
+        <v>Fredy</v>
+      </c>
+      <c r="E2517" t="str">
+        <v>Aguardiente Cristal Media (x1), Ginger Canada Dry (x1), Agua Botella Grande (x1)</v>
+      </c>
+      <c r="F2517">
+        <v>64000</v>
+      </c>
+      <c r="G2517">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2426"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2517"/>
   </ignoredErrors>
 </worksheet>
 </file>